--- a/raw/Features.xlsx
+++ b/raw/Features.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="615">
   <si>
     <t>feature_ID</t>
   </si>
@@ -41,73 +41,34 @@
     <t>Does the language have the same TAM marking in negated clauses?</t>
   </si>
   <si>
-    <t>050-1</t>
-  </si>
-  <si>
-    <t>Gender agreement of adnominal adjectives: No adjective agrees with the noun</t>
-  </si>
-  <si>
-    <t>040-1</t>
-  </si>
-  <si>
-    <t>Gender agreement of adnominal adjectives: Only few adjectives agree with the noun</t>
-  </si>
-  <si>
-    <t>040-2</t>
-  </si>
-  <si>
-    <t>Gender agreement of adnominal adjectives: Many adjectives agree with the noun</t>
-  </si>
-  <si>
-    <t>040-3</t>
-  </si>
-  <si>
-    <t>Gender agreement of adnominal adjectives: All adjectives agree with the noun</t>
-  </si>
-  <si>
-    <t>040-4</t>
-  </si>
-  <si>
-    <t>Predicative adjectives: Verbal encoding</t>
-  </si>
-  <si>
-    <t>074-1</t>
-  </si>
-  <si>
-    <t>Predicative adjectives: Nonverbal encoding</t>
-  </si>
-  <si>
-    <t>118A-2</t>
-  </si>
-  <si>
-    <t>Predicative adjectives: Mixed [encoding]</t>
-  </si>
-  <si>
-    <t>118A-3</t>
-  </si>
-  <si>
-    <t>Predicative noun phrases: (V) Invariant copula</t>
-  </si>
-  <si>
-    <t>073-1</t>
-  </si>
-  <si>
-    <t>Predicative noun phrases: (V) Variable copula</t>
-  </si>
-  <si>
-    <t>073-3</t>
-  </si>
-  <si>
-    <t>Predicative noun phrases: (V) No copula</t>
-  </si>
-  <si>
-    <t>073-2</t>
-  </si>
-  <si>
-    <t>Zero copula for predicate nominals: Zero copula is impossible</t>
-  </si>
-  <si>
-    <t>120A-1</t>
+    <t>050</t>
+  </si>
+  <si>
+    <t>Gender agreement of adnominal adjectives</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>Predicative adjectives</t>
+  </si>
+  <si>
+    <t>074</t>
+  </si>
+  <si>
+    <t>118A</t>
+  </si>
+  <si>
+    <t>Predicative noun phrases</t>
+  </si>
+  <si>
+    <t>073</t>
+  </si>
+  <si>
+    <t>Zero copula for predicate nominals</t>
+  </si>
+  <si>
+    <t>120A</t>
   </si>
   <si>
     <t>Is there an inclusive/exclusive distinction in personal pronouns? – no</t>
@@ -125,40 +86,25 @@
     <t>Is there an inclusive/exclusive distinction in personal pronouns? (V) yes</t>
   </si>
   <si>
-    <t>Inclusive/exclusive distinction in independent pronouns: No inclusive/exclusive</t>
-  </si>
-  <si>
-    <t>039A-3</t>
-  </si>
-  <si>
-    <t>Inclusive/exclusive distinction in independent pronouns: Inclusive/exclusive</t>
+    <t>Inclusive/exclusive distinction in independent pronouns</t>
   </si>
   <si>
     <t xml:space="preserve">For speakers of English (or any other European language), both the inclusive and the exclusive pronouns are to be translated as we. The difference between the two depends on the intended meaning. An inclusive pronoun necessarily includes reference to the addressee. For example, the Mandarin inclusive pronoun zámen means ‘we, I and you’; others can optionally be included. An exclusive pronoun, like the Mandarin pronoun wŏmen, excludes the addressee from the reference, resulting in a meaning like ‘I and some others, but not you’. </t>
   </si>
   <si>
-    <t>http://wals.info/chapter/39</t>
-  </si>
-  <si>
-    <t>039A-5</t>
-  </si>
-  <si>
-    <t>Inclusive/exclusive distinction in independent personal pronouns: No inclusive/exclusive distinction</t>
+    <t>039A</t>
+  </si>
+  <si>
+    <t>Inclusive/exclusive distinction in independent personal pronouns</t>
+  </si>
+  <si>
+    <t>In this feature (based on WALS feature 39, by Michael Cysouw), we ask whether a language has an inclusive/exclusive distinction in independent personal pronouns. An inclusive pronouns means 'we including the hearer', and an exclusive pronoun means 'we excluding the hearer'.</t>
   </si>
   <si>
     <t>http://apics-online.info/parameters/15</t>
   </si>
   <si>
-    <t>015-1</t>
-  </si>
-  <si>
-    <t>Inclusive/exclusive distinction in independent personal pronouns: Inclusive and exclusive differentiated</t>
-  </si>
-  <si>
-    <t>In this feature (based on WALS feature 39, by Michael Cysouw), we ask whether a language has an inclusive/exclusive distinction in independent personal pronouns. An inclusive pronouns means 'we including the hearer', and an exclusive pronoun means 'we excluding the hearer'.</t>
-  </si>
-  <si>
-    <t>015-2</t>
+    <t>015</t>
   </si>
   <si>
     <t>Complementizer Clause (V: Yes)</t>
@@ -197,7 +143,7 @@
     <t>Neg 14</t>
   </si>
   <si>
-    <t>Numeral classifiers: Absent</t>
+    <t>Numeral classifiers</t>
   </si>
   <si>
     <t>Gil (2005): Gil (2005): "in many ... languages, nouns in construction with numerals may occur with an additional grammatical element even when such nouns are of high countability... Such elements are typically referred to as sortal numeral classifiers. This term makes reference to one of the most salient functions of such forms, which is to divide the inventory of count nouns into semantic classes, each of which is associated with a different classifier."</t>
@@ -206,16 +152,16 @@
     <t>http://wals.info/feature/55A</t>
   </si>
   <si>
-    <t>055A-1</t>
-  </si>
-  <si>
-    <t>Number of genders: None</t>
+    <t>055A</t>
+  </si>
+  <si>
+    <t>Number of genders</t>
   </si>
   <si>
     <t>http://wals.info/feature/30A</t>
   </si>
   <si>
-    <t>030A-1</t>
+    <t>030A</t>
   </si>
   <si>
     <t>The language has no numeral classifiers</t>
@@ -224,85 +170,37 @@
     <t>http://apics-online.info/parameters/36</t>
   </si>
   <si>
-    <t>036-1</t>
-  </si>
-  <si>
-    <t>Numeral classifiers: Optional</t>
-  </si>
-  <si>
-    <t>055A-2</t>
-  </si>
-  <si>
-    <t>Numeral Classifiers: Obligatory</t>
-  </si>
-  <si>
-    <t>055A-3</t>
-  </si>
-  <si>
-    <t>Position of pronominal possessive affixes: Possessive prefixes</t>
+    <t>036</t>
+  </si>
+  <si>
+    <t>Position of pronominal possessive affixes</t>
   </si>
   <si>
     <t>http://wals.info/feature/57A</t>
   </si>
   <si>
-    <t>057A-1</t>
-  </si>
-  <si>
-    <t>Position of pronominal possessive affixes: Possessive suffixes</t>
-  </si>
-  <si>
-    <t>057A-2</t>
-  </si>
-  <si>
-    <t>Position of pronominal possessive affixes: Both possessive prefixes and possessive suffixes, with neither primary</t>
-  </si>
-  <si>
-    <t>057A-3</t>
-  </si>
-  <si>
-    <t>Position of pronominal possessive affixes: No possessive affixes</t>
-  </si>
-  <si>
-    <t>057A-4</t>
-  </si>
-  <si>
-    <t>Obligatory possessive inflection: Exists</t>
+    <t>057A</t>
+  </si>
+  <si>
+    <t>Obligatory possessive inflection</t>
   </si>
   <si>
     <t>http://wals.info/feature/58A</t>
   </si>
   <si>
-    <t>058A-1</t>
-  </si>
-  <si>
-    <t>Obligatory possessive inflection: Absent</t>
-  </si>
-  <si>
-    <t>058A-2</t>
-  </si>
-  <si>
-    <t>Number of possessive nouns: None reported</t>
+    <t>058A</t>
+  </si>
+  <si>
+    <t>Number of possessive nouns</t>
+  </si>
+  <si>
+    <t>Bickel &amp; Nichols (2005): "The head noun 'chicken' is grammatically non-possessible, though as the example indicates its referent can be owned, showing that non-possessibility is a grammatical rather than a purely semantic property. The formally possessed generic noun 'pet' is a more or less conventional choice in this construction.  Such nouns will be called possessive nouns here. ... In most languages with possessive nouns, there is a small and closed set of nouns grammaticalized for such usage, and their semantics amounts to classification of possessive relations (so that possessive nouns are also referred to as possessive classifiers)."</t>
   </si>
   <si>
     <t>http://wals.info/feature/58B</t>
   </si>
   <si>
-    <t>058B-1</t>
-  </si>
-  <si>
-    <t>Number of possessive nouns: Two to four</t>
-  </si>
-  <si>
-    <t>Bickel &amp; Nichols (2005): "The head noun 'chicken' is grammatically non-possessible, though as the example indicates its referent can be owned, showing that non-possessibility is a grammatical rather than a purely semantic property. The formally possessed generic noun 'pet' is a more or less conventional choice in this construction.  Such nouns will be called possessive nouns here. ... In most languages with possessive nouns, there is a small and closed set of nouns grammaticalized for such usage, and their semantics amounts to classification of possessive relations (so that possessive nouns are also referred to as possessive classifiers)."</t>
-  </si>
-  <si>
-    <t>058B-3</t>
-  </si>
-  <si>
-    <t>Number of possessive nouns: Five or more</t>
-  </si>
-  <si>
-    <t>058B-4</t>
+    <t>058B</t>
   </si>
   <si>
     <t>Are there definite or specific articles?</t>
@@ -318,13 +216,13 @@
     <t>GB020</t>
   </si>
   <si>
-    <t>Definite article: Definite affix</t>
+    <t>Definite article</t>
   </si>
   <si>
     <t>http://wals.info/feature/37A</t>
   </si>
   <si>
-    <t>037A-3</t>
+    <t>037A</t>
   </si>
   <si>
     <t>Do indefinite nominals commonly have indefinite articles?</t>
@@ -384,37 +282,13 @@
     <t>GB026</t>
   </si>
   <si>
-    <t>Marking of patient noun phrases: No marking of patient NPs</t>
+    <t>Marking of patient noun phrases</t>
   </si>
   <si>
     <t>http://apics-online.info/parameters/57</t>
   </si>
   <si>
-    <t>057-1</t>
-  </si>
-  <si>
-    <t>Marking of patient noun phrases: Only definite patient NPs are marked</t>
-  </si>
-  <si>
-    <t>057-2</t>
-  </si>
-  <si>
-    <t>Marking of patient noun phrases: Only animate patient NPs are marked</t>
-  </si>
-  <si>
-    <t>057-3</t>
-  </si>
-  <si>
-    <t>Marking of patient noun phrases: Only definite and animate patient NPs are marked</t>
-  </si>
-  <si>
-    <t>057-4</t>
-  </si>
-  <si>
-    <t>Marking of patient noun phrases: All patient NPs are marked</t>
-  </si>
-  <si>
-    <t>57-5</t>
+    <t>057</t>
   </si>
   <si>
     <t>Standard negation is a particle that precedes the verb</t>
@@ -486,40 +360,7 @@
     <t>22</t>
   </si>
   <si>
-    <t>Is the case marking obligatory on the adjective? – 1</t>
-  </si>
-  <si>
-    <t>https://diacl.ht.lu.se/TypoVariant/Details/263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CASE-ADJ </t>
-  </si>
-  <si>
-    <t>Is the case marking realized on the article? – 1</t>
-  </si>
-  <si>
-    <t>https://diacl.ht.lu.se/TypoVariant/Details/264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CASE-ART </t>
-  </si>
-  <si>
-    <t>Is the case marking obligatorily realized on the noun?  – 1</t>
-  </si>
-  <si>
-    <t>https://diacl.ht.lu.se/TypoVariant/Details/262</t>
-  </si>
-  <si>
-    <t>Gender Distinctions in Independent Personal Pronouns: No gender distinctions</t>
-  </si>
-  <si>
-    <t>http://wals.info/feature/44A</t>
-  </si>
-  <si>
-    <t>044A-6</t>
-  </si>
-  <si>
-    <t>Person syncretism in independent personal pronouns: No person syncretism</t>
+    <t>Person syncretism in independent personal pronouns</t>
   </si>
   <si>
     <t>In most languages, there are distinct forms for the three persons in both singular and plural (and in the dual as well, if there is one), e.g. French moi, toi, lui/elle, nous, vous, eux/elles. But in some languages, there is person syncretism, i.e. there is a form in the paradigm of independent personal pronouns that serves for more than one person. For instance, some languages have the same form in the 1st and 2nd person plural (e.g. Haitian Creole nou), and some languages have the same form in the 2nd and 3rd person plural (e.g. Seychelles Creole zot). Note that we are not concerned with pure number syncretism here (e.g. English you for 2sg/2pl).</t>
@@ -528,70 +369,22 @@
     <t>http://apics-online.info/parameters/16</t>
   </si>
   <si>
-    <t>016-1</t>
-  </si>
-  <si>
-    <t>Person syncretism in independent personal pronouns: Syncretism between 1st and 2nd person</t>
-  </si>
-  <si>
-    <t>016-2</t>
-  </si>
-  <si>
-    <t>Person syncretism in independent personal pronouns: Syncretism between 2nd and 3rd person</t>
-  </si>
-  <si>
-    <t>016-3</t>
-  </si>
-  <si>
-    <t>Special dependent person forms for subject and object: No dependent person forms</t>
-  </si>
-  <si>
-    <t>017-1</t>
-  </si>
-  <si>
-    <t>Special dependent person forms for subject and object: Only dependent subject forms</t>
-  </si>
-  <si>
-    <t>017-2</t>
-  </si>
-  <si>
-    <t>Special dependent person forms for subject and object: Only dependent object forms</t>
-  </si>
-  <si>
-    <t>017-3</t>
-  </si>
-  <si>
-    <t>Special dependent person forms for subject and object: Dependent subject and object forms</t>
-  </si>
-  <si>
-    <t>017-4</t>
-  </si>
-  <si>
-    <t>Politeness distinctions in second-person pronouns: No pronominal politeness distinction</t>
-  </si>
-  <si>
-    <t>018-1</t>
-  </si>
-  <si>
-    <t>Politeness distinctions in second-person pronouns: Binary pronominal politeness distinction</t>
-  </si>
-  <si>
-    <t>018-2</t>
-  </si>
-  <si>
-    <t>Politeness distinctions in second-person pronouns: Multiple pronominal politeness distinction</t>
-  </si>
-  <si>
-    <t>018-3</t>
-  </si>
-  <si>
-    <t>Politeness distinctions in second-person pronouns: Titles used as second person forms</t>
-  </si>
-  <si>
-    <t>018-4</t>
-  </si>
-  <si>
-    <t>Interrogative pronouns: All simple words</t>
+    <t>016</t>
+  </si>
+  <si>
+    <t>Special dependent person forms for subject and object</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>Politeness distinctions in second-person pronouns</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>Interrogative pronouns</t>
   </si>
   <si>
     <t>Here we look at the four interrogative pronouns ‘who’, ‘where’, ‘when’, and ‘how’ and ask whether they are expressed as simple, monomorphemic words as in the European lexifiers, or as compound expressions consisting of a generic noun and an adnominal interrogative word.
@@ -601,64 +394,16 @@
     <t>http://apics-online.info/parameters/19</t>
   </si>
   <si>
-    <t>019-1</t>
-  </si>
-  <si>
-    <t>Interrogative pronouns: One compound expression</t>
-  </si>
-  <si>
-    <t>019-2</t>
-  </si>
-  <si>
-    <t>Interrogative pronouns: Two compound expressions</t>
-  </si>
-  <si>
-    <t>019-3</t>
-  </si>
-  <si>
-    <t>Interrogative pronouns: Three compound expressions</t>
-  </si>
-  <si>
-    <t>019-4</t>
-  </si>
-  <si>
-    <t>Interrogative pronouns: Four compound expressions</t>
-  </si>
-  <si>
-    <t>019-5</t>
-  </si>
-  <si>
-    <t>Pronoun conjunction: Singular pronoun overtly conjoined with other conjunct</t>
+    <t>019</t>
+  </si>
+  <si>
+    <t>Pronoun conjunction</t>
   </si>
   <si>
     <t>apics-online.info/parameters/20</t>
   </si>
   <si>
-    <t>020-1</t>
-  </si>
-  <si>
-    <t>Pronoun conjunction: Inclusory pronoun juxtaposed with subset NP</t>
-  </si>
-  <si>
-    <t>020-2</t>
-  </si>
-  <si>
-    <t>Pronoun conjunction: Inclusory pronoun plus marker plus subset NP</t>
-  </si>
-  <si>
-    <t>020-3</t>
-  </si>
-  <si>
-    <t>Pronoun conjunction: Inclusory pronoun plus numeral plus subset NP</t>
-  </si>
-  <si>
-    <t>020-4</t>
-  </si>
-  <si>
-    <t>Pronoun conjunction: Singular pronoun juxtaposed with other conjunct</t>
-  </si>
-  <si>
-    <t>020-5</t>
+    <t>020</t>
   </si>
   <si>
     <t>Is there an instrumental applicative marker on the verb (including indexing)?</t>
@@ -682,25 +427,13 @@
     <t>GB105</t>
   </si>
   <si>
-    <t>Ditransitive Constructions: The Verb 'Give': Indirect-object construction</t>
+    <t>Ditransitive Constructions: The Verb 'Give'</t>
   </si>
   <si>
     <t>http://wals.info/feature/105A</t>
   </si>
   <si>
-    <t>105A-1</t>
-  </si>
-  <si>
-    <t>Ditransitive Constructions: The Verb 'Give': Double-object construction</t>
-  </si>
-  <si>
-    <t>105A-2</t>
-  </si>
-  <si>
-    <t>Ditransitive Constructions: The Verb 'Give': Secondary-object construction</t>
-  </si>
-  <si>
-    <t>105A-3</t>
+    <t>105A</t>
   </si>
   <si>
     <t>Is there directional or locative morphological marking on verbs?</t>
@@ -844,81 +577,31 @@
     <t>ARGEX1-2-8</t>
   </si>
   <si>
-    <t>Order of Subject, Object and Verb: SOV</t>
+    <t>Order of Subject, Object and Verb</t>
   </si>
   <si>
     <t>http://wals.info/feature/81A</t>
   </si>
   <si>
-    <t>081A-1</t>
-  </si>
-  <si>
-    <t>Order of Subject, Object and Verb: SVO</t>
-  </si>
-  <si>
-    <t>081A-2</t>
-  </si>
-  <si>
-    <t>Order of Subject, Object and Verb: VSO</t>
-  </si>
-  <si>
-    <t>081A-3</t>
-  </si>
-  <si>
-    <t>Order of Subject, Object and Verb: VOS</t>
-  </si>
-  <si>
-    <t>081A-4</t>
-  </si>
-  <si>
-    <t>Order of Subject, Object and Verb: OVS</t>
-  </si>
-  <si>
-    <t>081A-5</t>
-  </si>
-  <si>
-    <t>Order of Subject, Object and Verb: OSV</t>
-  </si>
-  <si>
-    <t>081A-6</t>
-  </si>
-  <si>
-    <t>Order of Subject, Object and Verb: No dominant order</t>
-  </si>
-  <si>
-    <t>081A-7</t>
-  </si>
-  <si>
-    <t>Occurrence of nominal plural markers: No plural marking</t>
+    <t>081A</t>
+  </si>
+  <si>
+    <t>Occurrence of nominal plural markers</t>
   </si>
   <si>
     <t>http://apics-online.info/parameters/22</t>
   </si>
   <si>
-    <t>022-1</t>
-  </si>
-  <si>
-    <t>Occurrence of nominal plural markers: Variable plural marking of human nouns</t>
-  </si>
-  <si>
-    <t>022-2</t>
-  </si>
-  <si>
-    <t>Occurrence of nominal plural markers: Variable plural marking of human or inanimate nouns</t>
-  </si>
-  <si>
-    <t>022-3</t>
-  </si>
-  <si>
-    <t>Occurrence of nominal plural markers: Invariant plural marking</t>
-  </si>
-  <si>
-    <t>022-4</t>
+    <t>022</t>
   </si>
   <si>
     <t>Is there a class of patient-labile verbs?</t>
   </si>
   <si>
+    <t>The term ‘labileʼ is the most commonly used label for verbs which can be used transitively or intransitively without any formal change. A distinction is made between patient lability, more commonly referred to as P-lability, and agent lability or A-lability. P-lability stands for patient-preserving lability, that is, the P argument is preserved in the intransitive construction, as in I broke the stick[P] / The stick broke. A-lability stands for agent-preserving lability, that is the A argument is preserved in the intransitive construction, as in John[A] drinks tea / John drinks.
+This question asks only about P-labile verbs. Semantically, two things can happen with P-labile verbs. In case of (a) argument structure modifying P-lability, an otherwise transitive verb is used in the intransitive construction encoding an argument structure from which the A argument of the transitive construction is absent. In case of (b) less common argument structure preserving P-lability, the verb in its intransitive use implies the same participants with the same roles as in its transitive use, but in the intransitive use, the A argument is not expressed and is interpreted as non-specific.</t>
+  </si>
+  <si>
     <t>http://grambank.clld.org/parameters/GB401</t>
   </si>
   <si>
@@ -928,6 +611,10 @@
     <t>Does the verb for 'see' have suppletive verb forms?</t>
   </si>
   <si>
+    <t>This question concerns strong suppletion in verb(s) of seeing/watching/looking. Suppletion is a process where a lexeme is changed in such a way that the new form does not resemble the previous when it appears in a different position in the paradigm. ‘Weak’ suppletion is not included. An example of this is English went and go. In this case, the verb is suppletive for tense.
+Please note that we are not interested in words that are translated as ‘look for’, ‘seek’ etc. This feature is concerned with the transitive verb of the act of seeing, not with metaphorical extensions such as 'seek up’.</t>
+  </si>
+  <si>
     <t>http://grambank.clld.org/parameters/GB402</t>
   </si>
   <si>
@@ -937,6 +624,9 @@
     <t>Does the verb for 'come' have suppletive verb forms?</t>
   </si>
   <si>
+    <t xml:space="preserve">This question concerns strong suppletion in verbs of coming. Suppletion is a process where a lexeme is changed in such a way that the new form does not resemble the previous when it appears in a different position in the paradigm. An example of this is English went and go. In this case, the verb is suppletive for tense. ‘Weak’ suppletion is not included. </t>
+  </si>
+  <si>
     <t>http://grambank.clld.org/parameters/GB403</t>
   </si>
   <si>
@@ -946,6 +636,9 @@
     <t>Is there any accusative alignment of flagging?</t>
   </si>
   <si>
+    <t>Are P arguments flagged differently from S arguments (i.e. do they show accusative alignment)? Flagging covers any kind of argument marking on the argument itself (e.g. by case or adposition marking). The marking can be phonologically free or bound. The marking of A arguments is not relevant for establishing whether there is any accusative flagging or not, it is the difference between S and P flagging that results in 1. In case of split flagging systems (specifically, differential object marking), code as 1 if any of the subsystems (e.g. only nouns or only pronouns, or a particular group of nouns) shows accusative alignment. Note that although alignment types are occasionally associated with entire languages (e.g. when one says that "Dyirbal is an ergative language"), they in fact apply only to individual constructions. This question asks only about the alignment of flagging, the alignment of indexing or of any other construction is irrelevant for this question.</t>
+  </si>
+  <si>
     <t>http://grambank.clld.org/parameters/GB408</t>
   </si>
   <si>
@@ -955,12 +648,18 @@
     <t>Is there any ergative alignment of flagging?</t>
   </si>
   <si>
+    <t>Are A arguments flagged differently from S arguments (i.e. do they show ergative alignment)? Flagging covers any kind of argument marking on the argument itself (e.g. by case or adposition marking). The marking can be phonologically free or bound. The marking of P arguments is not relevant for establishing whether there is any ergative flagging or not, it is the difference between S and A flagging that results in 1. In case of split flagging systems (specifically, split ergativity), code as 1 if any of the subsystems (e.g. only nouns or only pronouns, or a particular tense or person) shows ergative alignment. Note that although alignment types are occasionally associated with entire languages (e.g. when one says that "Dyirbal is an ergative language"), they in fact apply only to individual constructions. This question asks only about the alignment of flagging, the alignment of indexing or of any other construction is irrelevant for this question.</t>
+  </si>
+  <si>
     <t>GB409</t>
   </si>
   <si>
     <t>Is there any neutral alignment of monotransitive flagging?</t>
   </si>
   <si>
+    <t>Are S, A, and P arguments flagged identically (i.e. are they neutrally aligned)? Flagging covers any kind of argument marking on the argument itself (e.g. by case or adposition marking). The marking can be phonologically free or bound. Reply with 1 if none of the three arguments is overtly flagged (i.e. if all three arguments are zero-marked). In case of differential flagging systems, reply with 1 if any of the subsystems (e.g. a particular tense) shows neutral alignment. Reply with 1 if only nouns or only pronouns shows neutral alignment. Reply with 1 also if some or just one personal pronoun shows neutral alignment. Reply with 1 if a substantial class of nouns shows neutral alignment. Note that although alignment types are occasionally associated with entire languages (e.g. when one says that "Dyirbal is an ergative language"), they in fact apply only to individual constructions. This question asks only about the alignment of flagging, the alignment of indexing or of any other construction is irrelevant for this question.</t>
+  </si>
+  <si>
     <t>http://grambank.clld.org/parameters/GB410</t>
   </si>
   <si>
@@ -970,6 +669,9 @@
     <t>Is there a politeness distinction in 2nd person forms?</t>
   </si>
   <si>
+    <t>This feature asks whether there are different second person pronoun forms that are used based on the level of respect accorded by the speaker to the addressee. In some cases polite pronouns are used to indicate a level of formality or unfamiliarity between speaker and addressee. In other cases politeness distinctions are used according to very specific social relationships between speaker and addressee, such as relative age, social status, or kinship. If multiple second person pronoun forms exist in a single number category, and their use is patterned according to the level of intimacy or hierarchy of social relationship between speaker and addressee, this will suffice for a 1 code. The contrastive forms may or may not have other uses (e.g. in French the form _tu_ is used only for second person singular informal, while _vous_ is used for both second person singular polite and second person plural); a politeness distinction triggers a 1 for this feature regardless of whether the relevant forms have other functions/meanings.</t>
+  </si>
+  <si>
     <t>http://grambank.clld.org/parameters/GB415</t>
   </si>
   <si>
@@ -979,6 +681,10 @@
     <t>Is there a preposed complementizer in complements of verbs of thinking and/or knowing?</t>
   </si>
   <si>
+    <t>Complementizers are markers (free or bound) which are able to turn a clause into the subject or object of a sentence. In some of the literature these are also known as ‘conjunctions’. The complementizer in the sentence I knew that Ashley was a genius is that and it is preposed to the complement clause (Ashley was a genius). The complementizer does not have to be phonologically free, the position in relation to the complement clause is what is relevant. This feature concerns whether the complementizer precedes the complement or not.
+This feature specifically targets sentences with verbs of thinking and knowing, where the complement clause is an object (I know that he is truthful or I think that this is a bad idea). This is done so that we get more comparable data across the sample.</t>
+  </si>
+  <si>
     <t>http://grambank.clld.org/parameters/GB421</t>
   </si>
   <si>
@@ -1282,172 +988,43 @@
     <t>GB306</t>
   </si>
   <si>
-    <t>Gender distinctions in personal pronouns: No gender distinctions</t>
-  </si>
-  <si>
-    <t>http://apics-online.info/parameters/13</t>
-  </si>
-  <si>
-    <t>013-1</t>
-  </si>
-  <si>
-    <t>Gender distinctions in personal pronouns: In 3rd person singular only</t>
-  </si>
-  <si>
-    <t>013-2</t>
-  </si>
-  <si>
-    <t>Gender distinctions in personal pronouns: In 3rd person singular and plural only</t>
-  </si>
-  <si>
-    <t>013-3</t>
-  </si>
-  <si>
-    <t>Gender distinctions in personal pronouns: In 2nd person but not in 3rd person</t>
-  </si>
-  <si>
-    <t>013-4</t>
-  </si>
-  <si>
-    <t>Gender Distinctions in Independent Personal Pronouns: In 3rd person + 1st and/or 2nd person</t>
-  </si>
-  <si>
-    <t>044A-1</t>
-  </si>
-  <si>
-    <t>Gender Distinctions in Independent Personal Pronouns: 3rd person only, but also non-singular</t>
-  </si>
-  <si>
-    <t>044A-2</t>
-  </si>
-  <si>
-    <t>Gender Distinctions in Independent Personal Pronouns: 3rd person singular only</t>
-  </si>
-  <si>
-    <t>044A-3</t>
-  </si>
-  <si>
-    <t>Gender Distinctions in Independent Personal Pronouns: 1st or 2nd person but not 3rd</t>
-  </si>
-  <si>
-    <t>044A-4</t>
-  </si>
-  <si>
-    <t>Gender Distinctions in Independent Personal Pronouns: 3rd person non-singular only</t>
-  </si>
-  <si>
-    <t>044A-5</t>
-  </si>
-  <si>
-    <t>Dual in independent personal pronouns: No special dual form</t>
-  </si>
-  <si>
-    <t>http://apics-online.info/parameters/14</t>
-  </si>
-  <si>
-    <t>014-1</t>
-  </si>
-  <si>
-    <t>Dual in independent personal pronouns: Dual form in all three persons</t>
-  </si>
-  <si>
-    <t>014-2</t>
-  </si>
-  <si>
-    <t>Dual in independent personal pronouns: Dual form only in first person</t>
-  </si>
-  <si>
-    <t>014-3</t>
-  </si>
-  <si>
-    <t>Nominal plural marker and third-person-plural pronoun: No nominal plural word</t>
+    <t>Gender Distinctions in Independent Personal Pronouns</t>
+  </si>
+  <si>
+    <t>http://wals.info/feature/44A</t>
+  </si>
+  <si>
+    <t>044A</t>
+  </si>
+  <si>
+    <t>Nominal plural marker and third-person-plural pronoun</t>
   </si>
   <si>
     <t>http://apics-online.info/parameters/25</t>
   </si>
   <si>
-    <t>025-1</t>
-  </si>
-  <si>
-    <t>Nominal plural marker and third-person-plural pronoun: Identity</t>
-  </si>
-  <si>
-    <t>025-2</t>
-  </si>
-  <si>
-    <t>Nominal plural marker and third-person-plural pronoun: Differentiation</t>
-  </si>
-  <si>
-    <t>025-3</t>
-  </si>
-  <si>
-    <t>Nominal plural marker and third-person-plural pronoun: Overlap</t>
-  </si>
-  <si>
-    <t>025-4</t>
-  </si>
-  <si>
-    <t>Functions of reduplication: No reduplication</t>
+    <t>025</t>
+  </si>
+  <si>
+    <t>Functions of reduplication</t>
   </si>
   <si>
     <t>http://apics-online.info/parameters/26</t>
   </si>
   <si>
-    <t>026-1</t>
-  </si>
-  <si>
-    <t>Functions of reduplication: Only iconic functions</t>
-  </si>
-  <si>
-    <t>026-2</t>
-  </si>
-  <si>
-    <t>Functions of reduplication: Attenuating function</t>
-  </si>
-  <si>
-    <t>026-3</t>
-  </si>
-  <si>
-    <t>Functions of reduplication: Word-class-changing function</t>
-  </si>
-  <si>
-    <t>026-4</t>
-  </si>
-  <si>
-    <t>Functions of reduplication: Attenuating and word-class-changing function</t>
-  </si>
-  <si>
-    <t>026-5</t>
-  </si>
-  <si>
-    <t>Definite articles: Definite article distinct from demonstratives</t>
+    <t>026</t>
+  </si>
+  <si>
+    <t>Definite articles</t>
   </si>
   <si>
     <t>http://apics-online.info/parameters/28</t>
   </si>
   <si>
-    <t>028-1</t>
-  </si>
-  <si>
-    <t>Definite articles: Definite article identical to a demonstrative</t>
-  </si>
-  <si>
-    <t>028-2</t>
-  </si>
-  <si>
-    <t>Definite articles: No definite article, but indefinite article</t>
-  </si>
-  <si>
-    <t>028-3</t>
-  </si>
-  <si>
-    <t>Definite articles: Neither definite nor indefinite article</t>
-  </si>
-  <si>
-    <t>028-4</t>
-  </si>
-  <si>
-    <t>Indefinite articles: Indefinite article distinct from numeral ‘one’</t>
+    <t>028</t>
+  </si>
+  <si>
+    <t>Indefinite articles</t>
   </si>
   <si>
     <t>"Many pidgins and creoles are like English in that they have a special indefinite article that is distinct from the numeral ‘one’ ... This is the case in quite a few English-based and Dutch-based languages where the English (and similarly Dutch) distinction between a and one has survived." – "When a language has two different indefinite articles, one of which is identical to the numeral and one of which is distinct, it is classified as value 1 [distinct from numeral 'one'] (e.g. Nicaraguan Creole English, which has both a and wan)."</t>
@@ -1456,28 +1033,7 @@
     <t>http://apics-online.info/parameters/29</t>
   </si>
   <si>
-    <t>029-1</t>
-  </si>
-  <si>
-    <t>Indefinite articles: Indefinite article identical to numeral ‘one’</t>
-  </si>
-  <si>
-    <t>"In the majority of our languages the indefinite article is identical to the numeral ‘one’ ... This is the case in many Romance-based languages, where the nondistinctness of indefinite article and numeral was inherited from French/Spanish un and Portuguese um."</t>
-  </si>
-  <si>
-    <t>029-2</t>
-  </si>
-  <si>
-    <t>Indefinite articles: No indefinite article, but definite article</t>
-  </si>
-  <si>
-    <t>029-3</t>
-  </si>
-  <si>
-    <t>Indefinite articles: Neither indefinite nor definite article</t>
-  </si>
-  <si>
-    <t>029-4</t>
+    <t>029</t>
   </si>
   <si>
     <t>Are different posture verbs used obligatorily depending on an inanimate locatum's shape or position (e.g. 'to lie' vs. 'to stand')?</t>
@@ -1636,6 +1192,9 @@
     <t>Are all person categories neutralized in some voice, tense, aspect, mood and/or negation?</t>
   </si>
   <si>
+    <t>This question concerns languages which can index the person of an argument (S, A or P) somewhere in the clause (i.e. either on the verb or by clitics). The question asks whether person categories are not distinguished under certain circumstances. In order for there to be neutralization, there needs to be something to ‘neutralize’ to begin with, i.e. languages without person indexing should be coded 0 for this feature. All person categories should be neutralized for the language to be coded as 1. Do not consider phonologically independent pronouns for this question. Consider only independent clauses. Consider only the moods which allow all person categories of the language to be expressed (that is, ignore imperatives, jussives, etc.)</t>
+  </si>
+  <si>
     <t>http://grambank.clld.org/parameters/GB400</t>
   </si>
   <si>
@@ -1645,6 +1204,10 @@
     <t>Is there a postposed complementizer in complements of verbs of thinking and/or knowing?</t>
   </si>
   <si>
+    <t>Complementizers are markers (free or bound) which are able to turn a clause into the subject or object of a sentence. In some of the literature these are also known as ‘conjunctions’. The complementizer in the sentence _I knew that Ashley was a genius_ is _that_ and it is preposed to the complement clause (_Ashley was a genius_). The complementizer does not have to be phonologically free, the position in relation to the complement clause is what is relevant. This feature concerns if the complementizer follows the complement or not (e.g. _I knew Ashley was a genius that**_).
+This feature specifically targets sentences with verbs of thinking and knowing, where the complement clause is an object (_I know that he is truthful_ or _I think that this is a bad idea_). This is done so that we get more comparable data across the sample.</t>
+  </si>
+  <si>
     <t>http://grambank.clld.org/parameters/GB422</t>
   </si>
   <si>
@@ -1654,6 +1217,9 @@
     <t>Can adnominal possession be marked by a prefix on the possessor?</t>
   </si>
   <si>
+    <t>This feature targets a specific type of adnominal possessive construction, namely one where a possessor (either nominal or pronominal) is marked with a prefix or proclitic to indicate possession of an object. This frequently takes the form of a genitive prefix on a possessor, but may also involve other types of prefixes or proclitics. Crucially, the possession must be marked by an element that precedes and is phonologically bound to the possessor nominal/pronominal.</t>
+  </si>
+  <si>
     <t>http://grambank.clld.org/parameters/GB430</t>
   </si>
   <si>
@@ -1663,6 +1229,9 @@
     <t>Can adnominal possession be marked by a suffix on the possessor?</t>
   </si>
   <si>
+    <t>This feature targets a specific type of adnominal possessive construction, namely one where a possessor (either nominal or pronominal) is marked with a suffix or enclitic to indicate possession of an object. This frequently takes the form of a genitive suffix on a possessor, but may also involve other types of suffixes or enclitics. Crucially, the possession must be marked by an element that follows and is phonologically bound to the possessor noun/pronoun.</t>
+  </si>
+  <si>
     <t>http://grambank.clld.org/parameters/GB432</t>
   </si>
   <si>
@@ -1672,6 +1241,11 @@
     <t>Can the S or A argument be omitted from a pragmatically unmarked clause when the referent is inferrable from context ("pro-drop" or "null anaphora")?</t>
   </si>
   <si>
+    <t>This feature identifies languages that do not require a phonologically overt S or A argument expressed by a noun phrase or phonologically independent pronoun when the referent can be inferred from context. These languages are often called ‘pro-drop’ languages, and the phenomenon is generally referred to as ‘null anaphora’ or ‘zero anaphora’.
+Here ‘omitted’ means phonologically unexpressed (we do not intend for this feature to make any distinctions regarding the theoretical status of a null argument). To count as 1, pro-drop should occur where the S or A argument might otherwise be expressed by an independent pronoun or full noun phrase. Specifically, pro-drop should occur in simple, declarative main clauses.
+Pro-drop is not mutually exclusive with indexing of the S or A argument on the verb. If, in the absence of an independent pronoun or nominal S or A, there is indexing of this argument on the verb, you may still code 1.</t>
+  </si>
+  <si>
     <t>http://grambank.clld.org/parameters/GB522</t>
   </si>
   <si>
@@ -2134,34 +1708,22 @@
     <t>GB256</t>
   </si>
   <si>
-    <t>Exponence of Tense-Aspect-Mood Inflection: TAM+agreement</t>
+    <t>Exponence of Tense-Aspect-Mood Inflection</t>
   </si>
   <si>
     <t>https://wals.info/feature/21B</t>
   </si>
   <si>
-    <t>021B-2</t>
-  </si>
-  <si>
-    <t>Female and male animals: Preposed sex-denoting word</t>
+    <t>021B</t>
+  </si>
+  <si>
+    <t>Female and male animals</t>
   </si>
   <si>
     <t>https://apics-online.info/parameters/117</t>
   </si>
   <si>
-    <t>117-1</t>
-  </si>
-  <si>
-    <t>Female and male animals: Postposed sex-denoting word</t>
-  </si>
-  <si>
-    <t>117-2</t>
-  </si>
-  <si>
-    <t>Female and male animals: Sex-denoting suffix</t>
-  </si>
-  <si>
-    <t>117-4</t>
+    <t>117</t>
   </si>
   <si>
     <t>GUIDELINES</t>
@@ -2176,36 +1738,30 @@
 – [for multi-choice features, I propose that shared values should be ignored, even though this leads to including fewer languages]</t>
   </si>
   <si>
-    <t>Order of Subject and Verb: SV</t>
+    <t>Order of Subject and Verb</t>
   </si>
   <si>
     <t>http://wals.info/feature/82A</t>
   </si>
   <si>
-    <t>082A-1</t>
-  </si>
-  <si>
-    <t>Order of Subject and Verb: VS</t>
-  </si>
-  <si>
-    <t>082A-2</t>
-  </si>
-  <si>
-    <t>Order of Subject and Verb: No dominant order</t>
-  </si>
-  <si>
-    <t>082A-3</t>
+    <t>082A</t>
   </si>
   <si>
     <t>Gender distinctions in personal pronouns</t>
   </si>
   <si>
+    <t>http://apics-online.info/parameters/13</t>
+  </si>
+  <si>
     <t>013</t>
   </si>
   <si>
     <t>Dual in independent personal pronouns</t>
   </si>
   <si>
+    <t>http://apics-online.info/parameters/14</t>
+  </si>
+  <si>
     <t>014</t>
   </si>
   <si>
@@ -2216,6 +1772,119 @@
   </si>
   <si>
     <t>GB057</t>
+  </si>
+  <si>
+    <t>What are the exemplar alignments of nouns?</t>
+  </si>
+  <si>
+    <t>https://atlas.evolvinglanguage.ch/parameters/Align-01</t>
+  </si>
+  <si>
+    <t>Align-01</t>
+  </si>
+  <si>
+    <t>Is there Differential Object Marking (DOM) for nouns?</t>
+  </si>
+  <si>
+    <t>https://atlas.evolvinglanguage.ch/parameters/Align-03</t>
+  </si>
+  <si>
+    <t>Align-03</t>
+  </si>
+  <si>
+    <t>What are all the alignments of pronouns?</t>
+  </si>
+  <si>
+    <t>https://atlas.evolvinglanguage.ch/parameters/Align-05</t>
+  </si>
+  <si>
+    <t>Align-05</t>
+  </si>
+  <si>
+    <t>Is there indexing in the language?</t>
+  </si>
+  <si>
+    <t>https://atlas.evolvinglanguage.ch/parameters/Align-06</t>
+  </si>
+  <si>
+    <t>Align-06</t>
+  </si>
+  <si>
+    <t>What are all the alignments of indexing?</t>
+  </si>
+  <si>
+    <t>https://atlas.evolvinglanguage.ch/parameters/Align-08</t>
+  </si>
+  <si>
+    <t>Align-08</t>
+  </si>
+  <si>
+    <t>Fusion of selected inflectional formatives</t>
+  </si>
+  <si>
+    <t>"Fusion refers to the degree to which grammatical markers (called formatives in the following) are phonologically connected to a host word or stem. There are three basic values: isolating, concatenative, and nonlinear. Isolating formatives are full-fledged phonological words of their own... Concatenative formatives are phonologically bound. They need some other host word for their pronunciation and form one single phonological word together with that host... Once the phonological alternations are properly analyzed, strings of concatenative formatives can be segmented into clear-cut morphemes. Nonlinear formatives are not amenable to this because they are realized not in linear sequence but by direct modification of their host. In our sample, we found two subtypes of nonlinear formatives: ablaut and tonal."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wals.info/feature/20A
+</t>
+  </si>
+  <si>
+    <t>20A</t>
+  </si>
+  <si>
+    <t>Exponence of selected inflectional formatives</t>
+  </si>
+  <si>
+    <t>"Exponence refers to the number of categories that cumulate into a single formative. The universal default is to express each category by a dedicated formative. These are monoexponential (or separative) formatives. Polyexponential (or cumulative) formatives, i.e. formatives which simultaneously code more than one category, are much rarer. A well-known example is number and case in many Indo-European languages. Marking of case in these languages involves the same formative as marking of number, and it is impossible to identify separate markers of case and number. Thus, in Russian, genitive singular is -i or -a and genitive plural -ej or -ov or -ø, and there is no element in these forms that exclusively expresses case or number. When categories are not cumulated into a single formative, each has its own separate marker. This is so in Turkish, where number is always expressed on nouns by means of the suffix -ler and for each case there is a separate suffix that can combine with -ler, e.g. genitive -in (plural -ler-in), accusative -i (plural -ler-i ), dative -e (plural -ler-e), etc.
+Exponence is a purely morphological notion; in particular it is independent of the phonological connection between host and formative. Therefore, monoexponential formatives can combine with any fusion type (see Chapter 20 for the definition of fusion types)."</t>
+  </si>
+  <si>
+    <t>https://wals.info/feature/21A</t>
+  </si>
+  <si>
+    <t>21A</t>
+  </si>
+  <si>
+    <t>Inflectional synthesis of the verb</t>
+  </si>
+  <si>
+    <t>"Grammatical categories like tense, voice, or agreement can be expressed either by individual words or by affixes attached to some other word (or the stem of a word). If a word combines with affixes, the resulting construction is said to be synthetic; if not, it is said to be analytic. For example, in the past tense, the English verb combines with an affix expressing tense (cf. _she painted_, with suffix _-ed_). Forms like painted  are called synthetic. In the future tense, by contrast, the verb does not combine with an affix; the future is instead expressed by a separate word (will, as in she will paint ). Expressions like _will paint_ are called analytic... Within the same language, verbs can be used with more or less synthesis: the English past, for example, is more synthetic than the future. For surveying purposes, we looked for the maximally inflected verb form, i.e. the one form that is most synthetic, and determined its category-per-word value ("cpw value"). In English, the maximally inflected verb form expresses two categories: agreement (in the present: _-s_) and tense (past: _-ed_). The English verb has therefore a synthesis degree of 2 cpw (=categories per word)."</t>
+  </si>
+  <si>
+    <t>https://wals.info/feature/22A</t>
+  </si>
+  <si>
+    <t>22A</t>
+  </si>
+  <si>
+    <t>Order of subject, object, and verb</t>
+  </si>
+  <si>
+    <t>http://apics-online.info/parameters/1</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Order of possessor and possessum</t>
+  </si>
+  <si>
+    <t>http://apics-online.info/parameters/2</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>Order of adjective and noun</t>
+  </si>
+  <si>
+    <t>"In this feature (based on WALS feature 87, by Matthew S. Dryer) we consider the two possible orders of attributive (or modifying) adjective and noun: adjective-noun, with the adjective preceding the noun, as in English stupid question, and noun-adjective, with the adjective following the noun, as in French _la maison rouge_ [the house red] 'the red house'. The feature is not concerned with predicative adjectives (in clauses where the noun is the subject and the adjective is the predicate), as in English _The man is stupid._ – The term adjective is used here in a semantic sense, as a word with a lexical meaning such as 'hot', 'old', or 'blue'. We thus disregard demonstratives, numerals, or words meaning 'other'. In languages like French, or English, adjectives belong to a distinct class of words, while in other languages they are a subclass of nouns or verbs. We treat a word as an adjective as long as it denotes a property or quality, irrespective of its word class in the language."</t>
+  </si>
+  <si>
+    <t>http://apics-online.info/parameters/3</t>
+  </si>
+  <si>
+    <t>003</t>
   </si>
 </sst>
 </file>
@@ -2385,13 +2054,13 @@
     </row>
     <row r="5">
       <c r="A5" s="6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s" s="7">
         <v>13</v>
       </c>
       <c r="D5" s="9">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E5" s="10">
         <v>1</v>
@@ -2402,5256 +2071,3939 @@
     </row>
     <row r="6">
       <c r="A6" s="6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s" s="7">
+        <v>13</v>
+      </c>
+      <c r="D6" s="9">
+        <v>12</v>
+      </c>
+      <c r="E6" s="10">
+        <v>3</v>
+      </c>
+      <c r="G6" t="s" s="12">
         <v>15</v>
-      </c>
-      <c r="D6" s="9">
-        <v>9</v>
-      </c>
-      <c r="E6" s="10">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s" s="12">
-        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s" s="7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="9">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E7" s="10">
         <v>1</v>
       </c>
       <c r="G7" t="s" s="12">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s" s="7">
+        <v>18</v>
+      </c>
+      <c r="D8" s="9">
+        <v>16</v>
+      </c>
+      <c r="E8" s="10">
+        <v>3</v>
+      </c>
+      <c r="G8" t="s" s="12">
         <v>19</v>
-      </c>
-      <c r="B8" t="s" s="7">
-        <v>19</v>
-      </c>
-      <c r="D8" s="9">
-        <v>11</v>
-      </c>
-      <c r="E8" s="10">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s" s="12">
-        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s" s="7">
         <v>20</v>
       </c>
-      <c r="B9" t="s" s="7">
+      <c r="C9" t="s" s="8">
         <v>21</v>
       </c>
       <c r="D9" s="9">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E9" s="10">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="F9" t="s" s="11">
+        <v>22</v>
       </c>
       <c r="G9" t="s" s="12">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s" s="7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="9">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E10" s="10">
-        <v>3</v>
-      </c>
-      <c r="G10" t="s" s="12">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s" s="7">
         <v>25</v>
       </c>
+      <c r="C11" t="s" s="8">
+        <v>26</v>
+      </c>
       <c r="D11" s="9">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E11" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" t="s" s="12">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s" s="7">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="C12" t="s" s="8">
+        <v>29</v>
       </c>
       <c r="D12" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E12" s="10">
         <v>1</v>
       </c>
+      <c r="F12" t="s" s="11">
+        <v>30</v>
+      </c>
       <c r="G12" t="s" s="12">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s" s="7">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="C13" t="s" s="8">
+        <v>33</v>
       </c>
       <c r="D13" s="9">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E13" s="10">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F13" t="s" s="11">
+        <v>34</v>
       </c>
       <c r="G13" t="s" s="12">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s" s="7">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="C14" t="s" s="8">
+        <v>37</v>
       </c>
       <c r="D14" s="9">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E14" s="10">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F14" t="s" s="11">
+        <v>38</v>
       </c>
       <c r="G14" t="s" s="12">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s" s="7">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s" s="8">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D15" s="9">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E15" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s" s="11">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G15" t="s" s="12">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s" s="7">
-        <v>37</v>
+        <v>44</v>
+      </c>
+      <c r="C16" t="s" s="8">
+        <v>45</v>
       </c>
       <c r="D16" s="9">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E16" s="10">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F16" t="s" s="11">
+        <v>46</v>
+      </c>
+      <c r="G16" t="s" s="12">
+        <v>47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s" s="7">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D17" s="9">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E17" s="10">
         <v>3</v>
       </c>
+      <c r="F17" t="s" s="11">
+        <v>49</v>
+      </c>
       <c r="G17" t="s" s="12">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s" s="7">
-        <v>40</v>
-      </c>
-      <c r="C18" t="s" s="8">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D18" s="9">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E18" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" t="s" s="11">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G18" t="s" s="12">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s" s="7">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D19" s="9">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E19" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" t="s" s="11">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G19" t="s" s="12">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s" s="7">
-        <v>47</v>
-      </c>
-      <c r="C20" t="s" s="8">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D20" s="9">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E20" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" t="s" s="11">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="G20" t="s" s="12">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s" s="7">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s" s="8">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D21" s="9">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="E21" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F21" t="s" s="11">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="G21" t="s" s="12">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6">
+        <v>51</v>
+      </c>
+      <c r="B22" t="s" s="7">
+        <v>64</v>
+      </c>
+      <c r="C22" t="s" s="8">
+        <v>65</v>
+      </c>
+      <c r="D22" s="9">
         <v>33</v>
       </c>
-      <c r="B22" t="s" s="7">
-        <v>54</v>
-      </c>
-      <c r="C22" t="s" s="8">
-        <v>55</v>
-      </c>
-      <c r="D22" s="9">
-        <v>3</v>
-      </c>
       <c r="E22" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" t="s" s="11">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="G22" t="s" s="12">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s" s="7">
-        <v>58</v>
-      </c>
-      <c r="C23" t="s" s="8">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D23" s="9">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E23" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F23" t="s" s="11">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="G23" t="s" s="12">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s" s="7">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C24" t="s" s="8">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D24" s="9">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E24" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" t="s" s="11">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G24" t="s" s="12">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s" s="7">
-        <v>66</v>
+        <v>75</v>
+      </c>
+      <c r="C25" t="s" s="8">
+        <v>76</v>
       </c>
       <c r="D25" s="9">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E25" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" t="s" s="11">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s" s="12">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s" s="7">
-        <v>69</v>
+        <v>79</v>
+      </c>
+      <c r="C26" t="s" s="8">
+        <v>80</v>
       </c>
       <c r="D26" s="9">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E26" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F26" t="s" s="11">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s" s="12">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B27" t="s" s="7">
-        <v>72</v>
+        <v>83</v>
+      </c>
+      <c r="C27" t="s" s="8">
+        <v>84</v>
       </c>
       <c r="D27" s="9">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="E27" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" t="s" s="11">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="G27" t="s" s="12">
-        <v>73</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B28" t="s" s="7">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D28" s="9">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E28" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" t="s" s="11">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s" s="12">
-        <v>75</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="B29" t="s" s="7">
-        <v>76</v>
+        <v>90</v>
+      </c>
+      <c r="C29" t="s" s="8">
+        <v>91</v>
       </c>
       <c r="D29" s="9">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E29" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F29" t="s" s="11">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="G29" t="s" s="12">
-        <v>78</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s" s="7">
-        <v>79</v>
+        <v>94</v>
+      </c>
+      <c r="C30" t="s" s="8">
+        <v>95</v>
       </c>
       <c r="D30" s="9">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E30" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s" s="11">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="G30" t="s" s="12">
-        <v>80</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s" s="7">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="D31" s="9">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="E31" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F31" t="s" s="11">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="G31" t="s" s="12">
-        <v>82</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s" s="7">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="D32" s="9">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E32" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F32" t="s" s="11">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="G32" t="s" s="12">
-        <v>84</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B33" t="s" s="7">
-        <v>85</v>
+        <v>103</v>
+      </c>
+      <c r="C33" t="s" s="8">
+        <v>104</v>
       </c>
       <c r="D33" s="9">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E33" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33" t="s" s="11">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="G33" t="s" s="12">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s" s="7">
-        <v>88</v>
+        <v>107</v>
+      </c>
+      <c r="C34" t="s" s="8">
+        <v>108</v>
       </c>
       <c r="D34" s="9">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E34" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F34" t="s" s="11">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="G34" t="s" s="12">
-        <v>89</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B35" t="s" s="7">
-        <v>90</v>
+        <v>111</v>
+      </c>
+      <c r="C35" t="s" s="8">
+        <v>112</v>
       </c>
       <c r="D35" s="9">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E35" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" t="s" s="11">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="G35" t="s" s="12">
-        <v>92</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s" s="7">
-        <v>93</v>
-      </c>
-      <c r="C36" t="s" s="8">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D36" s="9">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="E36" s="10">
-        <v>3</v>
-      </c>
-      <c r="F36" t="s" s="11">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="G36" t="s" s="12">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="B37" t="s" s="7">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="D37" s="9">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E37" s="10">
-        <v>3</v>
-      </c>
-      <c r="F37" t="s" s="11">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="G37" t="s" s="12">
-        <v>97</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s" s="7">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="C38" t="s" s="8">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="D38" s="9">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="E38" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F38" t="s" s="11">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="G38" t="s" s="12">
-        <v>101</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="B39" t="s" s="7">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="D39" s="9">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="E39" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39" t="s" s="11">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="G39" t="s" s="12">
-        <v>104</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="B40" t="s" s="7">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C40" t="s" s="8">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="D40" s="9">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="E40" s="10">
         <v>4</v>
       </c>
       <c r="F40" t="s" s="11">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="G40" t="s" s="12">
-        <v>108</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="B41" t="s" s="7">
-        <v>109</v>
-      </c>
-      <c r="C41" t="s" s="8">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="D41" s="9">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="E41" s="10">
         <v>4</v>
       </c>
       <c r="F41" t="s" s="11">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="G41" t="s" s="12">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="B42" t="s" s="7">
-        <v>113</v>
-      </c>
-      <c r="C42" t="s" s="8">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D42" s="9">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="E42" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F42" t="s" s="11">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="G42" t="s" s="12">
-        <v>116</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="B43" t="s" s="7">
-        <v>117</v>
-      </c>
-      <c r="C43" t="s" s="8">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="D43" s="9">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="E43" s="10">
         <v>4</v>
       </c>
       <c r="F43" t="s" s="11">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="G43" t="s" s="12">
-        <v>120</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="B44" t="s" s="7">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="D44" s="9">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="E44" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F44" t="s" s="11">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="G44" t="s" s="12">
-        <v>123</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="B45" t="s" s="7">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="D45" s="9">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="E45" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F45" t="s" s="11">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="G45" t="s" s="12">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="B46" t="s" s="7">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="D46" s="9">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="E46" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F46" t="s" s="11">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="G46" t="s" s="12">
-        <v>127</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="B47" t="s" s="7">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="D47" s="9">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="E47" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F47" t="s" s="11">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="G47" t="s" s="12">
-        <v>129</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="B48" t="s" s="7">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="D48" s="9">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="E48" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F48" t="s" s="11">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="G48" t="s" s="12">
-        <v>131</v>
+        <v>153</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="B49" t="s" s="7">
-        <v>132</v>
-      </c>
-      <c r="C49" t="s" s="8">
-        <v>133</v>
-      </c>
-      <c r="D49" s="9">
-        <v>45</v>
+        <v>154</v>
       </c>
       <c r="E49" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F49" t="s" s="11">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="G49" t="s" s="12">
-        <v>135</v>
+        <v>156</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="B50" t="s" s="7">
-        <v>136</v>
-      </c>
-      <c r="C50" t="s" s="8">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="D50" s="9">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="E50" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F50" t="s" s="11">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="G50" t="s" s="12">
-        <v>139</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="B51" t="s" s="7">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="D51" s="9">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="E51" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F51" t="s" s="11">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="G51" t="s" s="12">
-        <v>142</v>
+        <v>162</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="B52" t="s" s="7">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D52" s="9">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="E52" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F52" t="s" s="11">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="G52" t="s" s="12">
-        <v>142</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="B53" t="s" s="7">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="C53" t="s" s="8">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="D53" s="9">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="E53" s="10">
         <v>2</v>
       </c>
       <c r="F53" t="s" s="11">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="G53" t="s" s="12">
-        <v>148</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="B54" t="s" s="7">
-        <v>149</v>
-      </c>
-      <c r="C54" t="s" s="8">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="D54" s="9">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="E54" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F54" t="s" s="11">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="G54" t="s" s="12">
-        <v>152</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6">
-        <v>68</v>
+        <v>125</v>
       </c>
       <c r="B55" t="s" s="7">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D55" s="9">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="E55" s="10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F55" t="s" s="11">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="G55" t="s" s="12">
-        <v>155</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="B56" t="s" s="7">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="D56" s="9">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="E56" s="10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F56" t="s" s="11">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="G56" t="s" s="12">
-        <v>158</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="B57" t="s" s="7">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="D57" s="9">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="E57" s="10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F57" t="s" s="11">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G57" t="s" s="12">
-        <v>155</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="B58" t="s" s="7">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="D58" s="9">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="E58" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F58" t="s" s="11">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="G58" t="s" s="12">
-        <v>163</v>
+        <v>178</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="B59" t="s" s="7">
-        <v>164</v>
-      </c>
-      <c r="C59" t="s" s="8">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D59" s="9">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="E59" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" t="s" s="11">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G59" t="s" s="12">
-        <v>167</v>
+        <v>180</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="B60" t="s" s="7">
-        <v>168</v>
-      </c>
-      <c r="C60" t="s" s="8">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="D60" s="9">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="E60" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" t="s" s="11">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G60" t="s" s="12">
-        <v>169</v>
+        <v>182</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="B61" t="s" s="7">
-        <v>170</v>
-      </c>
-      <c r="C61" t="s" s="8">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="D61" s="9">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="E61" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" t="s" s="11">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="G61" t="s" s="12">
-        <v>171</v>
+        <v>185</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="B62" t="s" s="7">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D62" s="9">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="E62" s="10">
         <v>1</v>
       </c>
+      <c r="F62" t="s" s="11">
+        <v>187</v>
+      </c>
       <c r="G62" t="s" s="12">
-        <v>173</v>
+        <v>188</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="B63" t="s" s="7">
-        <v>174</v>
+        <v>189</v>
+      </c>
+      <c r="C63" t="s" s="8">
+        <v>190</v>
       </c>
       <c r="D63" s="9">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="E63" s="10">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F63" t="s" s="11">
+        <v>191</v>
       </c>
       <c r="G63" t="s" s="12">
-        <v>175</v>
+        <v>192</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="B64" t="s" s="7">
-        <v>176</v>
+        <v>193</v>
+      </c>
+      <c r="C64" t="s" s="8">
+        <v>194</v>
       </c>
       <c r="D64" s="9">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="E64" s="10">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F64" t="s" s="11">
+        <v>195</v>
       </c>
       <c r="G64" t="s" s="12">
-        <v>177</v>
+        <v>196</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="B65" t="s" s="7">
-        <v>178</v>
+        <v>197</v>
+      </c>
+      <c r="C65" t="s" s="8">
+        <v>198</v>
       </c>
       <c r="D65" s="9">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="E65" s="10">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F65" t="s" s="11">
+        <v>199</v>
       </c>
       <c r="G65" t="s" s="12">
-        <v>179</v>
+        <v>200</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="B66" t="s" s="7">
-        <v>180</v>
+        <v>201</v>
+      </c>
+      <c r="C66" t="s" s="8">
+        <v>202</v>
       </c>
       <c r="D66" s="9">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="E66" s="10">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F66" t="s" s="11">
+        <v>203</v>
       </c>
       <c r="G66" t="s" s="12">
-        <v>181</v>
+        <v>204</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="B67" t="s" s="7">
-        <v>182</v>
+        <v>205</v>
+      </c>
+      <c r="C67" t="s" s="8">
+        <v>206</v>
       </c>
       <c r="D67" s="9">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="E67" s="10">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F67" t="s" s="11">
+        <v>203</v>
       </c>
       <c r="G67" t="s" s="12">
-        <v>183</v>
+        <v>207</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6">
-        <v>83</v>
+        <v>153</v>
       </c>
       <c r="B68" t="s" s="7">
-        <v>184</v>
+        <v>208</v>
+      </c>
+      <c r="C68" t="s" s="8">
+        <v>209</v>
       </c>
       <c r="D68" s="9">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="E68" s="10">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F68" t="s" s="11">
+        <v>210</v>
       </c>
       <c r="G68" t="s" s="12">
-        <v>185</v>
+        <v>211</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="B69" t="s" s="7">
-        <v>186</v>
+        <v>212</v>
+      </c>
+      <c r="C69" t="s" s="8">
+        <v>213</v>
       </c>
       <c r="D69" s="9">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="E69" s="10">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F69" t="s" s="11">
+        <v>214</v>
       </c>
       <c r="G69" t="s" s="12">
-        <v>187</v>
+        <v>215</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="B70" t="s" s="7">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="C70" t="s" s="8">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="D70" s="9">
-        <v>68</v>
+        <v>259</v>
       </c>
       <c r="E70" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F70" t="s" s="11">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="G70" t="s" s="12">
-        <v>191</v>
+        <v>219</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="B71" t="s" s="7">
-        <v>192</v>
-      </c>
-      <c r="C71" t="s" s="8">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="D71" s="9">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="E71" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F71" t="s" s="11">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="G71" t="s" s="12">
-        <v>193</v>
+        <v>222</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6">
-        <v>87</v>
+        <v>164</v>
       </c>
       <c r="B72" t="s" s="7">
-        <v>194</v>
-      </c>
-      <c r="C72" t="s" s="8">
-        <v>189</v>
+        <v>223</v>
       </c>
       <c r="D72" s="9">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="E72" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F72" t="s" s="11">
-        <v>190</v>
+        <v>224</v>
       </c>
       <c r="G72" t="s" s="12">
-        <v>195</v>
+        <v>225</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6">
-        <v>88</v>
+        <v>166</v>
       </c>
       <c r="B73" t="s" s="7">
-        <v>196</v>
-      </c>
-      <c r="C73" t="s" s="8">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="D73" s="9">
-        <v>71</v>
+        <v>137</v>
       </c>
       <c r="E73" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F73" t="s" s="11">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="G73" t="s" s="12">
-        <v>197</v>
+        <v>228</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="B74" t="s" s="7">
-        <v>198</v>
-      </c>
-      <c r="C74" t="s" s="8">
-        <v>189</v>
+        <v>229</v>
       </c>
       <c r="D74" s="9">
-        <v>72</v>
+        <v>139</v>
       </c>
       <c r="E74" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F74" t="s" s="11">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="G74" t="s" s="12">
-        <v>199</v>
+        <v>231</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="B75" t="s" s="7">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D75" s="9">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="E75" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F75" t="s" s="11">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G75" t="s" s="12">
-        <v>202</v>
+        <v>234</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6">
-        <v>91</v>
+        <v>171</v>
       </c>
       <c r="B76" t="s" s="7">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="D76" s="9">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="E76" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F76" t="s" s="11">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="G76" t="s" s="12">
-        <v>204</v>
+        <v>237</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6">
-        <v>92</v>
+        <v>173</v>
       </c>
       <c r="B77" t="s" s="7">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="D77" s="9">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="E77" s="10">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F77" t="s" s="11">
+        <v>239</v>
       </c>
       <c r="G77" t="s" s="12">
-        <v>206</v>
+        <v>240</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6">
-        <v>93</v>
+        <v>175</v>
       </c>
       <c r="B78" t="s" s="7">
-        <v>207</v>
+        <v>241</v>
       </c>
       <c r="D78" s="9">
-        <v>76</v>
+        <v>147</v>
       </c>
       <c r="E78" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F78" t="s" s="11">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="G78" t="s" s="12">
-        <v>208</v>
+        <v>243</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6">
-        <v>94</v>
+        <v>177</v>
       </c>
       <c r="B79" t="s" s="7">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="D79" s="9">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="E79" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F79" t="s" s="11">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="G79" t="s" s="12">
-        <v>210</v>
+        <v>246</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="B80" t="s" s="7">
-        <v>211</v>
-      </c>
-      <c r="C80" t="s" s="8">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="D80" s="9">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="E80" s="10">
         <v>4</v>
       </c>
       <c r="F80" t="s" s="11">
-        <v>213</v>
+        <v>248</v>
       </c>
       <c r="G80" t="s" s="12">
-        <v>214</v>
+        <v>249</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="B81" t="s" s="7">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="D81" s="9">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="E81" s="10">
         <v>4</v>
       </c>
       <c r="F81" t="s" s="11">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="G81" t="s" s="12">
-        <v>217</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="B82" t="s" s="7">
-        <v>218</v>
+        <v>253</v>
       </c>
       <c r="D82" s="9">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="E82" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="s" s="11">
-        <v>219</v>
+        <v>254</v>
       </c>
       <c r="G82" t="s" s="12">
-        <v>220</v>
+        <v>255</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6">
-        <v>101</v>
+        <v>185</v>
       </c>
       <c r="B83" t="s" s="7">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="D83" s="9">
-        <v>225</v>
+        <v>157</v>
       </c>
       <c r="E83" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F83" t="s" s="11">
-        <v>219</v>
+        <v>257</v>
       </c>
       <c r="G83" t="s" s="12">
-        <v>222</v>
+        <v>258</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6">
-        <v>102</v>
+        <v>188</v>
       </c>
       <c r="B84" t="s" s="7">
-        <v>223</v>
+        <v>259</v>
+      </c>
+      <c r="D84" s="9">
+        <v>160</v>
       </c>
       <c r="E84" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F84" t="s" s="11">
-        <v>219</v>
+        <v>260</v>
       </c>
       <c r="G84" t="s" s="12">
-        <v>224</v>
+        <v>261</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="B85" t="s" s="7">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="D85" s="9">
-        <v>84</v>
+        <v>162</v>
       </c>
       <c r="E85" s="10">
         <v>4</v>
       </c>
       <c r="F85" t="s" s="11">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="G85" t="s" s="12">
-        <v>227</v>
+        <v>264</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="B86" t="s" s="7">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="D86" s="9">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="E86" s="10">
         <v>4</v>
       </c>
       <c r="F86" t="s" s="11">
-        <v>229</v>
+        <v>266</v>
       </c>
       <c r="G86" t="s" s="12">
-        <v>230</v>
+        <v>267</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="B87" t="s" s="7">
-        <v>231</v>
+        <v>268</v>
       </c>
       <c r="D87" s="9">
-        <v>88</v>
+        <v>167</v>
       </c>
       <c r="E87" s="10">
         <v>4</v>
       </c>
       <c r="F87" t="s" s="11">
-        <v>232</v>
+        <v>269</v>
       </c>
       <c r="G87" t="s" s="12">
-        <v>233</v>
+        <v>270</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6">
-        <v>111</v>
+        <v>198</v>
       </c>
       <c r="B88" t="s" s="7">
-        <v>234</v>
+        <v>271</v>
       </c>
       <c r="D88" s="9">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="E88" s="10">
         <v>4</v>
       </c>
       <c r="F88" t="s" s="11">
-        <v>235</v>
+        <v>272</v>
       </c>
       <c r="G88" t="s" s="12">
-        <v>236</v>
+        <v>273</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6">
-        <v>113</v>
+        <v>200</v>
       </c>
       <c r="B89" t="s" s="7">
-        <v>237</v>
+        <v>274</v>
       </c>
       <c r="D89" s="9">
-        <v>92</v>
+        <v>171</v>
       </c>
       <c r="E89" s="10">
         <v>4</v>
       </c>
       <c r="F89" t="s" s="11">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="G89" t="s" s="12">
-        <v>239</v>
+        <v>276</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="B90" t="s" s="7">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="D90" s="9">
-        <v>94</v>
+        <v>173</v>
       </c>
       <c r="E90" s="10">
         <v>4</v>
       </c>
       <c r="F90" t="s" s="11">
-        <v>241</v>
+        <v>278</v>
       </c>
       <c r="G90" t="s" s="12">
-        <v>242</v>
+        <v>279</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6">
-        <v>117</v>
+        <v>204</v>
       </c>
       <c r="B91" t="s" s="7">
-        <v>243</v>
+        <v>280</v>
+      </c>
+      <c r="D91" s="9">
+        <v>175</v>
       </c>
       <c r="E91" s="10">
         <v>4</v>
       </c>
       <c r="F91" t="s" s="11">
-        <v>244</v>
+        <v>281</v>
       </c>
       <c r="G91" t="s" s="12">
-        <v>245</v>
+        <v>282</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="B92" t="s" s="7">
-        <v>246</v>
+        <v>283</v>
       </c>
       <c r="D92" s="9">
-        <v>98</v>
+        <v>177</v>
       </c>
       <c r="E92" s="10">
         <v>4</v>
       </c>
       <c r="F92" t="s" s="11">
-        <v>247</v>
+        <v>284</v>
       </c>
       <c r="G92" t="s" s="12">
-        <v>248</v>
+        <v>285</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6">
-        <v>121</v>
+        <v>208</v>
       </c>
       <c r="B93" t="s" s="7">
-        <v>249</v>
+        <v>286</v>
       </c>
       <c r="D93" s="9">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="E93" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F93" t="s" s="11">
-        <v>250</v>
+        <v>287</v>
       </c>
       <c r="G93" t="s" s="12">
-        <v>251</v>
+        <v>288</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6">
-        <v>122</v>
+        <v>209</v>
       </c>
       <c r="B94" t="s" s="7">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="D94" s="9">
-        <v>101</v>
+        <v>181</v>
       </c>
       <c r="E94" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F94" t="s" s="11">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="G94" t="s" s="12">
-        <v>253</v>
+        <v>291</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6">
-        <v>123</v>
+        <v>212</v>
       </c>
       <c r="B95" t="s" s="7">
-        <v>254</v>
-      </c>
-      <c r="C95" t="s" s="8">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="D95" s="9">
-        <v>102</v>
+        <v>183</v>
       </c>
       <c r="E95" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F95" t="s" s="11">
-        <v>250</v>
+        <v>293</v>
       </c>
       <c r="G95" t="s" s="12">
-        <v>256</v>
+        <v>294</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6">
-        <v>124</v>
+        <v>213</v>
       </c>
       <c r="B96" t="s" s="7">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="D96" s="9">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="E96" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F96" t="s" s="11">
-        <v>258</v>
+        <v>296</v>
       </c>
       <c r="G96" t="s" s="12">
-        <v>259</v>
+        <v>297</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6">
-        <v>125</v>
+        <v>216</v>
       </c>
       <c r="B97" t="s" s="7">
-        <v>260</v>
+        <v>298</v>
       </c>
       <c r="D97" s="9">
-        <v>103</v>
+        <v>187</v>
       </c>
       <c r="E97" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F97" t="s" s="11">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="G97" t="s" s="12">
-        <v>261</v>
+        <v>300</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6">
-        <v>126</v>
+        <v>217</v>
       </c>
       <c r="B98" t="s" s="7">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="D98" s="9">
-        <v>106</v>
+        <v>189</v>
       </c>
       <c r="E98" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F98" t="s" s="11">
-        <v>258</v>
+        <v>302</v>
       </c>
       <c r="G98" t="s" s="12">
-        <v>263</v>
+        <v>303</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6">
-        <v>127</v>
+        <v>220</v>
       </c>
       <c r="B99" t="s" s="7">
-        <v>264</v>
+        <v>304</v>
       </c>
       <c r="D99" s="9">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="E99" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F99" t="s" s="11">
-        <v>258</v>
+        <v>305</v>
       </c>
       <c r="G99" t="s" s="12">
-        <v>265</v>
+        <v>306</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6">
-        <v>128</v>
+        <v>221</v>
       </c>
       <c r="B100" t="s" s="7">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="D100" s="9">
-        <v>108</v>
+        <v>193</v>
       </c>
       <c r="E100" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F100" t="s" s="11">
-        <v>258</v>
+        <v>308</v>
       </c>
       <c r="G100" t="s" s="12">
-        <v>267</v>
+        <v>309</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6">
-        <v>129</v>
+        <v>224</v>
       </c>
       <c r="B101" t="s" s="7">
-        <v>268</v>
+        <v>310</v>
       </c>
       <c r="D101" s="9">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E101" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F101" t="s" s="11">
-        <v>258</v>
+        <v>311</v>
       </c>
       <c r="G101" t="s" s="12">
-        <v>269</v>
+        <v>312</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6">
-        <v>130</v>
+        <v>225</v>
       </c>
       <c r="B102" t="s" s="7">
-        <v>270</v>
+        <v>313</v>
       </c>
       <c r="D102" s="9">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="E102" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F102" t="s" s="11">
-        <v>258</v>
+        <v>314</v>
       </c>
       <c r="G102" t="s" s="12">
-        <v>271</v>
+        <v>315</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6">
-        <v>131</v>
+        <v>227</v>
       </c>
       <c r="B103" t="s" s="7">
-        <v>272</v>
+        <v>316</v>
       </c>
       <c r="D103" s="9">
-        <v>104</v>
+        <v>199</v>
       </c>
       <c r="E103" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F103" t="s" s="11">
-        <v>273</v>
+        <v>317</v>
       </c>
       <c r="G103" t="s" s="12">
-        <v>274</v>
+        <v>318</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6">
-        <v>132</v>
+        <v>233</v>
       </c>
       <c r="B104" t="s" s="7">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="D104" s="9">
-        <v>103</v>
+        <v>200</v>
       </c>
       <c r="E104" s="10">
         <v>3</v>
       </c>
       <c r="F104" t="s" s="11">
-        <v>273</v>
+        <v>320</v>
       </c>
       <c r="G104" t="s" s="12">
-        <v>276</v>
+        <v>321</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6">
-        <v>133</v>
+        <v>241</v>
       </c>
       <c r="B105" t="s" s="7">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="D105" s="9">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E105" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F105" t="s" s="11">
-        <v>273</v>
+        <v>323</v>
       </c>
       <c r="G105" t="s" s="12">
-        <v>278</v>
+        <v>324</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6">
-        <v>134</v>
+        <v>245</v>
       </c>
       <c r="B106" t="s" s="7">
-        <v>279</v>
+        <v>325</v>
       </c>
       <c r="D106" s="9">
-        <v>106</v>
+        <v>211</v>
       </c>
       <c r="E106" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F106" t="s" s="11">
-        <v>273</v>
+        <v>326</v>
       </c>
       <c r="G106" t="s" s="12">
-        <v>280</v>
+        <v>327</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6">
-        <v>135</v>
+        <v>250</v>
       </c>
       <c r="B107" t="s" s="7">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="D107" s="9">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="E107" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F107" t="s" s="11">
-        <v>273</v>
+        <v>329</v>
       </c>
       <c r="G107" t="s" s="12">
-        <v>282</v>
+        <v>330</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6">
-        <v>136</v>
+        <v>254</v>
       </c>
       <c r="B108" t="s" s="7">
-        <v>283</v>
+        <v>331</v>
+      </c>
+      <c r="C108" t="s" s="8">
+        <v>332</v>
       </c>
       <c r="D108" s="9">
-        <v>109</v>
+        <v>222</v>
       </c>
       <c r="E108" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F108" t="s" s="11">
-        <v>273</v>
+        <v>333</v>
       </c>
       <c r="G108" t="s" s="12">
-        <v>284</v>
+        <v>334</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6">
-        <v>137</v>
+        <v>258</v>
       </c>
       <c r="B109" t="s" s="7">
-        <v>285</v>
+        <v>335</v>
       </c>
       <c r="D109" s="9">
-        <v>110</v>
+        <v>223</v>
       </c>
       <c r="E109" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F109" t="s" s="11">
-        <v>273</v>
+        <v>336</v>
       </c>
       <c r="G109" t="s" s="12">
-        <v>286</v>
+        <v>337</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6">
-        <v>138</v>
+        <v>260</v>
       </c>
       <c r="B110" t="s" s="7">
-        <v>287</v>
+        <v>338</v>
       </c>
       <c r="D110" s="9">
-        <v>111</v>
+        <v>226</v>
       </c>
       <c r="E110" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F110" t="s" s="11">
-        <v>288</v>
+        <v>339</v>
       </c>
       <c r="G110" t="s" s="12">
-        <v>289</v>
+        <v>340</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6">
-        <v>139</v>
+        <v>262</v>
       </c>
       <c r="B111" t="s" s="7">
-        <v>290</v>
+        <v>341</v>
       </c>
       <c r="D111" s="9">
-        <v>114</v>
+        <v>228</v>
       </c>
       <c r="E111" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F111" t="s" s="11">
-        <v>288</v>
+        <v>342</v>
       </c>
       <c r="G111" t="s" s="12">
-        <v>291</v>
+        <v>343</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6">
-        <v>140</v>
+        <v>264</v>
       </c>
       <c r="B112" t="s" s="7">
-        <v>292</v>
+        <v>344</v>
       </c>
       <c r="D112" s="9">
-        <v>113</v>
+        <v>230</v>
       </c>
       <c r="E112" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F112" t="s" s="11">
-        <v>288</v>
+        <v>345</v>
       </c>
       <c r="G112" t="s" s="12">
-        <v>293</v>
+        <v>346</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6">
-        <v>141</v>
+        <v>266</v>
       </c>
       <c r="B113" t="s" s="7">
-        <v>294</v>
+        <v>347</v>
       </c>
       <c r="D113" s="9">
-        <v>112</v>
+        <v>232</v>
       </c>
       <c r="E113" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F113" t="s" s="11">
-        <v>288</v>
+        <v>348</v>
       </c>
       <c r="G113" t="s" s="12">
-        <v>295</v>
+        <v>349</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6">
-        <v>142</v>
+        <v>268</v>
       </c>
       <c r="B114" t="s" s="7">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="D114" s="9">
-        <v>115</v>
+        <v>234</v>
       </c>
       <c r="E114" s="10">
         <v>4</v>
       </c>
       <c r="F114" t="s" s="11">
-        <v>297</v>
+        <v>351</v>
       </c>
       <c r="G114" t="s" s="12">
-        <v>298</v>
+        <v>352</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6">
-        <v>145</v>
+        <v>270</v>
       </c>
       <c r="B115" t="s" s="7">
-        <v>299</v>
+        <v>353</v>
       </c>
       <c r="D115" s="9">
-        <v>118</v>
+        <v>236</v>
       </c>
       <c r="E115" s="10">
         <v>4</v>
       </c>
       <c r="F115" t="s" s="11">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="G115" t="s" s="12">
-        <v>301</v>
+        <v>355</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6">
-        <v>147</v>
+        <v>272</v>
       </c>
       <c r="B116" t="s" s="7">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="D116" s="9">
-        <v>121</v>
+        <v>238</v>
       </c>
       <c r="E116" s="10">
         <v>4</v>
       </c>
       <c r="F116" t="s" s="11">
-        <v>303</v>
+        <v>357</v>
       </c>
       <c r="G116" t="s" s="12">
-        <v>304</v>
+        <v>358</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6">
-        <v>149</v>
+        <v>274</v>
       </c>
       <c r="B117" t="s" s="7">
-        <v>305</v>
+        <v>359</v>
       </c>
       <c r="D117" s="9">
-        <v>122</v>
+        <v>240</v>
       </c>
       <c r="E117" s="10">
         <v>4</v>
       </c>
       <c r="F117" t="s" s="11">
-        <v>306</v>
+        <v>360</v>
       </c>
       <c r="G117" t="s" s="12">
-        <v>307</v>
+        <v>361</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="6">
-        <v>151</v>
+        <v>276</v>
       </c>
       <c r="B118" t="s" s="7">
-        <v>308</v>
+        <v>362</v>
       </c>
       <c r="D118" s="9">
-        <v>122</v>
+        <v>242</v>
       </c>
       <c r="E118" s="10">
         <v>4</v>
       </c>
       <c r="F118" t="s" s="11">
-        <v>306</v>
+        <v>363</v>
       </c>
       <c r="G118" t="s" s="12">
-        <v>309</v>
+        <v>364</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6">
-        <v>153</v>
+        <v>279</v>
       </c>
       <c r="B119" t="s" s="7">
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="D119" s="9">
-        <v>126</v>
+        <v>244</v>
       </c>
       <c r="E119" s="10">
         <v>4</v>
       </c>
       <c r="F119" t="s" s="11">
-        <v>311</v>
+        <v>366</v>
       </c>
       <c r="G119" t="s" s="12">
-        <v>312</v>
+        <v>367</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6">
-        <v>155</v>
+        <v>280</v>
       </c>
       <c r="B120" t="s" s="7">
-        <v>313</v>
+        <v>368</v>
       </c>
       <c r="D120" s="9">
-        <v>128</v>
+        <v>247</v>
       </c>
       <c r="E120" s="10">
         <v>4</v>
       </c>
       <c r="F120" t="s" s="11">
-        <v>314</v>
+        <v>369</v>
       </c>
       <c r="G120" t="s" s="12">
-        <v>315</v>
+        <v>370</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6">
-        <v>157</v>
+        <v>283</v>
       </c>
       <c r="B121" t="s" s="7">
-        <v>316</v>
+        <v>371</v>
       </c>
       <c r="D121" s="9">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E121" s="10">
         <v>4</v>
       </c>
       <c r="F121" t="s" s="11">
-        <v>317</v>
+        <v>372</v>
       </c>
       <c r="G121" t="s" s="12">
-        <v>318</v>
+        <v>373</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="6">
-        <v>161</v>
+        <v>284</v>
       </c>
       <c r="B122" t="s" s="7">
-        <v>319</v>
+        <v>374</v>
       </c>
       <c r="D122" s="9">
-        <v>133</v>
+        <v>250</v>
       </c>
       <c r="E122" s="10">
         <v>4</v>
       </c>
       <c r="F122" t="s" s="11">
-        <v>320</v>
+        <v>375</v>
       </c>
       <c r="G122" t="s" s="12">
-        <v>321</v>
+        <v>376</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6">
-        <v>164</v>
+        <v>286</v>
       </c>
       <c r="B123" t="s" s="7">
-        <v>322</v>
+        <v>377</v>
       </c>
       <c r="D123" s="9">
-        <v>135</v>
+        <v>252</v>
       </c>
       <c r="E123" s="10">
         <v>4</v>
       </c>
       <c r="F123" t="s" s="11">
-        <v>323</v>
+        <v>378</v>
       </c>
       <c r="G123" t="s" s="12">
-        <v>324</v>
+        <v>379</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="6">
-        <v>166</v>
+        <v>289</v>
       </c>
       <c r="B124" t="s" s="7">
-        <v>325</v>
+        <v>380</v>
       </c>
       <c r="D124" s="9">
-        <v>137</v>
+        <v>254</v>
       </c>
       <c r="E124" s="10">
         <v>4</v>
       </c>
       <c r="F124" t="s" s="11">
-        <v>326</v>
+        <v>381</v>
       </c>
       <c r="G124" t="s" s="12">
-        <v>327</v>
+        <v>382</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6">
-        <v>167</v>
+        <v>291</v>
       </c>
       <c r="B125" t="s" s="7">
-        <v>328</v>
+        <v>383</v>
       </c>
       <c r="D125" s="9">
-        <v>139</v>
+        <v>256</v>
       </c>
       <c r="E125" s="10">
         <v>4</v>
       </c>
       <c r="F125" t="s" s="11">
-        <v>329</v>
+        <v>384</v>
       </c>
       <c r="G125" t="s" s="12">
-        <v>330</v>
+        <v>385</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="6">
-        <v>169</v>
+        <v>293</v>
       </c>
       <c r="B126" t="s" s="7">
-        <v>331</v>
+        <v>386</v>
+      </c>
+      <c r="C126" t="s" s="8">
+        <v>387</v>
       </c>
       <c r="D126" s="9">
-        <v>141</v>
+        <v>258</v>
       </c>
       <c r="E126" s="10">
         <v>4</v>
       </c>
       <c r="F126" t="s" s="11">
-        <v>332</v>
+        <v>388</v>
       </c>
       <c r="G126" t="s" s="12">
-        <v>333</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6">
-        <v>171</v>
+        <v>294</v>
       </c>
       <c r="B127" t="s" s="7">
-        <v>334</v>
+        <v>390</v>
+      </c>
+      <c r="C127" t="s" s="8">
+        <v>391</v>
       </c>
       <c r="D127" s="9">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="E127" s="10">
         <v>4</v>
       </c>
       <c r="F127" t="s" s="11">
-        <v>335</v>
+        <v>392</v>
       </c>
       <c r="G127" t="s" s="12">
-        <v>336</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="6">
-        <v>173</v>
+        <v>296</v>
       </c>
       <c r="B128" t="s" s="7">
-        <v>337</v>
+        <v>394</v>
+      </c>
+      <c r="C128" t="s" s="8">
+        <v>395</v>
       </c>
       <c r="D128" s="9">
-        <v>145</v>
+        <v>261</v>
       </c>
       <c r="E128" s="10">
         <v>4</v>
       </c>
       <c r="F128" t="s" s="11">
-        <v>338</v>
+        <v>396</v>
       </c>
       <c r="G128" t="s" s="12">
-        <v>339</v>
+        <v>397</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6">
-        <v>175</v>
+        <v>299</v>
       </c>
       <c r="B129" t="s" s="7">
-        <v>340</v>
+        <v>398</v>
+      </c>
+      <c r="C129" t="s" s="8">
+        <v>399</v>
       </c>
       <c r="D129" s="9">
-        <v>147</v>
+        <v>264</v>
       </c>
       <c r="E129" s="10">
         <v>4</v>
       </c>
       <c r="F129" t="s" s="11">
-        <v>341</v>
+        <v>400</v>
       </c>
       <c r="G129" t="s" s="12">
-        <v>342</v>
+        <v>401</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="6">
-        <v>177</v>
+        <v>301</v>
       </c>
       <c r="B130" t="s" s="7">
-        <v>343</v>
+        <v>402</v>
+      </c>
+      <c r="C130" t="s" s="8">
+        <v>403</v>
       </c>
       <c r="D130" s="9">
-        <v>149</v>
+        <v>265</v>
       </c>
       <c r="E130" s="10">
         <v>4</v>
       </c>
       <c r="F130" t="s" s="11">
-        <v>344</v>
+        <v>404</v>
       </c>
       <c r="G130" t="s" s="12">
-        <v>345</v>
+        <v>405</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="6">
-        <v>179</v>
+        <v>307</v>
       </c>
       <c r="B131" t="s" s="7">
-        <v>346</v>
+        <v>406</v>
       </c>
       <c r="D131" s="9">
-        <v>151</v>
+        <v>269</v>
       </c>
       <c r="E131" s="10">
         <v>4</v>
       </c>
       <c r="F131" t="s" s="11">
-        <v>347</v>
+        <v>407</v>
       </c>
       <c r="G131" t="s" s="12">
-        <v>348</v>
+        <v>408</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="6">
-        <v>182</v>
+        <v>308</v>
       </c>
       <c r="B132" t="s" s="7">
-        <v>349</v>
+        <v>409</v>
       </c>
       <c r="D132" s="9">
-        <v>153</v>
+        <v>272</v>
       </c>
       <c r="E132" s="10">
         <v>4</v>
       </c>
       <c r="F132" t="s" s="11">
-        <v>350</v>
+        <v>410</v>
       </c>
       <c r="G132" t="s" s="12">
-        <v>351</v>
+        <v>411</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6">
-        <v>183</v>
+        <v>310</v>
       </c>
       <c r="B133" t="s" s="7">
-        <v>352</v>
+        <v>412</v>
       </c>
       <c r="D133" s="9">
-        <v>156</v>
+        <v>273</v>
       </c>
       <c r="E133" s="10">
         <v>4</v>
       </c>
       <c r="F133" t="s" s="11">
-        <v>353</v>
+        <v>413</v>
       </c>
       <c r="G133" t="s" s="12">
-        <v>354</v>
+        <v>414</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="6">
-        <v>185</v>
+        <v>313</v>
       </c>
       <c r="B134" t="s" s="7">
-        <v>355</v>
+        <v>415</v>
       </c>
       <c r="D134" s="9">
-        <v>157</v>
+        <v>276</v>
       </c>
       <c r="E134" s="10">
         <v>4</v>
       </c>
       <c r="F134" t="s" s="11">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="G134" t="s" s="12">
-        <v>357</v>
+        <v>417</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6">
-        <v>188</v>
+        <v>316</v>
       </c>
       <c r="B135" t="s" s="7">
-        <v>358</v>
+        <v>418</v>
       </c>
       <c r="D135" s="9">
-        <v>160</v>
+        <v>280</v>
       </c>
       <c r="E135" s="10">
         <v>4</v>
       </c>
       <c r="F135" t="s" s="11">
-        <v>359</v>
+        <v>419</v>
       </c>
       <c r="G135" t="s" s="12">
-        <v>360</v>
+        <v>420</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="6">
-        <v>191</v>
+        <v>318</v>
       </c>
       <c r="B136" t="s" s="7">
-        <v>361</v>
+        <v>421</v>
       </c>
       <c r="D136" s="9">
-        <v>162</v>
+        <v>281</v>
       </c>
       <c r="E136" s="10">
         <v>4</v>
       </c>
       <c r="F136" t="s" s="11">
-        <v>362</v>
+        <v>422</v>
       </c>
       <c r="G136" t="s" s="12">
-        <v>363</v>
+        <v>423</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6">
-        <v>192</v>
+        <v>320</v>
       </c>
       <c r="B137" t="s" s="7">
-        <v>364</v>
+        <v>424</v>
       </c>
       <c r="D137" s="9">
-        <v>165</v>
+        <v>283</v>
       </c>
       <c r="E137" s="10">
         <v>4</v>
       </c>
       <c r="F137" t="s" s="11">
-        <v>365</v>
+        <v>425</v>
       </c>
       <c r="G137" t="s" s="12">
-        <v>366</v>
+        <v>426</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="6">
-        <v>195</v>
+        <v>322</v>
       </c>
       <c r="B138" t="s" s="7">
-        <v>367</v>
+        <v>427</v>
       </c>
       <c r="D138" s="9">
-        <v>167</v>
+        <v>285</v>
       </c>
       <c r="E138" s="10">
         <v>4</v>
       </c>
       <c r="F138" t="s" s="11">
-        <v>368</v>
+        <v>428</v>
       </c>
       <c r="G138" t="s" s="12">
-        <v>369</v>
+        <v>429</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6">
-        <v>198</v>
+        <v>324</v>
       </c>
       <c r="B139" t="s" s="7">
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="D139" s="9">
-        <v>169</v>
+        <v>287</v>
       </c>
       <c r="E139" s="10">
         <v>4</v>
       </c>
       <c r="F139" t="s" s="11">
-        <v>371</v>
+        <v>431</v>
       </c>
       <c r="G139" t="s" s="12">
-        <v>372</v>
+        <v>432</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="6">
-        <v>200</v>
+        <v>326</v>
       </c>
       <c r="B140" t="s" s="7">
-        <v>373</v>
+        <v>433</v>
       </c>
       <c r="D140" s="9">
-        <v>171</v>
+        <v>289</v>
       </c>
       <c r="E140" s="10">
         <v>4</v>
       </c>
       <c r="F140" t="s" s="11">
-        <v>374</v>
+        <v>434</v>
       </c>
       <c r="G140" t="s" s="12">
-        <v>375</v>
+        <v>435</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6">
-        <v>201</v>
+        <v>328</v>
       </c>
       <c r="B141" t="s" s="7">
-        <v>376</v>
+        <v>436</v>
       </c>
       <c r="D141" s="9">
-        <v>173</v>
+        <v>291</v>
       </c>
       <c r="E141" s="10">
         <v>4</v>
       </c>
       <c r="F141" t="s" s="11">
-        <v>377</v>
+        <v>437</v>
       </c>
       <c r="G141" t="s" s="12">
-        <v>378</v>
+        <v>438</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="6">
-        <v>204</v>
+        <v>330</v>
       </c>
       <c r="B142" t="s" s="7">
-        <v>379</v>
+        <v>439</v>
       </c>
       <c r="D142" s="9">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="E142" s="10">
         <v>4</v>
       </c>
       <c r="F142" t="s" s="11">
-        <v>380</v>
+        <v>440</v>
       </c>
       <c r="G142" t="s" s="12">
-        <v>381</v>
+        <v>441</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6">
-        <v>205</v>
+        <v>332</v>
       </c>
       <c r="B143" t="s" s="7">
-        <v>382</v>
+        <v>442</v>
       </c>
       <c r="D143" s="9">
-        <v>177</v>
+        <v>295</v>
       </c>
       <c r="E143" s="10">
         <v>4</v>
       </c>
       <c r="F143" t="s" s="11">
-        <v>383</v>
+        <v>443</v>
       </c>
       <c r="G143" t="s" s="12">
-        <v>384</v>
+        <v>444</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="6">
-        <v>208</v>
+        <v>334</v>
       </c>
       <c r="B144" t="s" s="7">
-        <v>385</v>
+        <v>445</v>
       </c>
       <c r="D144" s="9">
-        <v>179</v>
+        <v>297</v>
       </c>
       <c r="E144" s="10">
         <v>4</v>
       </c>
       <c r="F144" t="s" s="11">
-        <v>386</v>
+        <v>446</v>
       </c>
       <c r="G144" t="s" s="12">
-        <v>387</v>
+        <v>447</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6">
-        <v>209</v>
+        <v>336</v>
       </c>
       <c r="B145" t="s" s="7">
-        <v>388</v>
+        <v>448</v>
       </c>
       <c r="D145" s="9">
-        <v>181</v>
+        <v>301</v>
       </c>
       <c r="E145" s="10">
         <v>4</v>
       </c>
       <c r="F145" t="s" s="11">
-        <v>389</v>
+        <v>449</v>
       </c>
       <c r="G145" t="s" s="12">
-        <v>390</v>
+        <v>450</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="6">
-        <v>212</v>
+        <v>338</v>
       </c>
       <c r="B146" t="s" s="7">
-        <v>391</v>
+        <v>451</v>
       </c>
       <c r="D146" s="9">
-        <v>183</v>
+        <v>299</v>
       </c>
       <c r="E146" s="10">
         <v>4</v>
       </c>
       <c r="F146" t="s" s="11">
-        <v>392</v>
+        <v>452</v>
       </c>
       <c r="G146" t="s" s="12">
-        <v>393</v>
+        <v>453</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6">
-        <v>213</v>
+        <v>340</v>
       </c>
       <c r="B147" t="s" s="7">
-        <v>394</v>
+        <v>454</v>
       </c>
       <c r="D147" s="9">
-        <v>185</v>
+        <v>304</v>
       </c>
       <c r="E147" s="10">
         <v>4</v>
       </c>
       <c r="F147" t="s" s="11">
-        <v>395</v>
+        <v>455</v>
       </c>
       <c r="G147" t="s" s="12">
-        <v>396</v>
+        <v>456</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="6">
-        <v>216</v>
+        <v>342</v>
       </c>
       <c r="B148" t="s" s="7">
-        <v>397</v>
+        <v>457</v>
       </c>
       <c r="D148" s="9">
-        <v>187</v>
+        <v>305</v>
       </c>
       <c r="E148" s="10">
         <v>4</v>
       </c>
       <c r="F148" t="s" s="11">
-        <v>398</v>
+        <v>458</v>
       </c>
       <c r="G148" t="s" s="12">
-        <v>399</v>
+        <v>459</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="6">
-        <v>217</v>
+        <v>344</v>
       </c>
       <c r="B149" t="s" s="7">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="D149" s="9">
-        <v>189</v>
+        <v>307</v>
       </c>
       <c r="E149" s="10">
         <v>4</v>
       </c>
       <c r="F149" t="s" s="11">
-        <v>401</v>
+        <v>461</v>
       </c>
       <c r="G149" t="s" s="12">
-        <v>402</v>
+        <v>462</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="6">
-        <v>220</v>
+        <v>347</v>
       </c>
       <c r="B150" t="s" s="7">
-        <v>403</v>
+        <v>463</v>
       </c>
       <c r="D150" s="9">
-        <v>191</v>
+        <v>310</v>
       </c>
       <c r="E150" s="10">
         <v>4</v>
       </c>
       <c r="F150" t="s" s="11">
-        <v>404</v>
+        <v>464</v>
       </c>
       <c r="G150" t="s" s="12">
-        <v>405</v>
+        <v>465</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6">
-        <v>221</v>
+        <v>349</v>
       </c>
       <c r="B151" t="s" s="7">
-        <v>406</v>
+        <v>466</v>
       </c>
       <c r="D151" s="9">
-        <v>193</v>
+        <v>312</v>
       </c>
       <c r="E151" s="10">
         <v>4</v>
       </c>
       <c r="F151" t="s" s="11">
-        <v>407</v>
+        <v>467</v>
       </c>
       <c r="G151" t="s" s="12">
-        <v>408</v>
+        <v>468</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="6">
-        <v>224</v>
+        <v>353</v>
       </c>
       <c r="B152" t="s" s="7">
-        <v>409</v>
+        <v>469</v>
       </c>
       <c r="D152" s="9">
-        <v>119</v>
+        <v>314</v>
       </c>
       <c r="E152" s="10">
         <v>4</v>
       </c>
       <c r="F152" t="s" s="11">
-        <v>410</v>
+        <v>470</v>
       </c>
       <c r="G152" t="s" s="12">
-        <v>411</v>
+        <v>471</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="6">
-        <v>225</v>
+        <v>354</v>
       </c>
       <c r="B153" t="s" s="7">
-        <v>412</v>
+        <v>472</v>
       </c>
       <c r="D153" s="9">
-        <v>196</v>
+        <v>317</v>
       </c>
       <c r="E153" s="10">
         <v>4</v>
       </c>
       <c r="F153" t="s" s="11">
-        <v>413</v>
+        <v>473</v>
       </c>
       <c r="G153" t="s" s="12">
-        <v>414</v>
+        <v>474</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="6">
-        <v>227</v>
+        <v>358</v>
       </c>
       <c r="B154" t="s" s="7">
-        <v>415</v>
+        <v>475</v>
       </c>
       <c r="D154" s="9">
-        <v>199</v>
+        <v>319</v>
       </c>
       <c r="E154" s="10">
         <v>4</v>
       </c>
       <c r="F154" t="s" s="11">
-        <v>416</v>
+        <v>476</v>
       </c>
       <c r="G154" t="s" s="12">
-        <v>417</v>
+        <v>477</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="6">
-        <v>229</v>
+        <v>361</v>
       </c>
       <c r="B155" t="s" s="7">
-        <v>418</v>
+        <v>478</v>
       </c>
       <c r="D155" s="9">
-        <v>56</v>
+        <v>321</v>
       </c>
       <c r="E155" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F155" t="s" s="11">
-        <v>419</v>
+        <v>479</v>
       </c>
       <c r="G155" t="s" s="12">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="6">
-        <v>230</v>
+        <v>363</v>
       </c>
       <c r="B156" t="s" s="7">
-        <v>421</v>
+        <v>481</v>
       </c>
       <c r="D156" s="9">
-        <v>202</v>
+        <v>323</v>
       </c>
       <c r="E156" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F156" t="s" s="11">
-        <v>419</v>
+        <v>482</v>
       </c>
       <c r="G156" t="s" s="12">
-        <v>422</v>
+        <v>483</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6">
-        <v>231</v>
+        <v>366</v>
       </c>
       <c r="B157" t="s" s="7">
-        <v>423</v>
+        <v>484</v>
       </c>
       <c r="D157" s="9">
-        <v>201</v>
+        <v>325</v>
       </c>
       <c r="E157" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F157" t="s" s="11">
-        <v>419</v>
+        <v>485</v>
       </c>
       <c r="G157" t="s" s="12">
-        <v>424</v>
+        <v>486</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="6">
-        <v>232</v>
+        <v>368</v>
       </c>
       <c r="B158" t="s" s="7">
-        <v>425</v>
+        <v>487</v>
       </c>
       <c r="D158" s="9">
-        <v>203</v>
+        <v>328</v>
       </c>
       <c r="E158" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F158" t="s" s="11">
-        <v>419</v>
+        <v>488</v>
       </c>
       <c r="G158" t="s" s="12">
-        <v>426</v>
+        <v>489</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="6">
-        <v>233</v>
+        <v>369</v>
       </c>
       <c r="B159" t="s" s="7">
-        <v>427</v>
+        <v>490</v>
       </c>
       <c r="D159" s="9">
-        <v>200</v>
+        <v>329</v>
       </c>
       <c r="E159" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F159" t="s" s="11">
-        <v>162</v>
+        <v>491</v>
       </c>
       <c r="G159" t="s" s="12">
-        <v>428</v>
+        <v>492</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="6">
-        <v>234</v>
+        <v>372</v>
       </c>
       <c r="B160" t="s" s="7">
-        <v>429</v>
+        <v>493</v>
       </c>
       <c r="D160" s="9">
-        <v>201</v>
+        <v>331</v>
       </c>
       <c r="E160" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F160" t="s" s="11">
-        <v>162</v>
+        <v>494</v>
       </c>
       <c r="G160" t="s" s="12">
-        <v>430</v>
+        <v>495</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="6">
-        <v>235</v>
+        <v>374</v>
       </c>
       <c r="B161" t="s" s="7">
-        <v>431</v>
+        <v>496</v>
       </c>
       <c r="D161" s="9">
-        <v>202</v>
+        <v>334</v>
       </c>
       <c r="E161" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F161" t="s" s="11">
-        <v>162</v>
+        <v>497</v>
       </c>
       <c r="G161" t="s" s="12">
-        <v>432</v>
+        <v>498</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="6">
-        <v>236</v>
+        <v>375</v>
       </c>
       <c r="B162" t="s" s="7">
-        <v>433</v>
+        <v>499</v>
       </c>
       <c r="D162" s="9">
-        <v>203</v>
+        <v>335</v>
       </c>
       <c r="E162" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F162" t="s" s="11">
-        <v>162</v>
+        <v>500</v>
       </c>
       <c r="G162" t="s" s="12">
-        <v>434</v>
+        <v>501</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="6">
-        <v>237</v>
+        <v>378</v>
       </c>
       <c r="B163" t="s" s="7">
-        <v>435</v>
+        <v>502</v>
       </c>
       <c r="D163" s="9">
-        <v>204</v>
+        <v>337</v>
       </c>
       <c r="E163" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F163" t="s" s="11">
-        <v>162</v>
+        <v>503</v>
       </c>
       <c r="G163" t="s" s="12">
-        <v>436</v>
+        <v>504</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="6">
-        <v>238</v>
+        <v>379</v>
       </c>
       <c r="B164" t="s" s="7">
-        <v>437</v>
+        <v>505</v>
       </c>
       <c r="D164" s="9">
-        <v>205</v>
+        <v>339</v>
       </c>
       <c r="E164" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F164" t="s" s="11">
-        <v>438</v>
+        <v>506</v>
       </c>
       <c r="G164" t="s" s="12">
-        <v>439</v>
+        <v>507</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="6">
-        <v>239</v>
+        <v>382</v>
       </c>
       <c r="B165" t="s" s="7">
-        <v>440</v>
+        <v>508</v>
       </c>
       <c r="D165" s="9">
-        <v>206</v>
+        <v>341</v>
       </c>
       <c r="E165" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F165" t="s" s="11">
-        <v>438</v>
+        <v>509</v>
       </c>
       <c r="G165" t="s" s="12">
-        <v>441</v>
+        <v>510</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="6">
-        <v>240</v>
+        <v>384</v>
       </c>
       <c r="B166" t="s" s="7">
-        <v>442</v>
+        <v>511</v>
       </c>
       <c r="D166" s="9">
-        <v>207</v>
+        <v>344</v>
       </c>
       <c r="E166" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F166" t="s" s="11">
-        <v>438</v>
+        <v>512</v>
       </c>
       <c r="G166" t="s" s="12">
-        <v>443</v>
+        <v>513</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="6">
-        <v>241</v>
+        <v>385</v>
       </c>
       <c r="B167" t="s" s="7">
-        <v>444</v>
+        <v>514</v>
       </c>
       <c r="D167" s="9">
-        <v>111</v>
+        <v>346</v>
       </c>
       <c r="E167" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F167" t="s" s="11">
-        <v>445</v>
+        <v>515</v>
       </c>
       <c r="G167" t="s" s="12">
-        <v>446</v>
+        <v>516</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="6">
-        <v>242</v>
+        <v>387</v>
       </c>
       <c r="B168" t="s" s="7">
-        <v>447</v>
+        <v>517</v>
       </c>
       <c r="D168" s="9">
-        <v>208</v>
+        <v>347</v>
       </c>
       <c r="E168" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F168" t="s" s="11">
-        <v>445</v>
+        <v>518</v>
       </c>
       <c r="G168" t="s" s="12">
-        <v>448</v>
+        <v>519</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="6">
-        <v>243</v>
+        <v>390</v>
       </c>
       <c r="B169" t="s" s="7">
-        <v>449</v>
+        <v>520</v>
       </c>
       <c r="D169" s="9">
-        <v>209</v>
+        <v>350</v>
       </c>
       <c r="E169" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F169" t="s" s="11">
-        <v>445</v>
+        <v>521</v>
       </c>
       <c r="G169" t="s" s="12">
-        <v>450</v>
+        <v>522</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="6">
-        <v>244</v>
+        <v>392</v>
       </c>
       <c r="B170" t="s" s="7">
-        <v>451</v>
+        <v>523</v>
       </c>
       <c r="D170" s="9">
-        <v>210</v>
+        <v>351</v>
       </c>
       <c r="E170" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F170" t="s" s="11">
-        <v>445</v>
+        <v>524</v>
       </c>
       <c r="G170" t="s" s="12">
-        <v>452</v>
+        <v>525</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="6">
-        <v>245</v>
+        <v>394</v>
       </c>
       <c r="B171" t="s" s="7">
-        <v>453</v>
+        <v>526</v>
       </c>
       <c r="D171" s="9">
-        <v>211</v>
+        <v>353</v>
       </c>
       <c r="E171" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F171" t="s" s="11">
-        <v>454</v>
+        <v>527</v>
       </c>
       <c r="G171" t="s" s="12">
-        <v>455</v>
+        <v>528</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="6">
-        <v>246</v>
+        <v>395</v>
       </c>
       <c r="B172" t="s" s="7">
-        <v>456</v>
+        <v>529</v>
       </c>
       <c r="D172" s="9">
-        <v>212</v>
+        <v>356</v>
       </c>
       <c r="E172" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F172" t="s" s="11">
-        <v>454</v>
+        <v>530</v>
       </c>
       <c r="G172" t="s" s="12">
-        <v>457</v>
+        <v>531</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="6">
-        <v>247</v>
+        <v>397</v>
       </c>
       <c r="B173" t="s" s="7">
-        <v>458</v>
+        <v>532</v>
       </c>
       <c r="D173" s="9">
-        <v>213</v>
+        <v>358</v>
       </c>
       <c r="E173" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F173" t="s" s="11">
-        <v>454</v>
+        <v>533</v>
       </c>
       <c r="G173" t="s" s="12">
-        <v>459</v>
+        <v>534</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="6">
-        <v>248</v>
+        <v>400</v>
       </c>
       <c r="B174" t="s" s="7">
-        <v>460</v>
+        <v>535</v>
       </c>
       <c r="D174" s="9">
-        <v>214</v>
+        <v>362</v>
       </c>
       <c r="E174" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F174" t="s" s="11">
-        <v>454</v>
+        <v>536</v>
       </c>
       <c r="G174" t="s" s="12">
-        <v>461</v>
+        <v>537</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="6">
-        <v>249</v>
+        <v>401</v>
       </c>
       <c r="B175" t="s" s="7">
-        <v>462</v>
+        <v>538</v>
       </c>
       <c r="D175" s="9">
-        <v>215</v>
+        <v>359</v>
       </c>
       <c r="E175" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F175" t="s" s="11">
-        <v>454</v>
+        <v>539</v>
       </c>
       <c r="G175" t="s" s="12">
-        <v>463</v>
+        <v>540</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="6">
-        <v>250</v>
+        <v>404</v>
       </c>
       <c r="B176" t="s" s="7">
-        <v>464</v>
+        <v>541</v>
       </c>
       <c r="D176" s="9">
-        <v>216</v>
+        <v>364</v>
       </c>
       <c r="E176" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F176" t="s" s="11">
-        <v>465</v>
+        <v>542</v>
       </c>
       <c r="G176" t="s" s="12">
-        <v>466</v>
+        <v>543</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="6">
-        <v>251</v>
+        <v>405</v>
       </c>
       <c r="B177" t="s" s="7">
-        <v>467</v>
+        <v>544</v>
       </c>
       <c r="D177" s="9">
-        <v>217</v>
+        <v>365</v>
       </c>
       <c r="E177" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F177" t="s" s="11">
-        <v>465</v>
+        <v>545</v>
       </c>
       <c r="G177" t="s" s="12">
-        <v>468</v>
+        <v>546</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="6">
-        <v>252</v>
+        <v>408</v>
       </c>
       <c r="B178" t="s" s="7">
-        <v>469</v>
+        <v>547</v>
       </c>
       <c r="D178" s="9">
-        <v>218</v>
+        <v>368</v>
       </c>
       <c r="E178" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F178" t="s" s="11">
-        <v>465</v>
+        <v>548</v>
       </c>
       <c r="G178" t="s" s="12">
-        <v>470</v>
+        <v>549</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="6">
-        <v>253</v>
+        <v>409</v>
       </c>
       <c r="B179" t="s" s="7">
-        <v>471</v>
+        <v>550</v>
       </c>
       <c r="D179" s="9">
-        <v>219</v>
+        <v>370</v>
       </c>
       <c r="E179" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F179" t="s" s="11">
-        <v>465</v>
+        <v>275</v>
       </c>
       <c r="G179" t="s" s="12">
-        <v>472</v>
+        <v>551</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="6">
-        <v>254</v>
+        <v>412</v>
       </c>
       <c r="B180" t="s" s="7">
-        <v>473</v>
-      </c>
-      <c r="C180" t="s" s="8">
-        <v>474</v>
+        <v>552</v>
       </c>
       <c r="D180" s="9">
-        <v>222</v>
+        <v>372</v>
       </c>
       <c r="E180" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F180" t="s" s="11">
-        <v>475</v>
+        <v>553</v>
       </c>
       <c r="G180" t="s" s="12">
-        <v>476</v>
+        <v>554</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="6">
-        <v>255</v>
+        <v>413</v>
       </c>
       <c r="B181" t="s" s="7">
-        <v>477</v>
-      </c>
-      <c r="C181" t="s" s="8">
-        <v>478</v>
+        <v>555</v>
       </c>
       <c r="D181" s="9">
-        <v>221</v>
+        <v>373</v>
       </c>
       <c r="E181" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F181" t="s" s="11">
-        <v>475</v>
+        <v>556</v>
       </c>
       <c r="G181" t="s" s="12">
-        <v>479</v>
+        <v>557</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="6">
-        <v>256</v>
+        <v>417</v>
       </c>
       <c r="B182" t="s" s="7">
-        <v>480</v>
+        <v>558</v>
       </c>
       <c r="D182" s="9">
-        <v>220</v>
+        <v>375</v>
       </c>
       <c r="E182" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F182" t="s" s="11">
-        <v>475</v>
+        <v>559</v>
       </c>
       <c r="G182" t="s" s="12">
-        <v>481</v>
+        <v>560</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="6">
-        <v>257</v>
+        <v>418</v>
       </c>
       <c r="B183" t="s" s="7">
-        <v>482</v>
+        <v>561</v>
       </c>
       <c r="D183" s="9">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E183" s="10">
         <v>1</v>
       </c>
       <c r="F183" t="s" s="11">
-        <v>475</v>
+        <v>562</v>
       </c>
       <c r="G183" t="s" s="12">
-        <v>483</v>
+        <v>563</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="6">
-        <v>258</v>
+        <v>421</v>
       </c>
       <c r="B184" t="s" s="7">
-        <v>484</v>
-      </c>
-      <c r="D184" s="9">
-        <v>223</v>
-      </c>
-      <c r="E184" s="10">
-        <v>4</v>
-      </c>
-      <c r="F184" t="s" s="11">
-        <v>485</v>
-      </c>
-      <c r="G184" t="s" s="12">
-        <v>486</v>
+        <v>564</v>
+      </c>
+      <c r="C184" t="s" s="8">
+        <v>565</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="6">
-        <v>260</v>
+        <v>436</v>
       </c>
       <c r="B185" t="s" s="7">
-        <v>487</v>
+        <v>566</v>
       </c>
       <c r="D185" s="9">
-        <v>226</v>
+        <v>376</v>
       </c>
       <c r="E185" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F185" t="s" s="11">
-        <v>488</v>
+        <v>567</v>
       </c>
       <c r="G185" t="s" s="12">
-        <v>489</v>
+        <v>568</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="6">
-        <v>262</v>
+        <v>440</v>
       </c>
       <c r="B186" t="s" s="7">
-        <v>490</v>
+        <v>569</v>
       </c>
       <c r="D186" s="9">
-        <v>228</v>
+        <v>379</v>
       </c>
       <c r="E186" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F186" t="s" s="11">
-        <v>491</v>
+        <v>570</v>
       </c>
       <c r="G186" t="s" s="12">
-        <v>492</v>
+        <v>571</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="6">
-        <v>264</v>
+        <v>441</v>
       </c>
       <c r="B187" t="s" s="7">
-        <v>493</v>
+        <v>572</v>
       </c>
       <c r="D187" s="9">
-        <v>230</v>
+        <v>380</v>
       </c>
       <c r="E187" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F187" t="s" s="11">
-        <v>494</v>
+        <v>573</v>
       </c>
       <c r="G187" t="s" s="12">
-        <v>495</v>
+        <v>574</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="6">
-        <v>266</v>
+        <v>442</v>
       </c>
       <c r="B188" t="s" s="7">
-        <v>496</v>
+        <v>575</v>
       </c>
       <c r="D188" s="9">
-        <v>232</v>
+        <v>314</v>
       </c>
       <c r="E188" s="10">
         <v>4</v>
       </c>
       <c r="F188" t="s" s="11">
-        <v>497</v>
+        <v>576</v>
       </c>
       <c r="G188" t="s" s="12">
-        <v>498</v>
+        <v>577</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="6">
-        <v>268</v>
+        <v>443</v>
       </c>
       <c r="B189" t="s" s="7">
-        <v>499</v>
-      </c>
-      <c r="D189" s="9">
-        <v>234</v>
+        <v>578</v>
       </c>
       <c r="E189" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F189" t="s" s="11">
-        <v>500</v>
+        <v>579</v>
       </c>
       <c r="G189" t="s" s="12">
-        <v>501</v>
+        <v>580</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="6">
-        <v>270</v>
+        <v>444</v>
       </c>
       <c r="B190" t="s" s="7">
-        <v>502</v>
-      </c>
-      <c r="D190" s="9">
-        <v>236</v>
+        <v>581</v>
       </c>
       <c r="E190" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F190" t="s" s="11">
-        <v>503</v>
+        <v>582</v>
       </c>
       <c r="G190" t="s" s="12">
-        <v>504</v>
+        <v>583</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="6">
-        <v>272</v>
+        <v>445</v>
       </c>
       <c r="B191" t="s" s="7">
-        <v>505</v>
-      </c>
-      <c r="D191" s="9">
-        <v>238</v>
+        <v>584</v>
       </c>
       <c r="E191" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F191" t="s" s="11">
-        <v>506</v>
+        <v>585</v>
       </c>
       <c r="G191" t="s" s="12">
-        <v>507</v>
+        <v>586</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="6">
-        <v>274</v>
+        <v>446</v>
       </c>
       <c r="B192" t="s" s="7">
-        <v>508</v>
-      </c>
-      <c r="D192" s="9">
-        <v>240</v>
+        <v>587</v>
       </c>
       <c r="E192" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F192" t="s" s="11">
-        <v>509</v>
+        <v>588</v>
       </c>
       <c r="G192" t="s" s="12">
-        <v>510</v>
+        <v>589</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="6">
-        <v>276</v>
+        <v>447</v>
       </c>
       <c r="B193" t="s" s="7">
-        <v>511</v>
-      </c>
-      <c r="D193" s="9">
-        <v>242</v>
+        <v>590</v>
       </c>
       <c r="E193" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F193" t="s" s="11">
-        <v>512</v>
+        <v>591</v>
       </c>
       <c r="G193" t="s" s="12">
-        <v>513</v>
+        <v>592</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="6">
-        <v>279</v>
+        <v>448</v>
       </c>
       <c r="B194" t="s" s="7">
-        <v>514</v>
-      </c>
-      <c r="D194" s="9">
-        <v>244</v>
+        <v>593</v>
+      </c>
+      <c r="C194" t="s" s="8">
+        <v>594</v>
       </c>
       <c r="E194" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F194" t="s" s="11">
-        <v>515</v>
+        <v>595</v>
       </c>
       <c r="G194" t="s" s="12">
-        <v>516</v>
+        <v>596</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="6">
-        <v>280</v>
+        <v>449</v>
       </c>
       <c r="B195" t="s" s="7">
-        <v>517</v>
-      </c>
-      <c r="D195" s="9">
-        <v>247</v>
+        <v>597</v>
+      </c>
+      <c r="C195" t="s" s="8">
+        <v>598</v>
       </c>
       <c r="E195" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F195" t="s" s="11">
-        <v>518</v>
+        <v>599</v>
       </c>
       <c r="G195" t="s" s="12">
-        <v>519</v>
+        <v>600</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="6">
-        <v>283</v>
+        <v>450</v>
       </c>
       <c r="B196" t="s" s="7">
-        <v>520</v>
-      </c>
-      <c r="D196" s="9">
-        <v>248</v>
+        <v>601</v>
+      </c>
+      <c r="C196" t="s" s="8">
+        <v>602</v>
       </c>
       <c r="E196" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F196" t="s" s="11">
-        <v>521</v>
+        <v>603</v>
       </c>
       <c r="G196" t="s" s="12">
-        <v>522</v>
+        <v>604</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="6">
-        <v>284</v>
+        <v>451</v>
       </c>
       <c r="B197" t="s" s="7">
-        <v>523</v>
+        <v>605</v>
       </c>
       <c r="D197" s="9">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="E197" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F197" t="s" s="11">
-        <v>524</v>
+        <v>606</v>
       </c>
       <c r="G197" t="s" s="12">
-        <v>525</v>
+        <v>607</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="6">
-        <v>286</v>
+        <v>452</v>
       </c>
       <c r="B198" t="s" s="7">
-        <v>526</v>
+        <v>608</v>
       </c>
       <c r="D198" s="9">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="E198" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F198" t="s" s="11">
-        <v>527</v>
+        <v>609</v>
       </c>
       <c r="G198" t="s" s="12">
-        <v>528</v>
+        <v>610</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="6">
-        <v>289</v>
+        <v>453</v>
       </c>
       <c r="B199" t="s" s="7">
-        <v>529</v>
+        <v>611</v>
+      </c>
+      <c r="C199" t="s" s="8">
+        <v>612</v>
       </c>
       <c r="D199" s="9">
-        <v>254</v>
+        <v>225</v>
       </c>
       <c r="E199" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F199" t="s" s="11">
-        <v>530</v>
+        <v>613</v>
       </c>
       <c r="G199" t="s" s="12">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="6">
-        <v>291</v>
-      </c>
-      <c r="B200" t="s" s="7">
-        <v>532</v>
-      </c>
-      <c r="D200" s="9">
-        <v>256</v>
-      </c>
-      <c r="E200" s="10">
-        <v>4</v>
-      </c>
-      <c r="F200" t="s" s="11">
-        <v>533</v>
-      </c>
-      <c r="G200" t="s" s="12">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="6">
-        <v>293</v>
-      </c>
-      <c r="B201" t="s" s="7">
-        <v>535</v>
-      </c>
-      <c r="D201" s="9">
-        <v>258</v>
-      </c>
-      <c r="E201" s="10">
-        <v>4</v>
-      </c>
-      <c r="F201" t="s" s="11">
-        <v>536</v>
-      </c>
-      <c r="G201" t="s" s="12">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="6">
-        <v>294</v>
-      </c>
-      <c r="B202" t="s" s="7">
-        <v>538</v>
-      </c>
-      <c r="D202" s="9">
-        <v>129</v>
-      </c>
-      <c r="E202" s="10">
-        <v>4</v>
-      </c>
-      <c r="F202" t="s" s="11">
-        <v>539</v>
-      </c>
-      <c r="G202" t="s" s="12">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="6">
-        <v>296</v>
-      </c>
-      <c r="B203" t="s" s="7">
-        <v>541</v>
-      </c>
-      <c r="D203" s="9">
-        <v>261</v>
-      </c>
-      <c r="E203" s="10">
-        <v>4</v>
-      </c>
-      <c r="F203" t="s" s="11">
-        <v>542</v>
-      </c>
-      <c r="G203" t="s" s="12">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="6">
-        <v>299</v>
-      </c>
-      <c r="B204" t="s" s="7">
-        <v>544</v>
-      </c>
-      <c r="D204" s="9">
-        <v>264</v>
-      </c>
-      <c r="E204" s="10">
-        <v>4</v>
-      </c>
-      <c r="F204" t="s" s="11">
-        <v>545</v>
-      </c>
-      <c r="G204" t="s" s="12">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="6">
-        <v>301</v>
-      </c>
-      <c r="B205" t="s" s="7">
-        <v>547</v>
-      </c>
-      <c r="D205" s="9">
-        <v>265</v>
-      </c>
-      <c r="E205" s="10">
-        <v>4</v>
-      </c>
-      <c r="F205" t="s" s="11">
-        <v>548</v>
-      </c>
-      <c r="G205" t="s" s="12">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="6">
-        <v>307</v>
-      </c>
-      <c r="B206" t="s" s="7">
-        <v>550</v>
-      </c>
-      <c r="D206" s="9">
-        <v>269</v>
-      </c>
-      <c r="E206" s="10">
-        <v>4</v>
-      </c>
-      <c r="F206" t="s" s="11">
-        <v>551</v>
-      </c>
-      <c r="G206" t="s" s="12">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="6">
-        <v>308</v>
-      </c>
-      <c r="B207" t="s" s="7">
-        <v>553</v>
-      </c>
-      <c r="D207" s="9">
-        <v>272</v>
-      </c>
-      <c r="E207" s="10">
-        <v>4</v>
-      </c>
-      <c r="F207" t="s" s="11">
-        <v>554</v>
-      </c>
-      <c r="G207" t="s" s="12">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="6">
-        <v>310</v>
-      </c>
-      <c r="B208" t="s" s="7">
-        <v>556</v>
-      </c>
-      <c r="D208" s="9">
-        <v>273</v>
-      </c>
-      <c r="E208" s="10">
-        <v>4</v>
-      </c>
-      <c r="F208" t="s" s="11">
-        <v>557</v>
-      </c>
-      <c r="G208" t="s" s="12">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="6">
-        <v>313</v>
-      </c>
-      <c r="B209" t="s" s="7">
-        <v>559</v>
-      </c>
-      <c r="D209" s="9">
-        <v>276</v>
-      </c>
-      <c r="E209" s="10">
-        <v>4</v>
-      </c>
-      <c r="F209" t="s" s="11">
-        <v>560</v>
-      </c>
-      <c r="G209" t="s" s="12">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="6">
-        <v>316</v>
-      </c>
-      <c r="B210" t="s" s="7">
-        <v>562</v>
-      </c>
-      <c r="D210" s="9">
-        <v>280</v>
-      </c>
-      <c r="E210" s="10">
-        <v>4</v>
-      </c>
-      <c r="F210" t="s" s="11">
-        <v>563</v>
-      </c>
-      <c r="G210" t="s" s="12">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="6">
-        <v>318</v>
-      </c>
-      <c r="B211" t="s" s="7">
-        <v>565</v>
-      </c>
-      <c r="D211" s="9">
-        <v>281</v>
-      </c>
-      <c r="E211" s="10">
-        <v>4</v>
-      </c>
-      <c r="F211" t="s" s="11">
-        <v>566</v>
-      </c>
-      <c r="G211" t="s" s="12">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="6">
-        <v>320</v>
-      </c>
-      <c r="B212" t="s" s="7">
-        <v>568</v>
-      </c>
-      <c r="D212" s="9">
-        <v>283</v>
-      </c>
-      <c r="E212" s="10">
-        <v>4</v>
-      </c>
-      <c r="F212" t="s" s="11">
-        <v>569</v>
-      </c>
-      <c r="G212" t="s" s="12">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="6">
-        <v>322</v>
-      </c>
-      <c r="B213" t="s" s="7">
-        <v>571</v>
-      </c>
-      <c r="D213" s="9">
-        <v>285</v>
-      </c>
-      <c r="E213" s="10">
-        <v>4</v>
-      </c>
-      <c r="F213" t="s" s="11">
-        <v>572</v>
-      </c>
-      <c r="G213" t="s" s="12">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="6">
-        <v>324</v>
-      </c>
-      <c r="B214" t="s" s="7">
-        <v>574</v>
-      </c>
-      <c r="D214" s="9">
-        <v>287</v>
-      </c>
-      <c r="E214" s="10">
-        <v>4</v>
-      </c>
-      <c r="F214" t="s" s="11">
-        <v>575</v>
-      </c>
-      <c r="G214" t="s" s="12">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="6">
-        <v>326</v>
-      </c>
-      <c r="B215" t="s" s="7">
-        <v>577</v>
-      </c>
-      <c r="D215" s="9">
-        <v>289</v>
-      </c>
-      <c r="E215" s="10">
-        <v>4</v>
-      </c>
-      <c r="F215" t="s" s="11">
-        <v>578</v>
-      </c>
-      <c r="G215" t="s" s="12">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="6">
-        <v>328</v>
-      </c>
-      <c r="B216" t="s" s="7">
-        <v>580</v>
-      </c>
-      <c r="D216" s="9">
-        <v>291</v>
-      </c>
-      <c r="E216" s="10">
-        <v>4</v>
-      </c>
-      <c r="F216" t="s" s="11">
-        <v>581</v>
-      </c>
-      <c r="G216" t="s" s="12">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="6">
-        <v>330</v>
-      </c>
-      <c r="B217" t="s" s="7">
-        <v>583</v>
-      </c>
-      <c r="D217" s="9">
-        <v>293</v>
-      </c>
-      <c r="E217" s="10">
-        <v>4</v>
-      </c>
-      <c r="F217" t="s" s="11">
-        <v>584</v>
-      </c>
-      <c r="G217" t="s" s="12">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="6">
-        <v>332</v>
-      </c>
-      <c r="B218" t="s" s="7">
-        <v>586</v>
-      </c>
-      <c r="D218" s="9">
-        <v>295</v>
-      </c>
-      <c r="E218" s="10">
-        <v>4</v>
-      </c>
-      <c r="F218" t="s" s="11">
-        <v>587</v>
-      </c>
-      <c r="G218" t="s" s="12">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="6">
-        <v>334</v>
-      </c>
-      <c r="B219" t="s" s="7">
-        <v>589</v>
-      </c>
-      <c r="D219" s="9">
-        <v>297</v>
-      </c>
-      <c r="E219" s="10">
-        <v>4</v>
-      </c>
-      <c r="F219" t="s" s="11">
-        <v>590</v>
-      </c>
-      <c r="G219" t="s" s="12">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="6">
-        <v>336</v>
-      </c>
-      <c r="B220" t="s" s="7">
-        <v>592</v>
-      </c>
-      <c r="D220" s="9">
-        <v>301</v>
-      </c>
-      <c r="E220" s="10">
-        <v>4</v>
-      </c>
-      <c r="F220" t="s" s="11">
-        <v>593</v>
-      </c>
-      <c r="G220" t="s" s="12">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="6">
-        <v>338</v>
-      </c>
-      <c r="B221" t="s" s="7">
-        <v>595</v>
-      </c>
-      <c r="D221" s="9">
-        <v>299</v>
-      </c>
-      <c r="E221" s="10">
-        <v>4</v>
-      </c>
-      <c r="F221" t="s" s="11">
-        <v>596</v>
-      </c>
-      <c r="G221" t="s" s="12">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="6">
-        <v>340</v>
-      </c>
-      <c r="B222" t="s" s="7">
-        <v>598</v>
-      </c>
-      <c r="D222" s="9">
-        <v>304</v>
-      </c>
-      <c r="E222" s="10">
-        <v>4</v>
-      </c>
-      <c r="F222" t="s" s="11">
-        <v>599</v>
-      </c>
-      <c r="G222" t="s" s="12">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="6">
-        <v>342</v>
-      </c>
-      <c r="B223" t="s" s="7">
-        <v>601</v>
-      </c>
-      <c r="D223" s="9">
-        <v>305</v>
-      </c>
-      <c r="E223" s="10">
-        <v>4</v>
-      </c>
-      <c r="F223" t="s" s="11">
-        <v>602</v>
-      </c>
-      <c r="G223" t="s" s="12">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="6">
-        <v>344</v>
-      </c>
-      <c r="B224" t="s" s="7">
-        <v>604</v>
-      </c>
-      <c r="D224" s="9">
-        <v>307</v>
-      </c>
-      <c r="E224" s="10">
-        <v>4</v>
-      </c>
-      <c r="F224" t="s" s="11">
-        <v>605</v>
-      </c>
-      <c r="G224" t="s" s="12">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="6">
-        <v>347</v>
-      </c>
-      <c r="B225" t="s" s="7">
-        <v>607</v>
-      </c>
-      <c r="D225" s="9">
-        <v>310</v>
-      </c>
-      <c r="E225" s="10">
-        <v>4</v>
-      </c>
-      <c r="F225" t="s" s="11">
-        <v>608</v>
-      </c>
-      <c r="G225" t="s" s="12">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="6">
-        <v>349</v>
-      </c>
-      <c r="B226" t="s" s="7">
-        <v>610</v>
-      </c>
-      <c r="D226" s="9">
-        <v>312</v>
-      </c>
-      <c r="E226" s="10">
-        <v>4</v>
-      </c>
-      <c r="F226" t="s" s="11">
-        <v>611</v>
-      </c>
-      <c r="G226" t="s" s="12">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="6">
-        <v>353</v>
-      </c>
-      <c r="B227" t="s" s="7">
-        <v>613</v>
-      </c>
-      <c r="D227" s="9">
-        <v>314</v>
-      </c>
-      <c r="E227" s="10">
-        <v>4</v>
-      </c>
-      <c r="F227" t="s" s="11">
         <v>614</v>
-      </c>
-      <c r="G227" t="s" s="12">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="6">
-        <v>354</v>
-      </c>
-      <c r="B228" t="s" s="7">
-        <v>616</v>
-      </c>
-      <c r="D228" s="9">
-        <v>317</v>
-      </c>
-      <c r="E228" s="10">
-        <v>4</v>
-      </c>
-      <c r="F228" t="s" s="11">
-        <v>617</v>
-      </c>
-      <c r="G228" t="s" s="12">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="6">
-        <v>358</v>
-      </c>
-      <c r="B229" t="s" s="7">
-        <v>619</v>
-      </c>
-      <c r="D229" s="9">
-        <v>319</v>
-      </c>
-      <c r="E229" s="10">
-        <v>4</v>
-      </c>
-      <c r="F229" t="s" s="11">
-        <v>620</v>
-      </c>
-      <c r="G229" t="s" s="12">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="6">
-        <v>361</v>
-      </c>
-      <c r="B230" t="s" s="7">
-        <v>622</v>
-      </c>
-      <c r="D230" s="9">
-        <v>321</v>
-      </c>
-      <c r="E230" s="10">
-        <v>4</v>
-      </c>
-      <c r="F230" t="s" s="11">
-        <v>623</v>
-      </c>
-      <c r="G230" t="s" s="12">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="6">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="6">
-        <v>363</v>
-      </c>
-      <c r="B232" t="s" s="7">
-        <v>625</v>
-      </c>
-      <c r="D232" s="9">
-        <v>323</v>
-      </c>
-      <c r="E232" s="10">
-        <v>4</v>
-      </c>
-      <c r="F232" t="s" s="11">
-        <v>626</v>
-      </c>
-      <c r="G232" t="s" s="12">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="6">
-        <v>366</v>
-      </c>
-      <c r="B233" t="s" s="7">
-        <v>628</v>
-      </c>
-      <c r="D233" s="9">
-        <v>325</v>
-      </c>
-      <c r="E233" s="10">
-        <v>4</v>
-      </c>
-      <c r="F233" t="s" s="11">
-        <v>629</v>
-      </c>
-      <c r="G233" t="s" s="12">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="6">
-        <v>368</v>
-      </c>
-      <c r="B234" t="s" s="7">
-        <v>631</v>
-      </c>
-      <c r="D234" s="9">
-        <v>328</v>
-      </c>
-      <c r="E234" s="10">
-        <v>4</v>
-      </c>
-      <c r="F234" t="s" s="11">
-        <v>632</v>
-      </c>
-      <c r="G234" t="s" s="12">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="6">
-        <v>369</v>
-      </c>
-      <c r="B235" t="s" s="7">
-        <v>634</v>
-      </c>
-      <c r="D235" s="9">
-        <v>329</v>
-      </c>
-      <c r="E235" s="10">
-        <v>4</v>
-      </c>
-      <c r="F235" t="s" s="11">
-        <v>635</v>
-      </c>
-      <c r="G235" t="s" s="12">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="6">
-        <v>372</v>
-      </c>
-      <c r="B236" t="s" s="7">
-        <v>637</v>
-      </c>
-      <c r="D236" s="9">
-        <v>331</v>
-      </c>
-      <c r="E236" s="10">
-        <v>4</v>
-      </c>
-      <c r="F236" t="s" s="11">
-        <v>638</v>
-      </c>
-      <c r="G236" t="s" s="12">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="6">
-        <v>374</v>
-      </c>
-      <c r="B237" t="s" s="7">
-        <v>640</v>
-      </c>
-      <c r="D237" s="9">
-        <v>334</v>
-      </c>
-      <c r="E237" s="10">
-        <v>4</v>
-      </c>
-      <c r="F237" t="s" s="11">
-        <v>641</v>
-      </c>
-      <c r="G237" t="s" s="12">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="6">
-        <v>375</v>
-      </c>
-      <c r="B238" t="s" s="7">
-        <v>643</v>
-      </c>
-      <c r="D238" s="9">
-        <v>335</v>
-      </c>
-      <c r="E238" s="10">
-        <v>4</v>
-      </c>
-      <c r="F238" t="s" s="11">
-        <v>644</v>
-      </c>
-      <c r="G238" t="s" s="12">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="6">
-        <v>378</v>
-      </c>
-      <c r="B239" t="s" s="7">
-        <v>646</v>
-      </c>
-      <c r="D239" s="9">
-        <v>337</v>
-      </c>
-      <c r="E239" s="10">
-        <v>4</v>
-      </c>
-      <c r="F239" t="s" s="11">
-        <v>647</v>
-      </c>
-      <c r="G239" t="s" s="12">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="6">
-        <v>379</v>
-      </c>
-      <c r="B240" t="s" s="7">
-        <v>649</v>
-      </c>
-      <c r="D240" s="9">
-        <v>339</v>
-      </c>
-      <c r="E240" s="10">
-        <v>4</v>
-      </c>
-      <c r="F240" t="s" s="11">
-        <v>650</v>
-      </c>
-      <c r="G240" t="s" s="12">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="6">
-        <v>382</v>
-      </c>
-      <c r="B241" t="s" s="7">
-        <v>652</v>
-      </c>
-      <c r="D241" s="9">
-        <v>341</v>
-      </c>
-      <c r="E241" s="10">
-        <v>4</v>
-      </c>
-      <c r="F241" t="s" s="11">
-        <v>653</v>
-      </c>
-      <c r="G241" t="s" s="12">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="6">
-        <v>384</v>
-      </c>
-      <c r="B242" t="s" s="7">
-        <v>655</v>
-      </c>
-      <c r="D242" s="9">
-        <v>344</v>
-      </c>
-      <c r="E242" s="10">
-        <v>4</v>
-      </c>
-      <c r="F242" t="s" s="11">
-        <v>656</v>
-      </c>
-      <c r="G242" t="s" s="12">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="6">
-        <v>385</v>
-      </c>
-      <c r="B243" t="s" s="7">
-        <v>658</v>
-      </c>
-      <c r="D243" s="9">
-        <v>346</v>
-      </c>
-      <c r="E243" s="10">
-        <v>4</v>
-      </c>
-      <c r="F243" t="s" s="11">
-        <v>659</v>
-      </c>
-      <c r="G243" t="s" s="12">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="6">
-        <v>387</v>
-      </c>
-      <c r="B244" t="s" s="7">
-        <v>661</v>
-      </c>
-      <c r="D244" s="9">
-        <v>347</v>
-      </c>
-      <c r="E244" s="10">
-        <v>4</v>
-      </c>
-      <c r="F244" t="s" s="11">
-        <v>662</v>
-      </c>
-      <c r="G244" t="s" s="12">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="6">
-        <v>390</v>
-      </c>
-      <c r="B245" t="s" s="7">
-        <v>664</v>
-      </c>
-      <c r="D245" s="9">
-        <v>350</v>
-      </c>
-      <c r="E245" s="10">
-        <v>4</v>
-      </c>
-      <c r="F245" t="s" s="11">
-        <v>665</v>
-      </c>
-      <c r="G245" t="s" s="12">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="6">
-        <v>392</v>
-      </c>
-      <c r="B246" t="s" s="7">
-        <v>667</v>
-      </c>
-      <c r="D246" s="9">
-        <v>351</v>
-      </c>
-      <c r="E246" s="10">
-        <v>4</v>
-      </c>
-      <c r="F246" t="s" s="11">
-        <v>668</v>
-      </c>
-      <c r="G246" t="s" s="12">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="6">
-        <v>394</v>
-      </c>
-      <c r="B247" t="s" s="7">
-        <v>670</v>
-      </c>
-      <c r="D247" s="9">
-        <v>353</v>
-      </c>
-      <c r="E247" s="10">
-        <v>4</v>
-      </c>
-      <c r="F247" t="s" s="11">
-        <v>671</v>
-      </c>
-      <c r="G247" t="s" s="12">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="6">
-        <v>395</v>
-      </c>
-      <c r="B248" t="s" s="7">
-        <v>673</v>
-      </c>
-      <c r="D248" s="9">
-        <v>356</v>
-      </c>
-      <c r="E248" s="10">
-        <v>4</v>
-      </c>
-      <c r="F248" t="s" s="11">
-        <v>674</v>
-      </c>
-      <c r="G248" t="s" s="12">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="6">
-        <v>397</v>
-      </c>
-      <c r="B249" t="s" s="7">
-        <v>676</v>
-      </c>
-      <c r="D249" s="9">
-        <v>358</v>
-      </c>
-      <c r="E249" s="10">
-        <v>4</v>
-      </c>
-      <c r="F249" t="s" s="11">
-        <v>677</v>
-      </c>
-      <c r="G249" t="s" s="12">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="6">
-        <v>400</v>
-      </c>
-      <c r="B250" t="s" s="7">
-        <v>679</v>
-      </c>
-      <c r="D250" s="9">
-        <v>362</v>
-      </c>
-      <c r="E250" s="10">
-        <v>4</v>
-      </c>
-      <c r="F250" t="s" s="11">
-        <v>680</v>
-      </c>
-      <c r="G250" t="s" s="12">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="6">
-        <v>401</v>
-      </c>
-      <c r="B251" t="s" s="7">
-        <v>682</v>
-      </c>
-      <c r="D251" s="9">
-        <v>359</v>
-      </c>
-      <c r="E251" s="10">
-        <v>4</v>
-      </c>
-      <c r="F251" t="s" s="11">
-        <v>683</v>
-      </c>
-      <c r="G251" t="s" s="12">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="6">
-        <v>404</v>
-      </c>
-      <c r="B252" t="s" s="7">
-        <v>685</v>
-      </c>
-      <c r="D252" s="9">
-        <v>364</v>
-      </c>
-      <c r="E252" s="10">
-        <v>4</v>
-      </c>
-      <c r="F252" t="s" s="11">
-        <v>686</v>
-      </c>
-      <c r="G252" t="s" s="12">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="6">
-        <v>405</v>
-      </c>
-      <c r="B253" t="s" s="7">
-        <v>688</v>
-      </c>
-      <c r="D253" s="9">
-        <v>365</v>
-      </c>
-      <c r="E253" s="10">
-        <v>4</v>
-      </c>
-      <c r="F253" t="s" s="11">
-        <v>689</v>
-      </c>
-      <c r="G253" t="s" s="12">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="6">
-        <v>408</v>
-      </c>
-      <c r="B254" t="s" s="7">
-        <v>691</v>
-      </c>
-      <c r="D254" s="9">
-        <v>368</v>
-      </c>
-      <c r="E254" s="10">
-        <v>4</v>
-      </c>
-      <c r="F254" t="s" s="11">
-        <v>692</v>
-      </c>
-      <c r="G254" t="s" s="12">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="6">
-        <v>409</v>
-      </c>
-      <c r="B255" t="s" s="7">
-        <v>694</v>
-      </c>
-      <c r="D255" s="9">
-        <v>370</v>
-      </c>
-      <c r="E255" s="10">
-        <v>4</v>
-      </c>
-      <c r="F255" t="s" s="11">
-        <v>374</v>
-      </c>
-      <c r="G255" t="s" s="12">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="6">
-        <v>412</v>
-      </c>
-      <c r="B256" t="s" s="7">
-        <v>696</v>
-      </c>
-      <c r="D256" s="9">
-        <v>372</v>
-      </c>
-      <c r="E256" s="10">
-        <v>4</v>
-      </c>
-      <c r="F256" t="s" s="11">
-        <v>697</v>
-      </c>
-      <c r="G256" t="s" s="12">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="6">
-        <v>413</v>
-      </c>
-      <c r="B257" t="s" s="7">
-        <v>699</v>
-      </c>
-      <c r="D257" s="9">
-        <v>373</v>
-      </c>
-      <c r="E257" s="10">
-        <v>4</v>
-      </c>
-      <c r="F257" t="s" s="11">
-        <v>700</v>
-      </c>
-      <c r="G257" t="s" s="12">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="6">
-        <v>417</v>
-      </c>
-      <c r="B258" t="s" s="7">
-        <v>702</v>
-      </c>
-      <c r="D258" s="9">
-        <v>375</v>
-      </c>
-      <c r="E258" s="10">
-        <v>3</v>
-      </c>
-      <c r="F258" t="s" s="11">
-        <v>703</v>
-      </c>
-      <c r="G258" t="s" s="12">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="6">
-        <v>418</v>
-      </c>
-      <c r="B259" t="s" s="7">
-        <v>705</v>
-      </c>
-      <c r="D259" s="9">
-        <v>225</v>
-      </c>
-      <c r="E259" s="10">
-        <v>1</v>
-      </c>
-      <c r="F259" t="s" s="11">
-        <v>706</v>
-      </c>
-      <c r="G259" t="s" s="12">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="6">
-        <v>419</v>
-      </c>
-      <c r="B260" t="s" s="7">
-        <v>708</v>
-      </c>
-      <c r="D260" s="9">
-        <v>225</v>
-      </c>
-      <c r="E260" s="10">
-        <v>1</v>
-      </c>
-      <c r="F260" t="s" s="11">
-        <v>706</v>
-      </c>
-      <c r="G260" t="s" s="12">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="6">
-        <v>420</v>
-      </c>
-      <c r="B261" t="s" s="7">
-        <v>710</v>
-      </c>
-      <c r="D261" s="9">
-        <v>225</v>
-      </c>
-      <c r="E261" s="10">
-        <v>1</v>
-      </c>
-      <c r="F261" t="s" s="11">
-        <v>706</v>
-      </c>
-      <c r="G261" t="s" s="12">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="6">
-        <v>421</v>
-      </c>
-      <c r="B262" t="s" s="7">
-        <v>712</v>
-      </c>
-      <c r="C262" t="s" s="8">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="6">
-        <v>436</v>
-      </c>
-      <c r="B263" t="s" s="7">
-        <v>714</v>
-      </c>
-      <c r="D263" s="9">
-        <v>376</v>
-      </c>
-      <c r="E263" s="10">
-        <v>3</v>
-      </c>
-      <c r="F263" t="s" s="11">
-        <v>715</v>
-      </c>
-      <c r="G263" t="s" s="12">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="6">
-        <v>437</v>
-      </c>
-      <c r="B264" t="s" s="7">
-        <v>717</v>
-      </c>
-      <c r="D264" s="9">
-        <v>377</v>
-      </c>
-      <c r="E264" s="10">
-        <v>3</v>
-      </c>
-      <c r="F264" t="s" s="11">
-        <v>715</v>
-      </c>
-      <c r="G264" t="s" s="12">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="6">
-        <v>438</v>
-      </c>
-      <c r="B265" t="s" s="7">
-        <v>719</v>
-      </c>
-      <c r="D265" s="9">
-        <v>378</v>
-      </c>
-      <c r="E265" s="10">
-        <v>3</v>
-      </c>
-      <c r="F265" t="s" s="11">
-        <v>715</v>
-      </c>
-      <c r="G265" t="s" s="12">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="6">
-        <v>440</v>
-      </c>
-      <c r="B266" t="s" s="7">
-        <v>721</v>
-      </c>
-      <c r="D266" s="9">
-        <v>379</v>
-      </c>
-      <c r="E266" s="10">
-        <v>1</v>
-      </c>
-      <c r="F266" t="s" s="11">
-        <v>419</v>
-      </c>
-      <c r="G266" t="s" s="12">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="6">
-        <v>441</v>
-      </c>
-      <c r="B267" t="s" s="7">
-        <v>723</v>
-      </c>
-      <c r="D267" s="9">
-        <v>380</v>
-      </c>
-      <c r="E267" s="10">
-        <v>1</v>
-      </c>
-      <c r="F267" t="s" s="11">
-        <v>438</v>
-      </c>
-      <c r="G267" t="s" s="12">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="6">
-        <v>442</v>
-      </c>
-      <c r="B268" t="s" s="7">
-        <v>725</v>
-      </c>
-      <c r="D268" s="9">
-        <v>314</v>
-      </c>
-      <c r="E268" s="10">
-        <v>4</v>
-      </c>
-      <c r="F268" t="s" s="11">
-        <v>726</v>
-      </c>
-      <c r="G268" t="s" s="12">
-        <v>727</v>
       </c>
     </row>
   </sheetData>

--- a/raw/Features.xlsx
+++ b/raw/Features.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="1952">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="1997">
   <si>
     <t>feature_ID</t>
   </si>
@@ -3857,15 +3857,24 @@
     <t>Imperative-hortative systems</t>
   </si>
   <si>
+    <t>(By Johan van der Auwera, Nina Dobrushina, and Valentin Goussev): "Imperatives and hortatives both have to do with the expression of a wish of the speaker about a future state of affairs. In this respect they are like optatives (see Chapter 73), but in contrast to optatives, they convey an appeal to the addressee(s) to help make the future state of affairs true. In case the person in control of the desired state of affairs is the addressee or addressees, then we speak of an imperative. In any other case, we speak of a hortative."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/72A</t>
   </si>
   <si>
     <t>72A</t>
   </si>
   <si>
+    <t>Here the term "imperative" is restricted to 2nd person forms, whereas in the Grammaticon, "imperative" is used broadly to encompass all persons, i.e. including jussive and hortative forms.</t>
+  </si>
+  <si>
     <t>The optative</t>
   </si>
   <si>
+    <t>(By Nina Dobrushina and Johan van der Auwera): "In this chapter, the term optative will refer to an inflected verb form dedicated to the expression of the wish of the speaker... This usage of the label optative is rather uncontroversial ..., but other terms are also found in descriptive grammars. The speaker’s wish can be expressed by different grammatical means across languages, for instance, by the use of modal verbs, such as English _may_ in (2), or by a Russian elliptical conditional in (3)..."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/73A</t>
   </si>
   <si>
@@ -3875,6 +3884,10 @@
     <t>Situational possibility</t>
   </si>
   <si>
+    <t>(By Johan van der Auwera and Andreas Ammann): "In this chapter, we will examine the expression of the equivalents of English may  and can  as in (1): (1) a. The children can swim across the lake. b. You may leave now. c. One can get to Staten Island using the ferry. In (1a) can  expresses ability and in (1b) may  expresses permission. Both permission and ability have to do with a notion of possibility. These two kinds of possibility belong to a subtype which also includes readings like can  in (1c), where neither an individual’s ability nor an authority granting permission is involved. What the three examples have in common is that the speaker merely describes a possibility that exists in a given situation. For this reason we call this subtype situational  (also termed “deontic” or “root” in the literature). It is different from the kind of possibility illustrated in (2). (2) John may have arrived. In (2) the possibility concerns the speaker’s evaluation of the truth-value of a proposition about a situation, that is, it expresses a degree of the speaker’s certainty. This kind of possibility is commonly called epistemic (see Chapter 75). ❡
+Possibility stands in direct contrast with necessity, and together they constitute the domain of modality. Just as there are two types of possibility, there are two types of necessity, a situational one, as in (3a), and an epistemic one, as in (3b)..."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/74A</t>
   </si>
   <si>
@@ -3884,6 +3897,9 @@
     <t>Epistemic possibility</t>
   </si>
   <si>
+    <t>(By Johan van der Auwera and Andreas Ammann): "This chapter deals with the kind of modality expressed by English _may_ in (1): (1) John may have arrived. In (1) may  indicates that the speaker holds that the proposition that John has arrived is not certain, relative to what he knows or to his evidence. It contrasts with the statement in (2). (2) John must have arrived. In (2) the speaker indicates that the proposition that John has arrived is certain, again relative to what he knows or to his evidence. This type of modality is commonly called epistemic, and it is distinguished from what we call situational modality.."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/75A</t>
   </si>
   <si>
@@ -3893,6 +3909,11 @@
     <t>Overlap between situational and epistemic modal marking</t>
   </si>
   <si>
+    <t>(By Johan van der Auwera and Andreas Ammann): "Modality is a dimension of meaning that crucially involves notions of possibility and necessity. These may relate to circumstances that allow or necessitate a situation, as in (1)... We call this type of modality situational (see Chapter 74). ❡
+Situational modality is distinguished from epistemic modality, ... (see Chapter 75)... In these instances of epistemic possibility (2a) and necessity (2b), the speaker asserts that a proposition is possibly or necessarily true, relative to some information or knowledge. If the proposition is only possibly true, the propositional attitude is that of uncertainty; if it is necessarily true, the propositional attitude is that of a high degree of certainty. Note that the English modals may  and must  can be used both for situational and for epistemic modality. ❡
+This chapter documents to what extent languages have identical markers for situational and epistemic modality. Three types will be distinguished."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/76A</t>
   </si>
   <si>
@@ -3902,6 +3923,9 @@
     <t>Semantic distinctions of evidentiality</t>
   </si>
   <si>
+    <t>(By Ferdinand de Haan): "Markers of evidentiality express the evidence a speaker has for his/her statement. For the purposes of this map and the following one, evidentiality is divided into two broad sub-categories, direct evidence and indirect evidence. Only grammaticalized evidentials have been included in this study; this excludes lexical adverbs, such as reportedly  in John is reportedly ill, and biclausal constructions, such as It is said that John is ill. Auxiliary verbs and particles have been included. Also, a distinction is made between evidentiality, which is used only for the evidence for the statement, and epistemic modality, which marks the speaker’s degree of confidence in the statement (see Chapter 75). Although it is possible for evidentials to develop from epistemic modals (see Chapter 78), this is not common."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/77A</t>
   </si>
   <si>
@@ -3911,12 +3935,18 @@
     <t>Coding of evidentiality</t>
   </si>
   <si>
+    <t>(By Ferdinand de Haan): "This chapter discusses the morphological coding of evidentiality, which marks the source of information the speaker has for his or her statement. This chapter complements Chapter 77, which deals with the semantic distinctions of evidentiality. As was the case in the previous chapter, only grammaticalized evidentials are included here."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/78A</t>
   </si>
   <si>
     <t>78A</t>
   </si>
   <si>
+    <t>(By Ljuba N. Veselinova): "The maps in this and the following chapter show the distribution of suppletion in verb paradigms according to tense-aspect, imperative and hortative moods, and verbal number. Suppletion is defined as the phenomenon whereby regular semantic relations are encoded by unpredictable formal patterns. Cases where the paradigmatically related forms share some phonological material are examples of weak suppletion, as in English buy vs. bought, while cases with no shared phonological material are instances of strong suppletion, as in English go vs. went (Dressler 1985). These types reflect two ends of a continuum rather than an either-or opposition. Mel’čuk (1994) also introduces the criterion of uniqueness, i.e. in order to be classified as suppletive, the alternation shown between two paradigmatically related forms should be unique, in that no other two forms in the language show exactly the same morphophonological alternation, as in Spanish digo ‘say.pres.1.sg’ vs. dije ‘say.pret.1.sg’. The maps concentrate on strong and unique cases."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/79A</t>
   </si>
   <si>
@@ -3926,6 +3956,9 @@
     <t>Verbal number and suppletion</t>
   </si>
   <si>
+    <t>(By Ljuba N. Veselinova): "This chapter shows the distribution of suppletion according to verbal number. The term verbal number requires some clarification: number as a verbal category can reflect the number of times an action is done or the number of participants in the action. When we say that a verb or verb phrase in an Indo-European language, say French, is in the plural, as in ils étaient fatigués  ('they were tired'), what we mean is that the verb phrase étaient fatigués  agrees with the subject ils  in number. The term plural verbs (or pluractional verbs) in many of the languages to be discussed below, on the other hand, refers to any or all of the following senses: the action is performed several times (iterative), or at several places (distributive), or the action affects or involves several participants."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/80A</t>
   </si>
   <si>
@@ -3935,6 +3968,9 @@
     <t>Order of object and verb</t>
   </si>
   <si>
+    <t>(By Matthew S. Dryer): "This map shows the dominant order of lexical (nonpronominal) object and verb. As with Map 81A, the notion of object is defined semantically, as the P or most patient-like argument (see discussion under Map 81A) in a transitive clause. The primary types shown are languages which are OV (in which the object precedes the verb), illustrated by Turkish in (1a), and languages which are VO (in which the verb precedes the object), illustrated in (1b) by Gulf Arabic..."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/83A</t>
   </si>
   <si>
@@ -3944,12 +3980,23 @@
     <t>Order of object, oblique, and verb</t>
   </si>
   <si>
+    <t>(By Matthew S. Dryer): "This map shows the dominant order of lexical object, oblique phrase and verb. An oblique phrase is a noun phrase or adpositional phrase (prepositional or postpositional) that functions as an adverbial modifier (or “adjunct”) of the verb. Of the six logically possible orders, five are attested...❡
+Oblique phrases include phrases expressing location (such as source and goal), instruments (as in (1a)), benefactives (as in (1c)), and comitatives (as in English with Pat  in I played tennis with Pat ). Indirect objects (recipients with ditransitive verbs) are not included; in some languages they pattern with the direct object, in others with obliques. Temporal expressions are not included, since in many languages they exhibit positional properties different from other obliques, often occurring at the beginning of the clause."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/84A</t>
   </si>
   <si>
     <t>84A</t>
   </si>
   <si>
+    <t>In the Grammaticon, "oblique" is defined as flagged differently from S-/A-/P-arguments, so recipient nominals are oblique if they are dative-flagged. There are no semantic-role limitations on the notion of "oblique", in contrast to this WALS chapter.</t>
+  </si>
+  <si>
+    <t>(By Matthew S. Dryer): "This map shows the order of adposition and noun phrase.  The two primary types of adpositions are prepositions and postpositions: prepositions precede the noun phrase they occur with, as in English and in the Boumaa Fijian (Austronesian) example in (1a), while postpositions follow the noun phrase they occur with, as in the Lezgian (Nakh-Daghestanian; Russia) example in (1b)...❡
+A word is treated here as an adposition (preposition or postposition) if it combines with a noun phrase and indicates the grammatical or semantic relationship of that noun phrase to the verb in the clause. Some languages also employ adpositions to indicate a relationship of a noun phrase to a noun (especially in a genitive/possessive relationship); however, if the only candidates in a language for adpositions are in the genitive construction, they are not treated as adpositions here."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/85A</t>
   </si>
   <si>
@@ -3959,18 +4006,27 @@
     <t>Order of genitive and noun</t>
   </si>
   <si>
+    <t>(By Matthew S. Dryer): "This map shows the order of a genitive or possessor noun phrase with respect to the head noun... The genitive noun phrase is often called the possessor (phrase) and the head noun is sometimes called the possessee (noun), and the construction itself is known either as a genitive construction  or as a possessive construction. It should be stressed that the term possession  is used in this context in a broader sense than the term is used in everyday English. Two basic semantic types of genitive relations involve body parts and kinship relations, as illustrated by the French examples in (3)..."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/86A</t>
   </si>
   <si>
     <t>86A</t>
   </si>
   <si>
+    <t>(By Matthew S. Dryer): "This map shows the distribution of the two possible orders of modifying adjective and noun... For the purposes of this map, the term adjective  should be interpreted in a semantic sense, as a word denoting a descriptive property, with meanings such as ‘big’, ‘good’, or ‘red’. It does not include nondescriptive words that commonly modify nouns, such as demonstratives (like this  in this dog ) (see Map 88A), numerals (as in two dogs ) (see Map 89A), or words meaning ‘other’ (as in the other dog ). In some languages, like English, adjectives form a distinct word class. In other languages, however, adjectives do not form a distinct word class and are verbs or nouns (see Chapter 118). For example, in Eastern Ojibwa (Algonquian; eastern Canada and United States), words expressing adjectival meaning are just like verbs morphologically and syntactically..."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/87A</t>
   </si>
   <si>
     <t>87A</t>
   </si>
   <si>
+    <t>(By Matthew S. Dryer): "This map shows the different orders of demonstrative and noun. For the purposes of this map, a word or affix is considered a demonstrative if it satisfies at least one of two criteria: (1) it has among its uses a meaning that contrasts with some other form in terms of physical proximity to the speaker, so that there is at least a two-way contrast of proximal (near speaker) versus distal (not near speaker); or (2) the form has among its uses an indication that the hearer is intended to direct their attention towards something in the physical environment. In many and probably most languages, demonstratives are associated with both of these functions. The words this  and that  (and their plural forms these  and those ) constitute the demonstratives of English. In many languages, including English, the demonstratives can be used without a difference in form, either as modifiers of nouns, as in (1a), or pronominally (not modifying a noun), as in (1b)."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/88A</t>
   </si>
   <si>
@@ -3980,18 +4036,32 @@
     <t>Order of numeral and noun</t>
   </si>
   <si>
+    <t>(By Matthew S. Dryer): "This map shows the order of cardinal numerals with respect to a noun they modify. Cardinal numerals are words denoting the number of things referred to, as in English four chairs, in contrast to ordinal numerals, which specify the rank in some order of objects, as in English the fourth chair. See also Map 131A on numeral bases and Map 53A on ordinal numerals."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/89A</t>
   </si>
   <si>
     <t>89A</t>
   </si>
   <si>
+    <t xml:space="preserve">(By Matthew S. Dryer): "Map 90A shows the order of relative clause and noun. A construction is considered a relative clause for the purposes of this map if it is a clause which, either alone or in combination with a noun, denotes something and if the thing denoted has a semantic role within the relative clause. If there is a noun inside or outside the relative clause that denotes the thing also denoted by the clause, that noun will be referred to as the head of the relative clause. Headless relative clauses (like English what I bought at the store ) are not relevant to this map. ❡
+The two basic types shown on Map 90A are languages in which the relative clause follows the noun, and languages in which the relative clause precedes the noun...❡
+The relative clauses illustrated in (1) and (2) occur with heads outside the relative clause; these can be referred to as externally-headed relative clauses. In some languages, the head is inside the relative clause; these can be called internally-headed relative clauses. These are illustrated by the examples in (3) from Mesa Grande Diegueño (Yuman; southern California and northwest Mexico); the fact that the head is inside the relative clause is clearest in (3a), in which the head (gaat  ‘cat’) occurs between the subject and verb of the relative clause.❡
+The fourth type shown on the map is correlative relative clauses... Correlative clauses are strictly speaking a subtype of internally-headed relative clauses in that the head noun occurs inside the clause, but they differ from those coded here as internally-headed in that the relative clause is outside the main clause and is connected anaphorically to a noun phrase in the main clause that corresponds to the head noun in the English translations. ❡
+The fifth type shown on the map consists of languages with adjoined relative clauses. As with the preceding type, adjoined relative clauses are outside the main clause; they do not form a constituent with the head noun, which is in the main clause, and they may be separated from it. However, unlike correlative clauses, the head occurs in the main clause rather than in the relative clause..."
+</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/90A</t>
   </si>
   <si>
     <t>90A</t>
   </si>
   <si>
+    <t>(By Matthew S. Dryer): "This map shows the position of degree words with respect to the adjective that they modify. For the purposes of this map, the term adjective  should be interpreted in a purely semantic sense, as a word denoting a property, since in many languages the words in question do not form a separate word class, but are verbs or nouns. Degree words are words with meanings like ‘very’, ‘more’, or ‘a little’ that modify the adjective to indicate the degree to which the property denoted by the adjective obtains. Degree words are traditionally referred to as adverbs, though in many languages the degree words do not belong to the same word class as adverbs; even for English there is little basis for saying that degree words belong to the same word class as adverbs which modify verbs."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/91A</t>
   </si>
   <si>
@@ -4001,12 +4071,18 @@
     <t>Position of polar question particles</t>
   </si>
   <si>
+    <t>(By Matthew S. Dryer): "This map shows the position of question particles in polar questions. Polar questions are ones that elicit the equivalent of a ‘yes’ or ‘no’ response. This map does not include interrogative affixes on verbs, although it should be noted that the distinction between interrogative affixes and separate interrogative particles is often hard to make. The map treats interrogative clitics that can attach to words of different categories as question particles."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/92A</t>
   </si>
   <si>
     <t>92A</t>
   </si>
   <si>
+    <t>(By Matthew S. Dryer): "This map shows the position of interrogative phrases in content questions. Content questions are questions that contain an interrogative phrase, like the elements in boldface in the English examples in (1)... Content questions differ from polar questions (see Maps 92A and 116A) in that they elicit a specific answer other than ‘yes’ or ‘no’, and in containing interrogative phrases. All languages have a set of interrogative words that are characteristic of content questions, though in many languages they are identical in form to indefinite words (like someone  in English) (see Map 46A). These interrogative words typically belong to different categories (interrogative pronouns, interrogative adverbs, “interrogative adjectives”, “interrogative verbs”). Because most interrogative words in English begin with wh-, content questions in English are often called wh-questions. Although interrogative phrases often consist of single words (interrogative pronouns or interrogative adverbs), they may contain additional words, as in _which book_ in (1b)."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/93A</t>
   </si>
   <si>
@@ -4016,12 +4092,18 @@
     <t>Order of adverbial subordinator and clause</t>
   </si>
   <si>
+    <t>(By Matthew S. Dryer): "This map shows the position of adverbial subordinators, morphemes which mark adverbial clauses for their semantic relationship to the main clause. Adverbial subordinators which are separate words are referred to as subordinating conjunctions  by traditional grammar. Examples of adverbial subordinators in English include because, although, when, while, and if. The map further distinguishes adverbial subordinators which are separate words from ones which are affixes on verbs."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/94A</t>
   </si>
   <si>
     <t>94A</t>
   </si>
   <si>
+    <t>(By Bernard Comrie): "The core argument of a canonical, one-place intransitive predicate may be symbolized S. The two core arguments of a canonical, two-place transitive predicate may be symbolized as A and P, with A representing the more agent-like argument and P the more patient-like (Comrie 1978). (In another terminology, the symbol O is used rather than P; Dixon 1994.) In studying the alignment of case marking, we ask the question which of S, A, and P are coded identically and which are coded differently. Note that for the purposes of this chapter, only case marking is considered. Alignment of person marking in the verb is treated in Chapter 100. Other manifestations of alignment are also possible, such as word order, but are not treated here."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/98A</t>
   </si>
   <si>
@@ -4031,6 +4113,10 @@
     <t>Alignment of case marking of pronouns</t>
   </si>
   <si>
+    <t>(By Bernard Comrie): "The core argument of a canonical, one-place intransitive predicate may be symbolized S. The two core arguments of a canonical, two-place transitive predicate may be symbolized as A and P, with A representing the more agent-like argument and P the more patient-like (Comrie 1978). (In another terminology, the symbol O is used rather than P; Dixon 1994.) In studying the alignment of case marking, we ask the question which of S, A, and P are coded identically and which are coded differently. Note that for the purposes of this chapter, only case marking is considered. Alignment of person marking in the verb is treated in Chapter 100. Other manifestations of alignment are also possible, such as word order, but are not treated here. ❡
+Pronouns merit a separate map from full noun phrases because in many languages pronouns have a different case marking system from full noun phrases — 23 languages in the sample used for these Chapters (25 if the marked nominative system is considered distinct from the rest of nominative–accusative). In English, for instance, while full noun phrases have a neutral case marking system, pronouns have a nominative–accusative system, e.g. with we  for S and A but us  for P. Some of the problems discussed in §2 apply also in the case of personal pronouns, and in such instances similar solutions are applied, with one additional criterion, namely the assignment of some weight to differentiating pronouns from full noun phrases. Thus, in English some pronouns have a nominative–accusative system, while others (in particular, second person you ) do not; the nominative–accusative system is selected here in part because it differs from the case marking system for full noun phrases. Sometimes the problems that occur with full noun phrases occur with somewhat less force in the case of pronouns; for instance, several languages where full noun phrase Ps sometimes take an accusative marker and sometimes not require pronouns to take this marker (e.g. Persian), so that there is no hesitation in assigning them to the nominative–accusative type with respect to case marking of pronouns. However, pronouns bring with them a host of other problems that can lead to uncertainties in assigning languages to case marking alignment types with respect to their pronominal systems."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/99A</t>
   </si>
   <si>
@@ -4040,12 +4126,18 @@
     <t>Alignment of verbal person marking</t>
   </si>
   <si>
+    <t>(By Anna Siewierska): "Languages differ not only in regard to the number and nature of the arguments displaying verbal person marking (see Chapter 102), but also in the alignment of the person markers. The term alignment may be intuitively understood as reflecting how the two arguments of the transitive verb, the agentive argument (A) and the more patient-like argument (P), align with the sole argument of the intransitive verb, the S."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/100A</t>
   </si>
   <si>
     <t>100A</t>
   </si>
   <si>
+    <t>(By Matthew S. Dryer): "Across languages, we can distinguish two types of simple sentences differing in the nature of their subjects. One sort of simple sentence involves a nominal subject, a subject consisting of a noun, plus possibly some modifiers. The second sort of simple sentence involves a pronominal subject, where there is no nominal subject and where the subject is expressed at most by a morpheme or morphemes coding semantic or grammatical features of the subject, such as person, number, or gender."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/101A</t>
   </si>
   <si>
@@ -4055,6 +4147,9 @@
     <t>Verbal person marking</t>
   </si>
   <si>
+    <t>(By Anna Siewierska): "Map 102A depicts the number and identity of the arguments of a transitive clause which display person marking on the verb. “A” stands for the agentive argument and “P” for the patient argument. Five feature values are represented."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/102A</t>
   </si>
   <si>
@@ -4064,6 +4159,9 @@
     <t>Third person zero of verbal person marking</t>
   </si>
   <si>
+    <t>(By Anna Siewierska): "Map 103A represents the distribution of third person zeroes among verbal person markers of the sole argument of an intransitive clause (i.e. of the S argument). I have chosen to depict the person marking of the S rather than of either of the transitive arguments, as the verbal person markers of the latter are sometimes fused with each other (see Chapter 104), which makes it difficult to decide which one has a zero realization. The zero realization of third person S markers is captured by means of six values..."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/103A</t>
   </si>
   <si>
@@ -4073,33 +4171,55 @@
     <t>Order of person markers on the verb</t>
   </si>
   <si>
+    <t>(By Anna Siewierska): "Map 104A represents the order of A and P person markers on the verb relative to each other, where A stands for the person marker of the agentive argument of a transitive verb and P for the person marker of the patient argument of the transitive verb. Five values are represented..."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/104A</t>
   </si>
   <si>
     <t>104A</t>
   </si>
   <si>
+    <t>(By Elena Maslova and Vladimir P. Nedjalkov): "Map 106A displays different ways in which languages encode reciprocal situations, i.e. situations like ‘They love each other’. The reciprocal situation comprises at least two simple situations (e.g., She loves him and He loves her), so one way to encode such a situation is to combine expressions for two simple situations... Apparently, this strategy of encoding reciprocated situations is possible in all languages, although the extent to which such a pattern is conventionalized in grammar and common in actual discourse differs from language to language. However, most languages also have simple or complex reciprocal markers (verbal affixes, pronouns, particles, adverbs, etc.), which, if combined with a verb within one clause, signal that the clause describes a reciprocal situation and not just the situation denoted by this verb, without repeating the verb for each simple situation. For example, English has two pronominal reciprocal markers, each other and one another; and in Kolyma Yukaghir (eastern Siberia), there is one reciprocal marker which is prefixed to the verb stem..."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/106A</t>
   </si>
   <si>
     <t>106A</t>
   </si>
   <si>
+    <t>The WALS chapter uses "reciprocal" both for situations ("reciprocal situations", corresponding to the Grammaticon's "mutual situation") and for constructions. The Grammaticon reserves "reciprocal" for strategies.</t>
+  </si>
+  <si>
+    <t>(By Anna Siewierska): "A construction has been classified as passive if it displays the following five properties:
+(i) it contrasts with another constuction, the active; (ii) the subject of the active corresponds to a non-obligatory oblique phrase of the passive or is not overtly expressed; (iii) the subject of the passive, if there is one, corresponds to the direct object of the active; (iv) the construction is pragmatically restricted relative to the active; (v) the construction displays some special morphological marking of the verb. A prototypical example of the passive, as defined above, is given in (1b) from Swahili..."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/107A</t>
   </si>
   <si>
     <t>107A</t>
   </si>
   <si>
+    <t>As in the Grammaticon, Siewierska's definition of "passive construction" includes the requirement of verbal marking. So-called "unmarked passives" do not fall under the definition.</t>
+  </si>
+  <si>
     <t>Antipassive constructions</t>
   </si>
   <si>
+    <t>(By Maria Polinsky): "An antipassive construction is a derived detransitivized construction with a two-place predicate, related to a corresponding transitive construction whose predicate is the same lexical item. In the basic transitive construction, the patient-like argument is realized as a direct object; in the antipassive construction, that argument is either suppressed (left implicit) or realized as an oblique complement. The term antipassive (Silverstein 1972) was coined to indicate that the construction is a mirror image of the passive: in the passive, the suppressed or demoted argument is the agent-like argument, in the antipassive, the patient-like argument."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/108A</t>
   </si>
   <si>
     <t>108A</t>
   </si>
   <si>
+    <t>(By Maria Polinsky): "In an applicative construction, the number of object arguments selected by the predicate is increased by one with respect to the basic construction. For example, in Tukang Besi (Austronesian; Sulawesi, Indonesia), the verb ‘fetch’ takes one theme object in the basic construction (as shown in 1a), but with the applicative marker it takes two objects, theme and benefactive (as shown in 1b)..."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/109A</t>
   </si>
   <si>
@@ -4109,6 +4229,10 @@
     <t>Periphrastic causative constructions</t>
   </si>
   <si>
+    <t>(By Jae Jung Song): "The causative construction is a linguistic expression which denotes a complex situation consisting of two component events (Comrie 1989: 165-166; Song 2001: 256-259): (i) the causing event, in which the causer does or initiates something; and (ii) the caused event, in which the causee carries out an action, or undergoes a change of condition or state as a result of the causer’s action...❡
+Periphrastic causative constructions are causative expressions with the following three properties. First, the expression of the causer’s action (or the predicate of cause) and the expression of the causee’s action or change of condition or state (or the predicate of effect) must be in different clauses, as in (1). To put it differently, causative expressions, for the purposes of the map, must be biclausal. (The notion of biclausality being a continuum, however, the causative construction in one language (as in (5)) may be less biclausal than in another language (as in (1)); for further discussion, see Song 1996.)"</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/110A</t>
   </si>
   <si>
@@ -4118,6 +4242,10 @@
     <t>Nonperiphrastic causative constructions</t>
   </si>
   <si>
+    <t>(By Jae Jung Song): "The causative construction is a linguistic expression which denotes a complex situation consisting of two component events (Comrie 1989: 165-166; Song 2001: 256-259): (i) the causing event, in which the causer does or initiates something; and (ii) the caused event, in which the causee carries out an action, or undergoes a change of condition or state as a result of the causer’s action. ❡
+Nonperiphrastic causative constructions are causative expressions with the following three properties. First, the expression of the causer’s action (e.g. -ase in (1)) and the expression of effect (e.g. ik- in (1)) must both be contained in one and the same predicate, which may consist of one or more verbs (e.g. one verb ik-ase- in (1), or two verbs me ŋò in (6) below). To put it differently, such causative expressions must be monoclausal. Second, the causer noun phrase must occupy a grammatically more ‘prominent’ position (e.g. the subject in (1)) than the causee noun phrase (the object in (1)). Third, the expression of the causer’s action, be it an affix or a separate verb, should be without specific meaning. In (1), the expression of cause -ase, as opposed to the expression of effect ik-, lacks specific meaning; all that is expressed by -ase is the pure notion of causation."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/111A</t>
   </si>
   <si>
@@ -4127,6 +4255,9 @@
     <t>Negative morphemes</t>
   </si>
   <si>
+    <t>(By Matthew S. Dryer): "This map shows the nature of morphemes signalling clausal negation in declarative sentences. By clausal negation is meant the simple negation of an entire clause... Not considered here are noun phrase negation (No students were present), negative pronouns (Nobody came), or negative adverbs (She never eats pizza) (though see Map 115A on negative pronouns). The map is based on the expression of negation in declarative sentences; thus, where a language employs a distinct construction in imperative sentences, that construction is ignored here (see Map 71A)."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/112A</t>
   </si>
   <si>
@@ -4136,6 +4267,9 @@
     <t>Subtypes of asymmetric standard negation</t>
   </si>
   <si>
+    <t>(By Matti Miestamo): "The term standard negation refers to the basic way(s) a language has for negating declarative verbal main clauses. In symmetric negation affirmative and negative structures are identical except for the presence of the negative marker(s), whereas in asymmetric negation the structure of negatives differs from the structure of affirmatives in various other ways too. Structural differences, i.e. asymmetry, can be found either between the affirmative and negative constructions or between the paradigms that the affirmative and negative constructions form. These distinctions are defined and illustrated in connection with Map 113A, which shows the geographical distribution of symmetric and asymmetric standard negation."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/114A</t>
   </si>
   <si>
@@ -4145,6 +4279,10 @@
     <t>Symmetric and asymmetric standard negation</t>
   </si>
   <si>
+    <t>(By Matti Miestamo): "Standard negation can be defined as the basic way (or ways) a language has for negating declarative verbal main clauses. Negative constructions that fall outside standard negation include the negation of existential, copular or non-verbal clauses, the negation of subordinate clauses, and the negation of non-declarative clauses like imperatives (see Chapter 71). These negatives are not taken into account here, but it is of course possible that languages use their standard negation constructions for the negation of these clause types too. ❡
+This map shows how symmetric and asymmetric standard negation are distributed among the languages of the world. In symmetric negation the structure of the negative is identical to the structure of the affirmative, except for the presence of the negative marker(s). In asymmetric negation the structure of the negative differs from the structure of the affirmative in various other ways too, i.e. there is asymmetry between affirmation and negation. Affirmative and negative structures can be symmetric or asymmetric in two ways: there can be (a)symmetry either between the affirmative and negative constructions, or between the paradigms that the affirmative and negative constructions form. Symmetric negative constructions do not differ from the corresponding affirmative constructions in any other way than by the presence of the negative marker(s), whereas asymmetric negative constructions show structural differences in comparison to the corresponding affirmative constructions..."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/113A</t>
   </si>
   <si>
@@ -4154,16 +4292,32 @@
     <t>Negative indefinite pronouns and predicate negation</t>
   </si>
   <si>
+    <t>(By Martin Haspelmath): "Negative indefinite pronouns like 'nobody', 'nothing', 'nowhere' may or may not co-occur with the ordinary marker of predicate negation. A language where they always co-occur with predicate negation is Russian... A language where negative indefinites never co-occur with predicate negation is German. In (2a-b), use of the predicate negator nicht would render the sentences ungrammatical (*Niemand kam nicht; *Ich habe nichts nicht gesehen)..."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/115A</t>
   </si>
   <si>
     <t>115A</t>
   </si>
   <si>
+    <t>It must be noted that WALS's "negative indefinite pronoun" is NOT the same as the Grammaticon's "negindefinite pronoun".</t>
+  </si>
+  <si>
+    <t>This map shows the method a language uses to indicate that an utterance is a polar question. Polar questions are ones to which the expected answer is the equivalent of ‘yes’ or ‘no’ (and which are thus sometimes called yes-no questions ). They contrast with content questions, which contain an interrogative word meaning something like ‘who’ or ‘where’, in which some more specific answer is expected; content questions in English are often called wh-questions... ❡
+The first strategy for forming polar questions is the use of a question particle which is added to a corresponding declarative sentence to indicate that it is a question... Interrogative clitics, which attach to some word, but which exhibit freedom as to the category of word they attach to, are treated here as question particles.  ❡
+The second general strategy for signalling polar questions involves the use of distinct interrogative verbal morphology. Most commonly, the verbal morphology may involve an affix that specifically signals that the utterance is a question...  ❡
+The third type is languages that have both question particles and interrogative verb morphology, either as two separate constructions or occurring together in a single construction...  ❡
+A fourth but fairly uncommon way to signal that an utterance is a question is by using a different word order from that used in corresponding declarative sentences. This method is used in a number of European languages..."</t>
+  </si>
+  <si>
     <t>https://wals.info/feature/116A</t>
   </si>
   <si>
     <t>116A</t>
+  </si>
+  <si>
+    <t>(By Leon Stassen): "This map illustrates the areal distribution of the various encoding options for predicative possession. The data base for this map thus includes sentences in which ownership of a certain object (the possessed item) is predicated of a possessor, in a way that is illustrated by the English sentence John has a motorcycle. It should be noted that the scope of this map is restricted by several conditions. First, the map deals only with the encoding of predicative possession, as in John has a motorcycle; cases of adnominal possession (as in John’s motorcycle) are not dealt with. Secondly, within predicative possession it often matters whether the noun phrase that indicates the possessed item is indefinite or not. English is a language in which this parameter gives rise to two different encoding options (see 1a-b). For the purposes of this map, only constructions in which the possessed NP has an indefinite reading - i.e., only those constructions that are parallel to (1a) - have been taken into account."</t>
   </si>
   <si>
     <t>https://wals.info/feature/117A</t>
@@ -5810,7 +5964,7 @@
 </t>
   </si>
   <si>
-    <t>tentativity</t>
+    <t>see-tentativity</t>
   </si>
   <si>
     <t>Passive marker: ‘Give’</t>
@@ -13315,6 +13469,9 @@
       <c r="B307" t="s" s="7">
         <v>1221</v>
       </c>
+      <c r="C307" t="s" s="8">
+        <v>1222</v>
+      </c>
       <c r="D307" s="9">
         <v>28</v>
       </c>
@@ -13322,10 +13479,13 @@
         <v>3</v>
       </c>
       <c r="F307" t="s" s="11">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="G307" t="s" s="12">
-        <v>1223</v>
+        <v>1224</v>
+      </c>
+      <c r="H307" t="s" s="13">
+        <v>1225</v>
       </c>
     </row>
     <row r="308">
@@ -13333,7 +13493,10 @@
         <v>587</v>
       </c>
       <c r="B308" t="s" s="7">
-        <v>1224</v>
+        <v>1226</v>
+      </c>
+      <c r="C308" t="s" s="8">
+        <v>1227</v>
       </c>
       <c r="D308" s="9">
         <v>28</v>
@@ -13342,10 +13505,10 @@
         <v>3</v>
       </c>
       <c r="F308" t="s" s="11">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="G308" t="s" s="12">
-        <v>1226</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="309">
@@ -13353,7 +13516,10 @@
         <v>588</v>
       </c>
       <c r="B309" t="s" s="7">
-        <v>1227</v>
+        <v>1230</v>
+      </c>
+      <c r="C309" t="s" s="8">
+        <v>1231</v>
       </c>
       <c r="D309" s="9">
         <v>28</v>
@@ -13362,10 +13528,10 @@
         <v>3</v>
       </c>
       <c r="F309" t="s" s="11">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="G309" t="s" s="12">
-        <v>1229</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="310">
@@ -13373,7 +13539,10 @@
         <v>589</v>
       </c>
       <c r="B310" t="s" s="7">
-        <v>1230</v>
+        <v>1234</v>
+      </c>
+      <c r="C310" t="s" s="8">
+        <v>1235</v>
       </c>
       <c r="D310" s="9">
         <v>28</v>
@@ -13382,10 +13551,10 @@
         <v>3</v>
       </c>
       <c r="F310" t="s" s="11">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="G310" t="s" s="12">
-        <v>1232</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="311">
@@ -13393,7 +13562,10 @@
         <v>590</v>
       </c>
       <c r="B311" t="s" s="7">
-        <v>1233</v>
+        <v>1238</v>
+      </c>
+      <c r="C311" t="s" s="8">
+        <v>1239</v>
       </c>
       <c r="D311" s="9">
         <v>28</v>
@@ -13402,10 +13574,10 @@
         <v>3</v>
       </c>
       <c r="F311" t="s" s="11">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="G311" t="s" s="12">
-        <v>1235</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="312">
@@ -13413,7 +13585,10 @@
         <v>591</v>
       </c>
       <c r="B312" t="s" s="7">
-        <v>1236</v>
+        <v>1242</v>
+      </c>
+      <c r="C312" t="s" s="8">
+        <v>1243</v>
       </c>
       <c r="D312" s="9">
         <v>28</v>
@@ -13422,10 +13597,10 @@
         <v>3</v>
       </c>
       <c r="F312" t="s" s="11">
-        <v>1237</v>
+        <v>1244</v>
       </c>
       <c r="G312" t="s" s="12">
-        <v>1238</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="313">
@@ -13433,7 +13608,10 @@
         <v>592</v>
       </c>
       <c r="B313" t="s" s="7">
-        <v>1239</v>
+        <v>1246</v>
+      </c>
+      <c r="C313" t="s" s="8">
+        <v>1247</v>
       </c>
       <c r="D313" s="9">
         <v>28</v>
@@ -13442,10 +13620,10 @@
         <v>3</v>
       </c>
       <c r="F313" t="s" s="11">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="G313" t="s" s="12">
-        <v>1241</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="314">
@@ -13455,6 +13633,9 @@
       <c r="B314" t="s" s="7">
         <v>853</v>
       </c>
+      <c r="C314" t="s" s="8">
+        <v>1250</v>
+      </c>
       <c r="D314" s="9">
         <v>28</v>
       </c>
@@ -13462,10 +13643,10 @@
         <v>3</v>
       </c>
       <c r="F314" t="s" s="11">
-        <v>1242</v>
+        <v>1251</v>
       </c>
       <c r="G314" t="s" s="12">
-        <v>1243</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="315">
@@ -13473,7 +13654,10 @@
         <v>594</v>
       </c>
       <c r="B315" t="s" s="7">
-        <v>1244</v>
+        <v>1253</v>
+      </c>
+      <c r="C315" t="s" s="8">
+        <v>1254</v>
       </c>
       <c r="D315" s="9">
         <v>28</v>
@@ -13482,10 +13666,10 @@
         <v>3</v>
       </c>
       <c r="F315" t="s" s="11">
-        <v>1245</v>
+        <v>1255</v>
       </c>
       <c r="G315" t="s" s="12">
-        <v>1246</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="316">
@@ -13493,7 +13677,10 @@
         <v>595</v>
       </c>
       <c r="B316" t="s" s="7">
-        <v>1247</v>
+        <v>1257</v>
+      </c>
+      <c r="C316" t="s" s="8">
+        <v>1258</v>
       </c>
       <c r="D316" s="9">
         <v>376</v>
@@ -13502,10 +13689,10 @@
         <v>3</v>
       </c>
       <c r="F316" t="s" s="11">
-        <v>1248</v>
+        <v>1259</v>
       </c>
       <c r="G316" t="s" s="12">
-        <v>1249</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="317">
@@ -13513,7 +13700,10 @@
         <v>596</v>
       </c>
       <c r="B317" t="s" s="7">
-        <v>1250</v>
+        <v>1261</v>
+      </c>
+      <c r="C317" t="s" s="8">
+        <v>1262</v>
       </c>
       <c r="D317" s="9">
         <v>376</v>
@@ -13522,10 +13712,13 @@
         <v>3</v>
       </c>
       <c r="F317" t="s" s="11">
-        <v>1251</v>
+        <v>1263</v>
       </c>
       <c r="G317" t="s" s="12">
-        <v>1252</v>
+        <v>1264</v>
+      </c>
+      <c r="H317" t="s" s="13">
+        <v>1265</v>
       </c>
     </row>
     <row r="318">
@@ -13535,6 +13728,9 @@
       <c r="B318" t="s" s="7">
         <v>713</v>
       </c>
+      <c r="C318" t="s" s="8">
+        <v>1266</v>
+      </c>
       <c r="D318" s="9">
         <v>376</v>
       </c>
@@ -13542,10 +13738,10 @@
         <v>3</v>
       </c>
       <c r="F318" t="s" s="11">
-        <v>1253</v>
+        <v>1267</v>
       </c>
       <c r="G318" t="s" s="12">
-        <v>1254</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="319">
@@ -13553,7 +13749,10 @@
         <v>599</v>
       </c>
       <c r="B319" t="s" s="7">
-        <v>1255</v>
+        <v>1269</v>
+      </c>
+      <c r="C319" t="s" s="8">
+        <v>1270</v>
       </c>
       <c r="D319" s="9">
         <v>376</v>
@@ -13562,10 +13761,10 @@
         <v>3</v>
       </c>
       <c r="F319" t="s" s="11">
-        <v>1256</v>
+        <v>1271</v>
       </c>
       <c r="G319" t="s" s="12">
-        <v>1257</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="320">
@@ -13575,6 +13774,9 @@
       <c r="B320" t="s" s="7">
         <v>705</v>
       </c>
+      <c r="C320" t="s" s="8">
+        <v>1273</v>
+      </c>
       <c r="D320" s="9">
         <v>376</v>
       </c>
@@ -13582,10 +13784,10 @@
         <v>3</v>
       </c>
       <c r="F320" t="s" s="11">
-        <v>1258</v>
+        <v>1274</v>
       </c>
       <c r="G320" t="s" s="12">
-        <v>1259</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="321">
@@ -13595,6 +13797,9 @@
       <c r="B321" t="s" s="7">
         <v>717</v>
       </c>
+      <c r="C321" t="s" s="8">
+        <v>1276</v>
+      </c>
       <c r="D321" s="9">
         <v>376</v>
       </c>
@@ -13602,10 +13807,10 @@
         <v>3</v>
       </c>
       <c r="F321" t="s" s="11">
-        <v>1260</v>
+        <v>1277</v>
       </c>
       <c r="G321" t="s" s="12">
-        <v>1261</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="322">
@@ -13613,7 +13818,10 @@
         <v>602</v>
       </c>
       <c r="B322" t="s" s="7">
-        <v>1262</v>
+        <v>1279</v>
+      </c>
+      <c r="C322" t="s" s="8">
+        <v>1280</v>
       </c>
       <c r="D322" s="9">
         <v>376</v>
@@ -13622,10 +13830,10 @@
         <v>3</v>
       </c>
       <c r="F322" t="s" s="11">
-        <v>1263</v>
+        <v>1281</v>
       </c>
       <c r="G322" t="s" s="12">
-        <v>1264</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="323">
@@ -13635,6 +13843,9 @@
       <c r="B323" t="s" s="7">
         <v>725</v>
       </c>
+      <c r="C323" t="s" s="8">
+        <v>1283</v>
+      </c>
       <c r="D323" s="9">
         <v>376</v>
       </c>
@@ -13642,10 +13853,10 @@
         <v>3</v>
       </c>
       <c r="F323" t="s" s="11">
-        <v>1265</v>
+        <v>1284</v>
       </c>
       <c r="G323" t="s" s="12">
-        <v>1266</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="324">
@@ -13655,6 +13866,9 @@
       <c r="B324" t="s" s="7">
         <v>729</v>
       </c>
+      <c r="C324" t="s" s="8">
+        <v>1286</v>
+      </c>
       <c r="D324" s="9">
         <v>376</v>
       </c>
@@ -13662,10 +13876,10 @@
         <v>3</v>
       </c>
       <c r="F324" t="s" s="11">
-        <v>1267</v>
+        <v>1287</v>
       </c>
       <c r="G324" t="s" s="12">
-        <v>1268</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="325">
@@ -13673,7 +13887,10 @@
         <v>605</v>
       </c>
       <c r="B325" t="s" s="7">
-        <v>1269</v>
+        <v>1289</v>
+      </c>
+      <c r="C325" t="s" s="8">
+        <v>1290</v>
       </c>
       <c r="D325" s="9">
         <v>376</v>
@@ -13682,10 +13899,10 @@
         <v>3</v>
       </c>
       <c r="F325" t="s" s="11">
-        <v>1270</v>
+        <v>1291</v>
       </c>
       <c r="G325" t="s" s="12">
-        <v>1271</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="326">
@@ -13695,6 +13912,9 @@
       <c r="B326" t="s" s="7">
         <v>745</v>
       </c>
+      <c r="C326" t="s" s="8">
+        <v>1293</v>
+      </c>
       <c r="D326" s="9">
         <v>376</v>
       </c>
@@ -13702,10 +13922,10 @@
         <v>3</v>
       </c>
       <c r="F326" t="s" s="11">
-        <v>1272</v>
+        <v>1294</v>
       </c>
       <c r="G326" t="s" s="12">
-        <v>1273</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="327">
@@ -13713,7 +13933,10 @@
         <v>607</v>
       </c>
       <c r="B327" t="s" s="7">
-        <v>1274</v>
+        <v>1296</v>
+      </c>
+      <c r="C327" t="s" s="8">
+        <v>1297</v>
       </c>
       <c r="D327" s="9">
         <v>376</v>
@@ -13722,10 +13945,10 @@
         <v>3</v>
       </c>
       <c r="F327" t="s" s="11">
-        <v>1275</v>
+        <v>1298</v>
       </c>
       <c r="G327" t="s" s="12">
-        <v>1276</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="328">
@@ -13735,6 +13958,9 @@
       <c r="B328" t="s" s="7">
         <v>865</v>
       </c>
+      <c r="C328" t="s" s="8">
+        <v>1300</v>
+      </c>
       <c r="D328" s="9">
         <v>376</v>
       </c>
@@ -13742,10 +13968,10 @@
         <v>3</v>
       </c>
       <c r="F328" t="s" s="11">
-        <v>1277</v>
+        <v>1301</v>
       </c>
       <c r="G328" t="s" s="12">
-        <v>1278</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="329">
@@ -13753,7 +13979,10 @@
         <v>610</v>
       </c>
       <c r="B329" t="s" s="7">
-        <v>1279</v>
+        <v>1303</v>
+      </c>
+      <c r="C329" t="s" s="8">
+        <v>1304</v>
       </c>
       <c r="D329" s="9">
         <v>376</v>
@@ -13762,10 +13991,10 @@
         <v>3</v>
       </c>
       <c r="F329" t="s" s="11">
-        <v>1280</v>
+        <v>1305</v>
       </c>
       <c r="G329" t="s" s="12">
-        <v>1281</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="330">
@@ -13773,7 +14002,10 @@
         <v>611</v>
       </c>
       <c r="B330" t="s" s="7">
-        <v>1282</v>
+        <v>1307</v>
+      </c>
+      <c r="C330" t="s" s="8">
+        <v>1308</v>
       </c>
       <c r="D330" s="9">
         <v>376</v>
@@ -13782,10 +14014,10 @@
         <v>3</v>
       </c>
       <c r="F330" t="s" s="11">
-        <v>1283</v>
+        <v>1309</v>
       </c>
       <c r="G330" t="s" s="12">
-        <v>1284</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="331">
@@ -13795,6 +14027,9 @@
       <c r="B331" t="s" s="7">
         <v>881</v>
       </c>
+      <c r="C331" t="s" s="8">
+        <v>1311</v>
+      </c>
       <c r="D331" s="9">
         <v>376</v>
       </c>
@@ -13802,10 +14037,10 @@
         <v>3</v>
       </c>
       <c r="F331" t="s" s="11">
-        <v>1285</v>
+        <v>1312</v>
       </c>
       <c r="G331" t="s" s="12">
-        <v>1286</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="332">
@@ -13813,7 +14048,10 @@
         <v>613</v>
       </c>
       <c r="B332" t="s" s="7">
-        <v>1287</v>
+        <v>1314</v>
+      </c>
+      <c r="C332" t="s" s="8">
+        <v>1315</v>
       </c>
       <c r="D332" s="9">
         <v>376</v>
@@ -13822,10 +14060,10 @@
         <v>3</v>
       </c>
       <c r="F332" t="s" s="11">
-        <v>1288</v>
+        <v>1316</v>
       </c>
       <c r="G332" t="s" s="12">
-        <v>1289</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="333">
@@ -13833,7 +14071,10 @@
         <v>614</v>
       </c>
       <c r="B333" t="s" s="7">
-        <v>1290</v>
+        <v>1318</v>
+      </c>
+      <c r="C333" t="s" s="8">
+        <v>1319</v>
       </c>
       <c r="D333" s="9">
         <v>376</v>
@@ -13842,10 +14083,10 @@
         <v>3</v>
       </c>
       <c r="F333" t="s" s="11">
-        <v>1291</v>
+        <v>1320</v>
       </c>
       <c r="G333" t="s" s="12">
-        <v>1292</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="334">
@@ -13853,7 +14094,10 @@
         <v>615</v>
       </c>
       <c r="B334" t="s" s="7">
-        <v>1293</v>
+        <v>1322</v>
+      </c>
+      <c r="C334" t="s" s="8">
+        <v>1323</v>
       </c>
       <c r="D334" s="9">
         <v>376</v>
@@ -13862,10 +14106,10 @@
         <v>3</v>
       </c>
       <c r="F334" t="s" s="11">
-        <v>1294</v>
+        <v>1324</v>
       </c>
       <c r="G334" t="s" s="12">
-        <v>1295</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="335">
@@ -13875,6 +14119,9 @@
       <c r="B335" t="s" s="7">
         <v>1058</v>
       </c>
+      <c r="C335" t="s" s="8">
+        <v>1326</v>
+      </c>
       <c r="D335" s="9">
         <v>81</v>
       </c>
@@ -13882,10 +14129,13 @@
         <v>3</v>
       </c>
       <c r="F335" t="s" s="11">
-        <v>1296</v>
+        <v>1327</v>
       </c>
       <c r="G335" t="s" s="12">
-        <v>1297</v>
+        <v>1328</v>
+      </c>
+      <c r="H335" t="s" s="13">
+        <v>1329</v>
       </c>
     </row>
     <row r="336">
@@ -13895,6 +14145,9 @@
       <c r="B336" t="s" s="7">
         <v>1062</v>
       </c>
+      <c r="C336" t="s" s="8">
+        <v>1330</v>
+      </c>
       <c r="D336" s="9">
         <v>81</v>
       </c>
@@ -13902,10 +14155,13 @@
         <v>3</v>
       </c>
       <c r="F336" t="s" s="11">
-        <v>1298</v>
+        <v>1331</v>
       </c>
       <c r="G336" t="s" s="12">
-        <v>1299</v>
+        <v>1332</v>
+      </c>
+      <c r="H336" t="s" s="13">
+        <v>1333</v>
       </c>
     </row>
     <row r="337">
@@ -13913,7 +14169,10 @@
         <v>618</v>
       </c>
       <c r="B337" t="s" s="7">
-        <v>1300</v>
+        <v>1334</v>
+      </c>
+      <c r="C337" t="s" s="8">
+        <v>1335</v>
       </c>
       <c r="D337" s="9">
         <v>81</v>
@@ -13922,10 +14181,10 @@
         <v>3</v>
       </c>
       <c r="F337" t="s" s="11">
-        <v>1301</v>
+        <v>1336</v>
       </c>
       <c r="G337" t="s" s="12">
-        <v>1302</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="338">
@@ -13935,6 +14194,9 @@
       <c r="B338" t="s" s="7">
         <v>1066</v>
       </c>
+      <c r="C338" t="s" s="8">
+        <v>1338</v>
+      </c>
       <c r="D338" s="9">
         <v>81</v>
       </c>
@@ -13942,10 +14204,10 @@
         <v>3</v>
       </c>
       <c r="F338" t="s" s="11">
-        <v>1303</v>
+        <v>1339</v>
       </c>
       <c r="G338" t="s" s="12">
-        <v>1304</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="339">
@@ -13953,7 +14215,10 @@
         <v>620</v>
       </c>
       <c r="B339" t="s" s="7">
-        <v>1305</v>
+        <v>1341</v>
+      </c>
+      <c r="C339" t="s" s="8">
+        <v>1342</v>
       </c>
       <c r="D339" s="9">
         <v>81</v>
@@ -13962,10 +14227,10 @@
         <v>3</v>
       </c>
       <c r="F339" t="s" s="11">
-        <v>1306</v>
+        <v>1343</v>
       </c>
       <c r="G339" t="s" s="12">
-        <v>1307</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="340">
@@ -13973,7 +14238,10 @@
         <v>621</v>
       </c>
       <c r="B340" t="s" s="7">
-        <v>1308</v>
+        <v>1345</v>
+      </c>
+      <c r="C340" t="s" s="8">
+        <v>1346</v>
       </c>
       <c r="D340" s="9">
         <v>81</v>
@@ -13982,10 +14250,10 @@
         <v>3</v>
       </c>
       <c r="F340" t="s" s="11">
-        <v>1309</v>
+        <v>1347</v>
       </c>
       <c r="G340" t="s" s="12">
-        <v>1310</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="341">
@@ -13993,7 +14261,10 @@
         <v>622</v>
       </c>
       <c r="B341" t="s" s="7">
-        <v>1311</v>
+        <v>1349</v>
+      </c>
+      <c r="C341" t="s" s="8">
+        <v>1350</v>
       </c>
       <c r="D341" s="9">
         <v>81</v>
@@ -14002,10 +14273,10 @@
         <v>3</v>
       </c>
       <c r="F341" t="s" s="11">
-        <v>1312</v>
+        <v>1351</v>
       </c>
       <c r="G341" t="s" s="12">
-        <v>1313</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="342">
@@ -14013,7 +14284,10 @@
         <v>623</v>
       </c>
       <c r="B342" t="s" s="7">
-        <v>1314</v>
+        <v>1353</v>
+      </c>
+      <c r="C342" t="s" s="8">
+        <v>1354</v>
       </c>
       <c r="D342" s="9">
         <v>81</v>
@@ -14022,10 +14296,10 @@
         <v>3</v>
       </c>
       <c r="F342" t="s" s="11">
-        <v>1315</v>
+        <v>1355</v>
       </c>
       <c r="G342" t="s" s="12">
-        <v>1316</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="343">
@@ -14033,7 +14307,10 @@
         <v>624</v>
       </c>
       <c r="B343" t="s" s="7">
-        <v>1317</v>
+        <v>1357</v>
+      </c>
+      <c r="C343" t="s" s="8">
+        <v>1358</v>
       </c>
       <c r="D343" s="9">
         <v>81</v>
@@ -14042,10 +14319,10 @@
         <v>3</v>
       </c>
       <c r="F343" t="s" s="11">
-        <v>1318</v>
+        <v>1359</v>
       </c>
       <c r="G343" t="s" s="12">
-        <v>1319</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="344">
@@ -14053,7 +14330,10 @@
         <v>625</v>
       </c>
       <c r="B344" t="s" s="7">
-        <v>1320</v>
+        <v>1361</v>
+      </c>
+      <c r="C344" t="s" s="8">
+        <v>1362</v>
       </c>
       <c r="D344" s="9">
         <v>81</v>
@@ -14062,10 +14342,13 @@
         <v>3</v>
       </c>
       <c r="F344" t="s" s="11">
-        <v>1321</v>
+        <v>1363</v>
       </c>
       <c r="G344" t="s" s="12">
-        <v>1322</v>
+        <v>1364</v>
+      </c>
+      <c r="H344" t="s" s="13">
+        <v>1365</v>
       </c>
     </row>
     <row r="345">
@@ -14075,6 +14358,9 @@
       <c r="B345" t="s" s="7">
         <v>1128</v>
       </c>
+      <c r="C345" t="s" s="8">
+        <v>1366</v>
+      </c>
       <c r="D345" s="9">
         <v>81</v>
       </c>
@@ -14082,10 +14368,10 @@
         <v>3</v>
       </c>
       <c r="F345" t="s" s="11">
-        <v>1323</v>
+        <v>1367</v>
       </c>
       <c r="G345" t="s" s="12">
-        <v>1324</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="346">
@@ -14095,6 +14381,9 @@
       <c r="B346" t="s" s="7">
         <v>948</v>
       </c>
+      <c r="C346" t="s" s="8">
+        <v>1369</v>
+      </c>
       <c r="D346" s="9">
         <v>81</v>
       </c>
@@ -14102,10 +14391,10 @@
         <v>3</v>
       </c>
       <c r="F346" t="s" s="11">
-        <v>1325</v>
+        <v>1370</v>
       </c>
       <c r="G346" t="s" s="12">
-        <v>1326</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="347">
@@ -14113,7 +14402,7 @@
         <v>628</v>
       </c>
       <c r="B347" t="s" s="7">
-        <v>1327</v>
+        <v>1372</v>
       </c>
       <c r="D347" s="9">
         <v>12</v>
@@ -14122,10 +14411,10 @@
         <v>3</v>
       </c>
       <c r="F347" t="s" s="11">
-        <v>1328</v>
+        <v>1373</v>
       </c>
       <c r="G347" t="s" s="12">
-        <v>1329</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="348">
@@ -14133,7 +14422,7 @@
         <v>629</v>
       </c>
       <c r="B348" t="s" s="7">
-        <v>1330</v>
+        <v>1375</v>
       </c>
       <c r="D348" s="9">
         <v>16</v>
@@ -14142,10 +14431,10 @@
         <v>3</v>
       </c>
       <c r="F348" t="s" s="11">
-        <v>1331</v>
+        <v>1376</v>
       </c>
       <c r="G348" t="s" s="12">
-        <v>1332</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="349">
@@ -14153,7 +14442,7 @@
         <v>630</v>
       </c>
       <c r="B349" t="s" s="7">
-        <v>1333</v>
+        <v>1378</v>
       </c>
       <c r="D349" s="9">
         <v>16</v>
@@ -14162,10 +14451,10 @@
         <v>3</v>
       </c>
       <c r="F349" t="s" s="11">
-        <v>1334</v>
+        <v>1379</v>
       </c>
       <c r="G349" t="s" s="12">
-        <v>1335</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="350">
@@ -14173,7 +14462,7 @@
         <v>631</v>
       </c>
       <c r="B350" t="s" s="7">
-        <v>1336</v>
+        <v>1381</v>
       </c>
       <c r="D350" s="9">
         <v>16</v>
@@ -14182,10 +14471,10 @@
         <v>3</v>
       </c>
       <c r="F350" t="s" s="11">
-        <v>1337</v>
+        <v>1382</v>
       </c>
       <c r="G350" t="s" s="12">
-        <v>1338</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="351">
@@ -14193,7 +14482,7 @@
         <v>632</v>
       </c>
       <c r="B351" t="s" s="7">
-        <v>1339</v>
+        <v>1384</v>
       </c>
       <c r="D351" s="9">
         <v>16</v>
@@ -14202,10 +14491,10 @@
         <v>3</v>
       </c>
       <c r="F351" t="s" s="11">
-        <v>1340</v>
+        <v>1385</v>
       </c>
       <c r="G351" t="s" s="12">
-        <v>1341</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="352">
@@ -14213,7 +14502,7 @@
         <v>633</v>
       </c>
       <c r="B352" t="s" s="7">
-        <v>1342</v>
+        <v>1387</v>
       </c>
       <c r="D352" s="9">
         <v>16</v>
@@ -14222,10 +14511,10 @@
         <v>3</v>
       </c>
       <c r="F352" t="s" s="11">
-        <v>1343</v>
+        <v>1388</v>
       </c>
       <c r="G352" t="s" s="12">
-        <v>1344</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="353">
@@ -14233,7 +14522,7 @@
         <v>634</v>
       </c>
       <c r="B353" t="s" s="7">
-        <v>1345</v>
+        <v>1390</v>
       </c>
       <c r="D353" s="9">
         <v>16</v>
@@ -14242,10 +14531,10 @@
         <v>3</v>
       </c>
       <c r="F353" t="s" s="11">
-        <v>1346</v>
+        <v>1391</v>
       </c>
       <c r="G353" t="s" s="12">
-        <v>1347</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="354">
@@ -14253,7 +14542,7 @@
         <v>635</v>
       </c>
       <c r="B354" t="s" s="7">
-        <v>1348</v>
+        <v>1393</v>
       </c>
       <c r="D354" s="9">
         <v>16</v>
@@ -14262,10 +14551,10 @@
         <v>3</v>
       </c>
       <c r="F354" t="s" s="11">
-        <v>1349</v>
+        <v>1394</v>
       </c>
       <c r="G354" t="s" s="12">
-        <v>1350</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="355">
@@ -14273,7 +14562,7 @@
         <v>636</v>
       </c>
       <c r="B355" t="s" s="7">
-        <v>1351</v>
+        <v>1396</v>
       </c>
       <c r="D355" s="9">
         <v>16</v>
@@ -14282,10 +14571,10 @@
         <v>3</v>
       </c>
       <c r="F355" t="s" s="11">
-        <v>1352</v>
+        <v>1397</v>
       </c>
       <c r="G355" t="s" s="12">
-        <v>1353</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="356">
@@ -14293,7 +14582,7 @@
         <v>637</v>
       </c>
       <c r="B356" t="s" s="7">
-        <v>1354</v>
+        <v>1399</v>
       </c>
       <c r="D356" s="9">
         <v>16</v>
@@ -14302,10 +14591,10 @@
         <v>3</v>
       </c>
       <c r="F356" t="s" s="11">
-        <v>1355</v>
+        <v>1400</v>
       </c>
       <c r="G356" t="s" s="12">
-        <v>1356</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="357">
@@ -14313,7 +14602,7 @@
         <v>638</v>
       </c>
       <c r="B357" t="s" s="7">
-        <v>1354</v>
+        <v>1399</v>
       </c>
       <c r="D357" s="9">
         <v>16</v>
@@ -14322,10 +14611,10 @@
         <v>3</v>
       </c>
       <c r="F357" t="s" s="11">
-        <v>1357</v>
+        <v>1402</v>
       </c>
       <c r="G357" t="s" s="12">
-        <v>1358</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="358">
@@ -14333,10 +14622,10 @@
         <v>639</v>
       </c>
       <c r="B358" t="s" s="7">
-        <v>1359</v>
+        <v>1404</v>
       </c>
       <c r="C358" t="s" s="8">
-        <v>1360</v>
+        <v>1405</v>
       </c>
       <c r="D358" s="9">
         <v>289</v>
@@ -14345,10 +14634,10 @@
         <v>4</v>
       </c>
       <c r="F358" t="s" s="11">
-        <v>1361</v>
+        <v>1406</v>
       </c>
       <c r="G358" t="s" s="12">
-        <v>1362</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="359">
@@ -14356,19 +14645,19 @@
         <v>640</v>
       </c>
       <c r="B359" t="s" s="7">
-        <v>1363</v>
+        <v>1408</v>
       </c>
       <c r="C359" t="s" s="8">
-        <v>1364</v>
+        <v>1409</v>
       </c>
       <c r="E359" s="10">
         <v>4</v>
       </c>
       <c r="F359" t="s" s="11">
-        <v>1365</v>
+        <v>1410</v>
       </c>
       <c r="G359" t="s" s="12">
-        <v>1366</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="360">
@@ -14376,19 +14665,19 @@
         <v>641</v>
       </c>
       <c r="B360" t="s" s="7">
-        <v>1367</v>
+        <v>1412</v>
       </c>
       <c r="C360" t="s" s="8">
-        <v>1368</v>
+        <v>1413</v>
       </c>
       <c r="E360" s="10">
         <v>4</v>
       </c>
       <c r="F360" t="s" s="11">
-        <v>1369</v>
+        <v>1414</v>
       </c>
       <c r="G360" t="s" s="12">
-        <v>1370</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="361">
@@ -14396,19 +14685,19 @@
         <v>642</v>
       </c>
       <c r="B361" t="s" s="7">
-        <v>1371</v>
+        <v>1416</v>
       </c>
       <c r="C361" t="s" s="8">
-        <v>1372</v>
+        <v>1417</v>
       </c>
       <c r="E361" s="10">
         <v>4</v>
       </c>
       <c r="F361" t="s" s="11">
-        <v>1373</v>
+        <v>1418</v>
       </c>
       <c r="G361" t="s" s="12">
-        <v>1374</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="362">
@@ -14416,19 +14705,19 @@
         <v>643</v>
       </c>
       <c r="B362" t="s" s="7">
-        <v>1375</v>
+        <v>1420</v>
       </c>
       <c r="C362" t="s" s="8">
-        <v>1376</v>
+        <v>1421</v>
       </c>
       <c r="E362" s="10">
         <v>4</v>
       </c>
       <c r="F362" t="s" s="11">
-        <v>1377</v>
+        <v>1422</v>
       </c>
       <c r="G362" t="s" s="12">
-        <v>1378</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="363">
@@ -14436,19 +14725,19 @@
         <v>644</v>
       </c>
       <c r="B363" t="s" s="7">
-        <v>1379</v>
+        <v>1424</v>
       </c>
       <c r="C363" t="s" s="8">
-        <v>1380</v>
+        <v>1425</v>
       </c>
       <c r="E363" s="10">
         <v>4</v>
       </c>
       <c r="F363" t="s" s="11">
-        <v>1381</v>
+        <v>1426</v>
       </c>
       <c r="G363" t="s" s="12">
-        <v>1382</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="364">
@@ -14456,22 +14745,22 @@
         <v>645</v>
       </c>
       <c r="B364" t="s" s="7">
-        <v>1383</v>
+        <v>1428</v>
       </c>
       <c r="C364" t="s" s="8">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="E364" s="10">
         <v>4</v>
       </c>
       <c r="F364" t="s" s="11">
-        <v>1385</v>
+        <v>1430</v>
       </c>
       <c r="G364" t="s" s="12">
-        <v>1386</v>
+        <v>1431</v>
       </c>
       <c r="H364" t="s" s="13">
-        <v>1387</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="365">
@@ -14479,22 +14768,22 @@
         <v>646</v>
       </c>
       <c r="B365" t="s" s="7">
-        <v>1388</v>
+        <v>1433</v>
       </c>
       <c r="C365" t="s" s="8">
-        <v>1389</v>
+        <v>1434</v>
       </c>
       <c r="E365" s="10">
         <v>4</v>
       </c>
       <c r="F365" t="s" s="11">
-        <v>1390</v>
+        <v>1435</v>
       </c>
       <c r="G365" t="s" s="12">
-        <v>1391</v>
+        <v>1436</v>
       </c>
       <c r="H365" t="s" s="13">
-        <v>1392</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="366">
@@ -14502,19 +14791,19 @@
         <v>647</v>
       </c>
       <c r="B366" t="s" s="7">
-        <v>1393</v>
+        <v>1438</v>
       </c>
       <c r="C366" t="s" s="8">
-        <v>1394</v>
+        <v>1439</v>
       </c>
       <c r="E366" s="10">
         <v>4</v>
       </c>
       <c r="F366" t="s" s="11">
-        <v>1395</v>
+        <v>1440</v>
       </c>
       <c r="G366" t="s" s="12">
-        <v>1396</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="367">
@@ -14522,19 +14811,19 @@
         <v>648</v>
       </c>
       <c r="B367" t="s" s="7">
-        <v>1397</v>
+        <v>1442</v>
       </c>
       <c r="C367" t="s" s="8">
-        <v>1398</v>
+        <v>1443</v>
       </c>
       <c r="E367" s="10">
         <v>4</v>
       </c>
       <c r="F367" t="s" s="11">
-        <v>1399</v>
+        <v>1444</v>
       </c>
       <c r="G367" t="s" s="12">
-        <v>1400</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="368">
@@ -14542,19 +14831,19 @@
         <v>649</v>
       </c>
       <c r="B368" t="s" s="7">
-        <v>1401</v>
+        <v>1446</v>
       </c>
       <c r="C368" t="s" s="8">
-        <v>1402</v>
+        <v>1447</v>
       </c>
       <c r="E368" s="10">
         <v>4</v>
       </c>
       <c r="F368" t="s" s="11">
-        <v>1403</v>
+        <v>1448</v>
       </c>
       <c r="G368" t="s" s="12">
-        <v>1404</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="369">
@@ -14562,19 +14851,19 @@
         <v>650</v>
       </c>
       <c r="B369" t="s" s="7">
-        <v>1405</v>
+        <v>1450</v>
       </c>
       <c r="C369" t="s" s="8">
-        <v>1406</v>
+        <v>1451</v>
       </c>
       <c r="E369" s="10">
         <v>4</v>
       </c>
       <c r="F369" t="s" s="11">
-        <v>1407</v>
+        <v>1452</v>
       </c>
       <c r="G369" t="s" s="12">
-        <v>1408</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="370">
@@ -14582,19 +14871,19 @@
         <v>651</v>
       </c>
       <c r="B370" t="s" s="7">
-        <v>1409</v>
+        <v>1454</v>
       </c>
       <c r="C370" t="s" s="8">
-        <v>1410</v>
+        <v>1455</v>
       </c>
       <c r="E370" s="10">
         <v>4</v>
       </c>
       <c r="F370" t="s" s="11">
-        <v>1411</v>
+        <v>1456</v>
       </c>
       <c r="G370" t="s" s="12">
-        <v>1412</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="371">
@@ -14602,19 +14891,19 @@
         <v>652</v>
       </c>
       <c r="B371" t="s" s="7">
-        <v>1413</v>
+        <v>1458</v>
       </c>
       <c r="C371" t="s" s="8">
-        <v>1414</v>
+        <v>1459</v>
       </c>
       <c r="E371" s="10">
         <v>4</v>
       </c>
       <c r="F371" t="s" s="11">
-        <v>1415</v>
+        <v>1460</v>
       </c>
       <c r="G371" t="s" s="12">
-        <v>1416</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="372">
@@ -14622,19 +14911,19 @@
         <v>653</v>
       </c>
       <c r="B372" t="s" s="7">
-        <v>1417</v>
+        <v>1462</v>
       </c>
       <c r="C372" t="s" s="8">
-        <v>1418</v>
+        <v>1463</v>
       </c>
       <c r="E372" s="10">
         <v>4</v>
       </c>
       <c r="F372" t="s" s="11">
-        <v>1419</v>
+        <v>1464</v>
       </c>
       <c r="G372" t="s" s="12">
-        <v>1420</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="373">
@@ -14642,19 +14931,19 @@
         <v>654</v>
       </c>
       <c r="B373" t="s" s="7">
-        <v>1421</v>
+        <v>1466</v>
       </c>
       <c r="C373" t="s" s="8">
-        <v>1422</v>
+        <v>1467</v>
       </c>
       <c r="E373" s="10">
         <v>4</v>
       </c>
       <c r="F373" t="s" s="11">
-        <v>1423</v>
+        <v>1468</v>
       </c>
       <c r="G373" t="s" s="12">
-        <v>1424</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="374">
@@ -14662,19 +14951,19 @@
         <v>655</v>
       </c>
       <c r="B374" t="s" s="7">
-        <v>1425</v>
+        <v>1470</v>
       </c>
       <c r="C374" t="s" s="8">
-        <v>1426</v>
+        <v>1471</v>
       </c>
       <c r="E374" s="10">
         <v>4</v>
       </c>
       <c r="F374" t="s" s="11">
-        <v>1427</v>
+        <v>1472</v>
       </c>
       <c r="G374" t="s" s="12">
-        <v>1428</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="375">
@@ -14682,19 +14971,19 @@
         <v>656</v>
       </c>
       <c r="B375" t="s" s="7">
-        <v>1429</v>
+        <v>1474</v>
       </c>
       <c r="C375" t="s" s="8">
-        <v>1430</v>
+        <v>1475</v>
       </c>
       <c r="E375" s="10">
         <v>4</v>
       </c>
       <c r="F375" t="s" s="11">
-        <v>1431</v>
+        <v>1476</v>
       </c>
       <c r="G375" t="s" s="12">
-        <v>1432</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="376">
@@ -14702,19 +14991,19 @@
         <v>657</v>
       </c>
       <c r="B376" t="s" s="7">
-        <v>1433</v>
+        <v>1478</v>
       </c>
       <c r="C376" t="s" s="8">
-        <v>1434</v>
+        <v>1479</v>
       </c>
       <c r="E376" s="10">
         <v>4</v>
       </c>
       <c r="F376" t="s" s="11">
-        <v>1435</v>
+        <v>1480</v>
       </c>
       <c r="G376" t="s" s="12">
-        <v>1436</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="377">
@@ -14722,22 +15011,22 @@
         <v>658</v>
       </c>
       <c r="B377" t="s" s="7">
-        <v>1437</v>
+        <v>1482</v>
       </c>
       <c r="C377" t="s" s="8">
-        <v>1438</v>
+        <v>1483</v>
       </c>
       <c r="E377" s="10">
         <v>4</v>
       </c>
       <c r="F377" t="s" s="11">
-        <v>1439</v>
+        <v>1484</v>
       </c>
       <c r="G377" t="s" s="12">
-        <v>1440</v>
+        <v>1485</v>
       </c>
       <c r="H377" t="s" s="13">
-        <v>1441</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="378">
@@ -14745,22 +15034,22 @@
         <v>659</v>
       </c>
       <c r="B378" t="s" s="7">
-        <v>1442</v>
+        <v>1487</v>
       </c>
       <c r="C378" t="s" s="8">
-        <v>1443</v>
+        <v>1488</v>
       </c>
       <c r="E378" s="10">
         <v>4</v>
       </c>
       <c r="F378" t="s" s="11">
-        <v>1444</v>
+        <v>1489</v>
       </c>
       <c r="G378" t="s" s="12">
-        <v>1445</v>
+        <v>1490</v>
       </c>
       <c r="H378" t="s" s="13">
-        <v>1446</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="379">
@@ -14768,22 +15057,22 @@
         <v>660</v>
       </c>
       <c r="B379" t="s" s="7">
-        <v>1447</v>
+        <v>1492</v>
       </c>
       <c r="C379" t="s" s="8">
-        <v>1448</v>
+        <v>1493</v>
       </c>
       <c r="E379" s="10">
         <v>4</v>
       </c>
       <c r="F379" t="s" s="11">
-        <v>1449</v>
+        <v>1494</v>
       </c>
       <c r="G379" t="s" s="12">
-        <v>1450</v>
+        <v>1495</v>
       </c>
       <c r="H379" t="s" s="13">
-        <v>1451</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="380">
@@ -14791,22 +15080,22 @@
         <v>661</v>
       </c>
       <c r="B380" t="s" s="7">
-        <v>1452</v>
+        <v>1497</v>
       </c>
       <c r="C380" t="s" s="8">
-        <v>1453</v>
+        <v>1498</v>
       </c>
       <c r="E380" s="10">
         <v>4</v>
       </c>
       <c r="F380" t="s" s="11">
-        <v>1454</v>
+        <v>1499</v>
       </c>
       <c r="G380" t="s" s="12">
-        <v>1455</v>
+        <v>1500</v>
       </c>
       <c r="H380" t="s" s="13">
-        <v>1456</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="381">
@@ -14814,22 +15103,22 @@
         <v>662</v>
       </c>
       <c r="B381" t="s" s="7">
-        <v>1457</v>
+        <v>1502</v>
       </c>
       <c r="C381" t="s" s="8">
-        <v>1458</v>
+        <v>1503</v>
       </c>
       <c r="E381" s="10">
         <v>4</v>
       </c>
       <c r="F381" t="s" s="11">
-        <v>1459</v>
+        <v>1504</v>
       </c>
       <c r="G381" t="s" s="12">
-        <v>1460</v>
+        <v>1505</v>
       </c>
       <c r="H381" t="s" s="13">
-        <v>1461</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="382">
@@ -14837,7 +15126,7 @@
         <v>663</v>
       </c>
       <c r="B382" t="s" s="7">
-        <v>1462</v>
+        <v>1507</v>
       </c>
       <c r="C382" t="s" s="8">
         <v>208</v>
@@ -14846,13 +15135,13 @@
         <v>4</v>
       </c>
       <c r="F382" t="s" s="11">
-        <v>1463</v>
+        <v>1508</v>
       </c>
       <c r="G382" t="s" s="12">
-        <v>1464</v>
+        <v>1509</v>
       </c>
       <c r="H382" t="s" s="13">
-        <v>1465</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="383">
@@ -14860,22 +15149,22 @@
         <v>664</v>
       </c>
       <c r="B383" t="s" s="7">
-        <v>1466</v>
+        <v>1511</v>
       </c>
       <c r="C383" t="s" s="8">
-        <v>1467</v>
+        <v>1512</v>
       </c>
       <c r="E383" s="10">
         <v>4</v>
       </c>
       <c r="F383" t="s" s="11">
-        <v>1468</v>
+        <v>1513</v>
       </c>
       <c r="G383" t="s" s="12">
-        <v>1469</v>
+        <v>1514</v>
       </c>
       <c r="H383" t="s" s="13">
-        <v>1470</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="384">
@@ -14883,22 +15172,22 @@
         <v>665</v>
       </c>
       <c r="B384" t="s" s="7">
-        <v>1471</v>
+        <v>1516</v>
       </c>
       <c r="C384" t="s" s="8">
-        <v>1472</v>
+        <v>1517</v>
       </c>
       <c r="E384" s="10">
         <v>4</v>
       </c>
       <c r="F384" t="s" s="11">
-        <v>1473</v>
+        <v>1518</v>
       </c>
       <c r="G384" t="s" s="12">
-        <v>1474</v>
+        <v>1519</v>
       </c>
       <c r="H384" t="s" s="13">
-        <v>1475</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="385">
@@ -14906,22 +15195,22 @@
         <v>666</v>
       </c>
       <c r="B385" t="s" s="7">
-        <v>1476</v>
+        <v>1521</v>
       </c>
       <c r="C385" t="s" s="8">
-        <v>1477</v>
+        <v>1522</v>
       </c>
       <c r="E385" s="10">
         <v>4</v>
       </c>
       <c r="F385" t="s" s="11">
-        <v>1478</v>
+        <v>1523</v>
       </c>
       <c r="G385" t="s" s="12">
-        <v>1479</v>
+        <v>1524</v>
       </c>
       <c r="H385" t="s" s="13">
-        <v>1475</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="386">
@@ -14929,19 +15218,19 @@
         <v>667</v>
       </c>
       <c r="B386" t="s" s="7">
-        <v>1480</v>
+        <v>1525</v>
       </c>
       <c r="C386" t="s" s="8">
-        <v>1481</v>
+        <v>1526</v>
       </c>
       <c r="E386" s="10">
         <v>4</v>
       </c>
       <c r="F386" t="s" s="11">
-        <v>1482</v>
+        <v>1527</v>
       </c>
       <c r="G386" t="s" s="12">
-        <v>1483</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="387">
@@ -14949,19 +15238,19 @@
         <v>668</v>
       </c>
       <c r="B387" t="s" s="7">
-        <v>1484</v>
+        <v>1529</v>
       </c>
       <c r="C387" t="s" s="8">
-        <v>1485</v>
+        <v>1530</v>
       </c>
       <c r="E387" s="10">
         <v>4</v>
       </c>
       <c r="F387" t="s" s="11">
-        <v>1486</v>
+        <v>1531</v>
       </c>
       <c r="G387" t="s" s="12">
-        <v>1487</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="388">
@@ -14969,19 +15258,19 @@
         <v>669</v>
       </c>
       <c r="B388" t="s" s="7">
-        <v>1488</v>
+        <v>1533</v>
       </c>
       <c r="C388" t="s" s="8">
-        <v>1489</v>
+        <v>1534</v>
       </c>
       <c r="E388" s="10">
         <v>4</v>
       </c>
       <c r="F388" t="s" s="11">
-        <v>1490</v>
+        <v>1535</v>
       </c>
       <c r="G388" t="s" s="12">
-        <v>1491</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="389">
@@ -14989,19 +15278,19 @@
         <v>670</v>
       </c>
       <c r="B389" t="s" s="7">
-        <v>1492</v>
+        <v>1537</v>
       </c>
       <c r="C389" t="s" s="8">
-        <v>1493</v>
+        <v>1538</v>
       </c>
       <c r="E389" s="10">
         <v>4</v>
       </c>
       <c r="F389" t="s" s="11">
-        <v>1494</v>
+        <v>1539</v>
       </c>
       <c r="G389" t="s" s="12">
-        <v>1495</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="390">
@@ -15009,19 +15298,19 @@
         <v>671</v>
       </c>
       <c r="B390" t="s" s="7">
-        <v>1496</v>
+        <v>1541</v>
       </c>
       <c r="C390" t="s" s="8">
-        <v>1497</v>
+        <v>1542</v>
       </c>
       <c r="E390" s="10">
         <v>4</v>
       </c>
       <c r="F390" t="s" s="11">
-        <v>1498</v>
+        <v>1543</v>
       </c>
       <c r="G390" t="s" s="12">
-        <v>1499</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="391">
@@ -15029,19 +15318,19 @@
         <v>672</v>
       </c>
       <c r="B391" t="s" s="7">
-        <v>1500</v>
+        <v>1545</v>
       </c>
       <c r="C391" t="s" s="8">
-        <v>1501</v>
+        <v>1546</v>
       </c>
       <c r="E391" s="10">
         <v>4</v>
       </c>
       <c r="F391" t="s" s="11">
-        <v>1502</v>
+        <v>1547</v>
       </c>
       <c r="G391" t="s" s="12">
-        <v>1503</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="392">
@@ -15049,22 +15338,22 @@
         <v>673</v>
       </c>
       <c r="B392" t="s" s="7">
-        <v>1504</v>
+        <v>1549</v>
       </c>
       <c r="C392" t="s" s="8">
-        <v>1505</v>
+        <v>1550</v>
       </c>
       <c r="E392" s="10">
         <v>4</v>
       </c>
       <c r="F392" t="s" s="11">
-        <v>1506</v>
+        <v>1551</v>
       </c>
       <c r="G392" t="s" s="12">
-        <v>1507</v>
+        <v>1552</v>
       </c>
       <c r="H392" t="s" s="13">
-        <v>1508</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="393">
@@ -15072,22 +15361,22 @@
         <v>674</v>
       </c>
       <c r="B393" t="s" s="7">
-        <v>1509</v>
+        <v>1554</v>
       </c>
       <c r="C393" t="s" s="8">
-        <v>1510</v>
+        <v>1555</v>
       </c>
       <c r="E393" s="10">
         <v>4</v>
       </c>
       <c r="F393" t="s" s="11">
-        <v>1511</v>
+        <v>1556</v>
       </c>
       <c r="G393" t="s" s="12">
-        <v>1512</v>
+        <v>1557</v>
       </c>
       <c r="H393" t="s" s="13">
-        <v>1513</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="394">
@@ -15095,22 +15384,22 @@
         <v>675</v>
       </c>
       <c r="B394" t="s" s="7">
-        <v>1514</v>
+        <v>1559</v>
       </c>
       <c r="C394" t="s" s="8">
-        <v>1515</v>
+        <v>1560</v>
       </c>
       <c r="E394" s="10">
         <v>4</v>
       </c>
       <c r="F394" t="s" s="11">
-        <v>1516</v>
+        <v>1561</v>
       </c>
       <c r="G394" t="s" s="12">
-        <v>1517</v>
+        <v>1562</v>
       </c>
       <c r="H394" t="s" s="13">
-        <v>1518</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="395">
@@ -15118,19 +15407,19 @@
         <v>676</v>
       </c>
       <c r="B395" t="s" s="7">
-        <v>1519</v>
+        <v>1564</v>
       </c>
       <c r="C395" t="s" s="8">
-        <v>1520</v>
+        <v>1565</v>
       </c>
       <c r="E395" s="10">
         <v>4</v>
       </c>
       <c r="F395" t="s" s="11">
-        <v>1521</v>
+        <v>1566</v>
       </c>
       <c r="G395" t="s" s="12">
-        <v>1522</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="396">
@@ -15138,19 +15427,19 @@
         <v>677</v>
       </c>
       <c r="B396" t="s" s="7">
-        <v>1523</v>
+        <v>1568</v>
       </c>
       <c r="C396" t="s" s="8">
-        <v>1524</v>
+        <v>1569</v>
       </c>
       <c r="E396" s="10">
         <v>4</v>
       </c>
       <c r="F396" t="s" s="11">
-        <v>1525</v>
+        <v>1570</v>
       </c>
       <c r="G396" t="s" s="12">
-        <v>1526</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="397">
@@ -15158,19 +15447,19 @@
         <v>678</v>
       </c>
       <c r="B397" t="s" s="7">
-        <v>1527</v>
+        <v>1572</v>
       </c>
       <c r="C397" t="s" s="8">
-        <v>1528</v>
+        <v>1573</v>
       </c>
       <c r="E397" s="10">
         <v>4</v>
       </c>
       <c r="F397" t="s" s="11">
-        <v>1529</v>
+        <v>1574</v>
       </c>
       <c r="G397" t="s" s="12">
-        <v>1530</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="398">
@@ -15178,19 +15467,19 @@
         <v>679</v>
       </c>
       <c r="B398" t="s" s="7">
-        <v>1531</v>
+        <v>1576</v>
       </c>
       <c r="C398" t="s" s="8">
-        <v>1532</v>
+        <v>1577</v>
       </c>
       <c r="E398" s="10">
         <v>4</v>
       </c>
       <c r="F398" t="s" s="11">
-        <v>1533</v>
+        <v>1578</v>
       </c>
       <c r="G398" t="s" s="12">
-        <v>1534</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="399">
@@ -15198,19 +15487,19 @@
         <v>680</v>
       </c>
       <c r="B399" t="s" s="7">
-        <v>1535</v>
+        <v>1580</v>
       </c>
       <c r="C399" t="s" s="8">
-        <v>1536</v>
+        <v>1581</v>
       </c>
       <c r="E399" s="10">
         <v>4</v>
       </c>
       <c r="F399" t="s" s="11">
-        <v>1537</v>
+        <v>1582</v>
       </c>
       <c r="G399" t="s" s="12">
-        <v>1538</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="400">
@@ -15218,19 +15507,19 @@
         <v>681</v>
       </c>
       <c r="B400" t="s" s="7">
-        <v>1539</v>
+        <v>1584</v>
       </c>
       <c r="C400" t="s" s="8">
-        <v>1540</v>
+        <v>1585</v>
       </c>
       <c r="E400" s="10">
         <v>4</v>
       </c>
       <c r="F400" t="s" s="11">
-        <v>1541</v>
+        <v>1586</v>
       </c>
       <c r="G400" t="s" s="12">
-        <v>1542</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="401">
@@ -15238,19 +15527,19 @@
         <v>682</v>
       </c>
       <c r="B401" t="s" s="7">
-        <v>1543</v>
+        <v>1588</v>
       </c>
       <c r="C401" t="s" s="8">
-        <v>1544</v>
+        <v>1589</v>
       </c>
       <c r="E401" s="10">
         <v>4</v>
       </c>
       <c r="F401" t="s" s="11">
-        <v>1545</v>
+        <v>1590</v>
       </c>
       <c r="G401" t="s" s="12">
-        <v>1546</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="402">
@@ -15258,19 +15547,19 @@
         <v>683</v>
       </c>
       <c r="B402" t="s" s="7">
-        <v>1547</v>
+        <v>1592</v>
       </c>
       <c r="C402" t="s" s="8">
-        <v>1548</v>
+        <v>1593</v>
       </c>
       <c r="E402" s="10">
         <v>4</v>
       </c>
       <c r="F402" t="s" s="11">
-        <v>1549</v>
+        <v>1594</v>
       </c>
       <c r="G402" t="s" s="12">
-        <v>1550</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="403">
@@ -15278,19 +15567,19 @@
         <v>684</v>
       </c>
       <c r="B403" t="s" s="7">
-        <v>1551</v>
+        <v>1596</v>
       </c>
       <c r="C403" t="s" s="8">
-        <v>1552</v>
+        <v>1597</v>
       </c>
       <c r="E403" s="10">
         <v>4</v>
       </c>
       <c r="F403" t="s" s="11">
-        <v>1553</v>
+        <v>1598</v>
       </c>
       <c r="G403" t="s" s="12">
-        <v>1554</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="404">
@@ -15298,19 +15587,19 @@
         <v>685</v>
       </c>
       <c r="B404" t="s" s="7">
-        <v>1555</v>
+        <v>1600</v>
       </c>
       <c r="C404" t="s" s="8">
-        <v>1556</v>
+        <v>1601</v>
       </c>
       <c r="E404" s="10">
         <v>4</v>
       </c>
       <c r="F404" t="s" s="11">
-        <v>1557</v>
+        <v>1602</v>
       </c>
       <c r="G404" t="s" s="12">
-        <v>1558</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="405">
@@ -15318,19 +15607,19 @@
         <v>686</v>
       </c>
       <c r="B405" t="s" s="7">
-        <v>1559</v>
+        <v>1604</v>
       </c>
       <c r="C405" t="s" s="8">
-        <v>1560</v>
+        <v>1605</v>
       </c>
       <c r="E405" s="10">
         <v>4</v>
       </c>
       <c r="F405" t="s" s="11">
-        <v>1561</v>
+        <v>1606</v>
       </c>
       <c r="G405" t="s" s="12">
-        <v>1562</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="406">
@@ -15338,19 +15627,19 @@
         <v>687</v>
       </c>
       <c r="B406" t="s" s="7">
-        <v>1563</v>
+        <v>1608</v>
       </c>
       <c r="C406" t="s" s="8">
-        <v>1564</v>
+        <v>1609</v>
       </c>
       <c r="E406" s="10">
         <v>4</v>
       </c>
       <c r="F406" t="s" s="11">
-        <v>1565</v>
+        <v>1610</v>
       </c>
       <c r="G406" t="s" s="12">
-        <v>1566</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="407">
@@ -15358,22 +15647,22 @@
         <v>688</v>
       </c>
       <c r="B407" t="s" s="7">
-        <v>1567</v>
+        <v>1612</v>
       </c>
       <c r="C407" t="s" s="8">
-        <v>1568</v>
+        <v>1613</v>
       </c>
       <c r="E407" s="10">
         <v>4</v>
       </c>
       <c r="F407" t="s" s="11">
-        <v>1569</v>
+        <v>1614</v>
       </c>
       <c r="G407" t="s" s="12">
-        <v>1570</v>
+        <v>1615</v>
       </c>
       <c r="H407" t="s" s="13">
-        <v>1571</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="408">
@@ -15381,22 +15670,22 @@
         <v>689</v>
       </c>
       <c r="B408" t="s" s="7">
-        <v>1572</v>
+        <v>1617</v>
       </c>
       <c r="C408" t="s" s="8">
-        <v>1573</v>
+        <v>1618</v>
       </c>
       <c r="E408" s="10">
         <v>4</v>
       </c>
       <c r="F408" t="s" s="11">
-        <v>1574</v>
+        <v>1619</v>
       </c>
       <c r="G408" t="s" s="12">
-        <v>1575</v>
+        <v>1620</v>
       </c>
       <c r="H408" t="s" s="13">
-        <v>1576</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="409">
@@ -15404,19 +15693,19 @@
         <v>690</v>
       </c>
       <c r="B409" t="s" s="7">
-        <v>1577</v>
+        <v>1622</v>
       </c>
       <c r="C409" t="s" s="8">
-        <v>1578</v>
+        <v>1623</v>
       </c>
       <c r="E409" s="10">
         <v>4</v>
       </c>
       <c r="F409" t="s" s="11">
-        <v>1579</v>
+        <v>1624</v>
       </c>
       <c r="G409" t="s" s="12">
-        <v>1580</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="410">
@@ -15424,19 +15713,19 @@
         <v>691</v>
       </c>
       <c r="B410" t="s" s="7">
-        <v>1581</v>
+        <v>1626</v>
       </c>
       <c r="C410" t="s" s="8">
-        <v>1582</v>
+        <v>1627</v>
       </c>
       <c r="E410" s="10">
         <v>4</v>
       </c>
       <c r="F410" t="s" s="11">
-        <v>1583</v>
+        <v>1628</v>
       </c>
       <c r="G410" t="s" s="12">
-        <v>1584</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="411">
@@ -15444,19 +15733,19 @@
         <v>692</v>
       </c>
       <c r="B411" t="s" s="7">
-        <v>1585</v>
+        <v>1630</v>
       </c>
       <c r="C411" t="s" s="8">
-        <v>1586</v>
+        <v>1631</v>
       </c>
       <c r="E411" s="10">
         <v>4</v>
       </c>
       <c r="F411" t="s" s="11">
-        <v>1587</v>
+        <v>1632</v>
       </c>
       <c r="G411" t="s" s="12">
-        <v>1588</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="412">
@@ -15464,22 +15753,22 @@
         <v>693</v>
       </c>
       <c r="B412" t="s" s="7">
-        <v>1589</v>
+        <v>1634</v>
       </c>
       <c r="C412" t="s" s="8">
-        <v>1590</v>
+        <v>1635</v>
       </c>
       <c r="E412" s="10">
         <v>4</v>
       </c>
       <c r="F412" t="s" s="11">
-        <v>1591</v>
+        <v>1636</v>
       </c>
       <c r="G412" t="s" s="12">
-        <v>1592</v>
+        <v>1637</v>
       </c>
       <c r="H412" t="s" s="13">
-        <v>1593</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="413">
@@ -15487,19 +15776,19 @@
         <v>694</v>
       </c>
       <c r="B413" t="s" s="7">
-        <v>1594</v>
+        <v>1639</v>
       </c>
       <c r="C413" t="s" s="8">
-        <v>1595</v>
+        <v>1640</v>
       </c>
       <c r="E413" s="10">
         <v>4</v>
       </c>
       <c r="F413" t="s" s="11">
-        <v>1596</v>
+        <v>1641</v>
       </c>
       <c r="G413" t="s" s="12">
-        <v>1597</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="414">
@@ -15507,19 +15796,19 @@
         <v>695</v>
       </c>
       <c r="B414" t="s" s="7">
-        <v>1598</v>
+        <v>1643</v>
       </c>
       <c r="C414" t="s" s="8">
-        <v>1599</v>
+        <v>1644</v>
       </c>
       <c r="E414" s="10">
         <v>4</v>
       </c>
       <c r="F414" t="s" s="11">
-        <v>1600</v>
+        <v>1645</v>
       </c>
       <c r="G414" t="s" s="12">
-        <v>1601</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="415">
@@ -15527,19 +15816,19 @@
         <v>696</v>
       </c>
       <c r="B415" t="s" s="7">
-        <v>1602</v>
+        <v>1647</v>
       </c>
       <c r="C415" t="s" s="8">
-        <v>1603</v>
+        <v>1648</v>
       </c>
       <c r="E415" s="10">
         <v>4</v>
       </c>
       <c r="F415" t="s" s="11">
-        <v>1604</v>
+        <v>1649</v>
       </c>
       <c r="G415" t="s" s="12">
-        <v>1605</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="416">
@@ -15547,19 +15836,19 @@
         <v>697</v>
       </c>
       <c r="B416" t="s" s="7">
-        <v>1606</v>
+        <v>1651</v>
       </c>
       <c r="C416" t="s" s="8">
-        <v>1607</v>
+        <v>1652</v>
       </c>
       <c r="E416" s="10">
         <v>4</v>
       </c>
       <c r="F416" t="s" s="11">
-        <v>1608</v>
+        <v>1653</v>
       </c>
       <c r="G416" t="s" s="12">
-        <v>1609</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="417">
@@ -15567,19 +15856,19 @@
         <v>698</v>
       </c>
       <c r="B417" t="s" s="7">
-        <v>1610</v>
+        <v>1655</v>
       </c>
       <c r="C417" t="s" s="8">
-        <v>1611</v>
+        <v>1656</v>
       </c>
       <c r="E417" s="10">
         <v>4</v>
       </c>
       <c r="F417" t="s" s="11">
-        <v>1612</v>
+        <v>1657</v>
       </c>
       <c r="G417" t="s" s="12">
-        <v>1613</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="418">
@@ -15587,19 +15876,19 @@
         <v>699</v>
       </c>
       <c r="B418" t="s" s="7">
-        <v>1614</v>
+        <v>1659</v>
       </c>
       <c r="C418" t="s" s="8">
-        <v>1615</v>
+        <v>1660</v>
       </c>
       <c r="E418" s="10">
         <v>4</v>
       </c>
       <c r="F418" t="s" s="11">
-        <v>1616</v>
+        <v>1661</v>
       </c>
       <c r="G418" t="s" s="12">
-        <v>1617</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="419">
@@ -15607,19 +15896,19 @@
         <v>700</v>
       </c>
       <c r="B419" t="s" s="7">
-        <v>1618</v>
+        <v>1663</v>
       </c>
       <c r="C419" t="s" s="8">
-        <v>1619</v>
+        <v>1664</v>
       </c>
       <c r="E419" s="10">
         <v>4</v>
       </c>
       <c r="F419" t="s" s="11">
-        <v>1620</v>
+        <v>1665</v>
       </c>
       <c r="G419" t="s" s="12">
-        <v>1621</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="420">
@@ -15627,22 +15916,22 @@
         <v>701</v>
       </c>
       <c r="B420" t="s" s="7">
-        <v>1622</v>
+        <v>1667</v>
       </c>
       <c r="C420" t="s" s="8">
-        <v>1623</v>
+        <v>1668</v>
       </c>
       <c r="E420" s="10">
         <v>4</v>
       </c>
       <c r="F420" t="s" s="11">
-        <v>1624</v>
+        <v>1669</v>
       </c>
       <c r="G420" t="s" s="12">
-        <v>1625</v>
+        <v>1670</v>
       </c>
       <c r="H420" t="s" s="13">
-        <v>1626</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="421">
@@ -15650,19 +15939,19 @@
         <v>702</v>
       </c>
       <c r="B421" t="s" s="7">
-        <v>1627</v>
+        <v>1672</v>
       </c>
       <c r="C421" t="s" s="8">
-        <v>1628</v>
+        <v>1673</v>
       </c>
       <c r="E421" s="10">
         <v>4</v>
       </c>
       <c r="F421" t="s" s="11">
-        <v>1629</v>
+        <v>1674</v>
       </c>
       <c r="G421" t="s" s="12">
-        <v>1630</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="422">
@@ -15670,19 +15959,19 @@
         <v>703</v>
       </c>
       <c r="B422" t="s" s="7">
-        <v>1631</v>
+        <v>1676</v>
       </c>
       <c r="C422" t="s" s="8">
-        <v>1632</v>
+        <v>1677</v>
       </c>
       <c r="E422" s="10">
         <v>4</v>
       </c>
       <c r="F422" t="s" s="11">
-        <v>1633</v>
+        <v>1678</v>
       </c>
       <c r="G422" t="s" s="12">
-        <v>1634</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="423">
@@ -15690,19 +15979,19 @@
         <v>705</v>
       </c>
       <c r="B423" t="s" s="7">
-        <v>1635</v>
+        <v>1680</v>
       </c>
       <c r="C423" t="s" s="8">
-        <v>1636</v>
+        <v>1681</v>
       </c>
       <c r="E423" s="10">
         <v>11</v>
       </c>
       <c r="F423" t="s" s="11">
-        <v>1637</v>
+        <v>1682</v>
       </c>
       <c r="G423" t="s" s="12">
-        <v>1638</v>
+        <v>1683</v>
       </c>
       <c r="I423" s="14">
         <v>40</v>
@@ -15713,19 +16002,19 @@
         <v>706</v>
       </c>
       <c r="B424" t="s" s="7">
-        <v>1639</v>
+        <v>1684</v>
       </c>
       <c r="C424" t="s" s="8">
-        <v>1640</v>
+        <v>1685</v>
       </c>
       <c r="E424" s="10">
         <v>11</v>
       </c>
       <c r="F424" t="s" s="11">
-        <v>1641</v>
+        <v>1686</v>
       </c>
       <c r="G424" t="s" s="12">
-        <v>1642</v>
+        <v>1687</v>
       </c>
       <c r="I424" s="14">
         <v>40</v>
@@ -15736,19 +16025,19 @@
         <v>707</v>
       </c>
       <c r="B425" t="s" s="7">
-        <v>1643</v>
+        <v>1688</v>
       </c>
       <c r="C425" t="s" s="8">
-        <v>1644</v>
+        <v>1689</v>
       </c>
       <c r="E425" s="10">
         <v>11</v>
       </c>
       <c r="F425" t="s" s="11">
-        <v>1645</v>
+        <v>1690</v>
       </c>
       <c r="G425" t="s" s="12">
-        <v>1646</v>
+        <v>1691</v>
       </c>
       <c r="I425" s="14">
         <v>40</v>
@@ -15759,19 +16048,19 @@
         <v>708</v>
       </c>
       <c r="B426" t="s" s="7">
-        <v>1647</v>
+        <v>1692</v>
       </c>
       <c r="C426" t="s" s="8">
-        <v>1648</v>
+        <v>1693</v>
       </c>
       <c r="E426" s="10">
         <v>11</v>
       </c>
       <c r="F426" t="s" s="11">
-        <v>1649</v>
+        <v>1694</v>
       </c>
       <c r="G426" t="s" s="12">
-        <v>1650</v>
+        <v>1695</v>
       </c>
       <c r="I426" s="14">
         <v>40</v>
@@ -15782,19 +16071,19 @@
         <v>709</v>
       </c>
       <c r="B427" t="s" s="7">
-        <v>1651</v>
+        <v>1696</v>
       </c>
       <c r="C427" t="s" s="8">
-        <v>1652</v>
+        <v>1697</v>
       </c>
       <c r="E427" s="10">
         <v>11</v>
       </c>
       <c r="F427" t="s" s="11">
-        <v>1653</v>
+        <v>1698</v>
       </c>
       <c r="G427" t="s" s="12">
-        <v>1654</v>
+        <v>1699</v>
       </c>
       <c r="I427" s="14">
         <v>40</v>
@@ -15805,19 +16094,19 @@
         <v>710</v>
       </c>
       <c r="B428" t="s" s="7">
-        <v>1655</v>
+        <v>1700</v>
       </c>
       <c r="C428" t="s" s="8">
-        <v>1656</v>
+        <v>1701</v>
       </c>
       <c r="E428" s="10">
         <v>11</v>
       </c>
       <c r="F428" t="s" s="11">
-        <v>1657</v>
+        <v>1702</v>
       </c>
       <c r="G428" t="s" s="12">
-        <v>1658</v>
+        <v>1703</v>
       </c>
       <c r="I428" s="14">
         <v>40</v>
@@ -15828,19 +16117,19 @@
         <v>711</v>
       </c>
       <c r="B429" t="s" s="7">
-        <v>1659</v>
+        <v>1704</v>
       </c>
       <c r="C429" t="s" s="8">
-        <v>1660</v>
+        <v>1705</v>
       </c>
       <c r="E429" s="10">
         <v>11</v>
       </c>
       <c r="F429" t="s" s="11">
-        <v>1661</v>
+        <v>1706</v>
       </c>
       <c r="G429" t="s" s="12">
-        <v>1662</v>
+        <v>1707</v>
       </c>
       <c r="I429" s="14">
         <v>40</v>
@@ -15851,19 +16140,19 @@
         <v>712</v>
       </c>
       <c r="B430" t="s" s="7">
-        <v>1663</v>
+        <v>1708</v>
       </c>
       <c r="C430" t="s" s="8">
-        <v>1664</v>
+        <v>1709</v>
       </c>
       <c r="E430" s="10">
         <v>11</v>
       </c>
       <c r="F430" t="s" s="11">
-        <v>1665</v>
+        <v>1710</v>
       </c>
       <c r="G430" t="s" s="12">
-        <v>1666</v>
+        <v>1711</v>
       </c>
       <c r="I430" s="14">
         <v>40</v>
@@ -15874,19 +16163,19 @@
         <v>713</v>
       </c>
       <c r="B431" t="s" s="7">
-        <v>1667</v>
+        <v>1712</v>
       </c>
       <c r="C431" t="s" s="8">
-        <v>1668</v>
+        <v>1713</v>
       </c>
       <c r="E431" s="10">
         <v>11</v>
       </c>
       <c r="F431" t="s" s="11">
-        <v>1669</v>
+        <v>1714</v>
       </c>
       <c r="G431" t="s" s="12">
-        <v>1670</v>
+        <v>1715</v>
       </c>
       <c r="I431" s="14">
         <v>40</v>
@@ -15897,19 +16186,19 @@
         <v>714</v>
       </c>
       <c r="B432" t="s" s="7">
-        <v>1671</v>
+        <v>1716</v>
       </c>
       <c r="C432" t="s" s="8">
-        <v>1672</v>
+        <v>1717</v>
       </c>
       <c r="E432" s="10">
         <v>9</v>
       </c>
       <c r="F432" t="s" s="11">
-        <v>1673</v>
+        <v>1718</v>
       </c>
       <c r="G432" t="s" s="12">
-        <v>1674</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="433">
@@ -15917,19 +16206,19 @@
         <v>715</v>
       </c>
       <c r="B433" t="s" s="7">
-        <v>1675</v>
+        <v>1720</v>
       </c>
       <c r="C433" t="s" s="8">
-        <v>1676</v>
+        <v>1721</v>
       </c>
       <c r="E433" s="10">
         <v>9</v>
       </c>
       <c r="F433" t="s" s="11">
-        <v>1677</v>
+        <v>1722</v>
       </c>
       <c r="G433" t="s" s="12">
-        <v>1678</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="434">
@@ -15937,19 +16226,19 @@
         <v>716</v>
       </c>
       <c r="B434" t="s" s="7">
-        <v>1679</v>
+        <v>1724</v>
       </c>
       <c r="C434" t="s" s="8">
-        <v>1680</v>
+        <v>1725</v>
       </c>
       <c r="E434" s="10">
         <v>9</v>
       </c>
       <c r="F434" t="s" s="11">
-        <v>1681</v>
+        <v>1726</v>
       </c>
       <c r="G434" t="s" s="12">
-        <v>1682</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="435">
@@ -15957,19 +16246,19 @@
         <v>717</v>
       </c>
       <c r="B435" t="s" s="7">
-        <v>1683</v>
+        <v>1728</v>
       </c>
       <c r="C435" t="s" s="8">
-        <v>1684</v>
+        <v>1729</v>
       </c>
       <c r="E435" s="10">
         <v>9</v>
       </c>
       <c r="F435" t="s" s="11">
-        <v>1685</v>
+        <v>1730</v>
       </c>
       <c r="G435" t="s" s="12">
-        <v>1686</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="436">
@@ -15977,19 +16266,19 @@
         <v>718</v>
       </c>
       <c r="B436" t="s" s="7">
-        <v>1687</v>
+        <v>1732</v>
       </c>
       <c r="C436" t="s" s="8">
-        <v>1688</v>
+        <v>1733</v>
       </c>
       <c r="E436" s="10">
         <v>9</v>
       </c>
       <c r="F436" t="s" s="11">
-        <v>1689</v>
+        <v>1734</v>
       </c>
       <c r="G436" t="s" s="12">
-        <v>1690</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="437">
@@ -15997,19 +16286,19 @@
         <v>719</v>
       </c>
       <c r="B437" t="s" s="7">
-        <v>1691</v>
+        <v>1736</v>
       </c>
       <c r="C437" t="s" s="8">
-        <v>1692</v>
+        <v>1737</v>
       </c>
       <c r="E437" s="10">
         <v>9</v>
       </c>
       <c r="F437" t="s" s="11">
-        <v>1693</v>
+        <v>1738</v>
       </c>
       <c r="G437" t="s" s="12">
-        <v>1694</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="438">
@@ -16017,19 +16306,19 @@
         <v>720</v>
       </c>
       <c r="B438" t="s" s="7">
-        <v>1695</v>
+        <v>1740</v>
       </c>
       <c r="C438" t="s" s="8">
-        <v>1696</v>
+        <v>1741</v>
       </c>
       <c r="E438" s="10">
         <v>9</v>
       </c>
       <c r="F438" t="s" s="11">
-        <v>1697</v>
+        <v>1742</v>
       </c>
       <c r="G438" t="s" s="12">
-        <v>1698</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="439">
@@ -16037,19 +16326,19 @@
         <v>721</v>
       </c>
       <c r="B439" t="s" s="7">
-        <v>1699</v>
+        <v>1744</v>
       </c>
       <c r="C439" t="s" s="8">
-        <v>1700</v>
+        <v>1745</v>
       </c>
       <c r="E439" s="10">
         <v>9</v>
       </c>
       <c r="F439" t="s" s="11">
-        <v>1701</v>
+        <v>1746</v>
       </c>
       <c r="G439" t="s" s="12">
-        <v>1702</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="440">
@@ -16057,19 +16346,19 @@
         <v>723</v>
       </c>
       <c r="B440" t="s" s="7">
-        <v>1703</v>
+        <v>1748</v>
       </c>
       <c r="C440" t="s" s="8">
-        <v>1704</v>
+        <v>1749</v>
       </c>
       <c r="E440" s="10">
         <v>9</v>
       </c>
       <c r="F440" t="s" s="11">
-        <v>1705</v>
+        <v>1750</v>
       </c>
       <c r="G440" t="s" s="12">
-        <v>1706</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="441">
@@ -16077,19 +16366,19 @@
         <v>724</v>
       </c>
       <c r="B441" t="s" s="7">
-        <v>1707</v>
+        <v>1752</v>
       </c>
       <c r="C441" t="s" s="8">
-        <v>1708</v>
+        <v>1753</v>
       </c>
       <c r="E441" s="10">
         <v>9</v>
       </c>
       <c r="F441" t="s" s="11">
-        <v>1709</v>
+        <v>1754</v>
       </c>
       <c r="G441" t="s" s="12">
-        <v>1710</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="442">
@@ -16097,19 +16386,19 @@
         <v>725</v>
       </c>
       <c r="B442" t="s" s="7">
-        <v>1711</v>
+        <v>1756</v>
       </c>
       <c r="C442" t="s" s="8">
-        <v>1712</v>
+        <v>1757</v>
       </c>
       <c r="E442" s="10">
         <v>9</v>
       </c>
       <c r="F442" t="s" s="11">
-        <v>1713</v>
+        <v>1758</v>
       </c>
       <c r="G442" t="s" s="12">
-        <v>1714</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="443">
@@ -16117,16 +16406,16 @@
         <v>726</v>
       </c>
       <c r="B443" t="s" s="7">
-        <v>1715</v>
+        <v>1760</v>
       </c>
       <c r="E443" s="10">
         <v>2</v>
       </c>
       <c r="F443" t="s" s="11">
-        <v>1716</v>
+        <v>1761</v>
       </c>
       <c r="G443" t="s" s="12">
-        <v>1717</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="444">
@@ -16134,16 +16423,16 @@
         <v>727</v>
       </c>
       <c r="B444" t="s" s="7">
-        <v>1718</v>
+        <v>1763</v>
       </c>
       <c r="E444" s="10">
         <v>2</v>
       </c>
       <c r="F444" t="s" s="11">
-        <v>1719</v>
+        <v>1764</v>
       </c>
       <c r="G444" t="s" s="12">
-        <v>1720</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="445">
@@ -16151,16 +16440,16 @@
         <v>728</v>
       </c>
       <c r="B445" t="s" s="7">
-        <v>1721</v>
+        <v>1766</v>
       </c>
       <c r="E445" s="10">
         <v>2</v>
       </c>
       <c r="F445" t="s" s="11">
-        <v>1722</v>
+        <v>1767</v>
       </c>
       <c r="G445" t="s" s="12">
-        <v>1723</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="446">
@@ -16168,16 +16457,16 @@
         <v>729</v>
       </c>
       <c r="B446" t="s" s="7">
-        <v>1724</v>
+        <v>1769</v>
       </c>
       <c r="E446" s="10">
         <v>2</v>
       </c>
       <c r="F446" t="s" s="11">
-        <v>1725</v>
+        <v>1770</v>
       </c>
       <c r="G446" t="s" s="12">
-        <v>1726</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="447">
@@ -16185,16 +16474,16 @@
         <v>730</v>
       </c>
       <c r="B447" t="s" s="7">
-        <v>1727</v>
+        <v>1772</v>
       </c>
       <c r="E447" s="10">
         <v>2</v>
       </c>
       <c r="F447" t="s" s="11">
-        <v>1728</v>
+        <v>1773</v>
       </c>
       <c r="G447" t="s" s="12">
-        <v>1729</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="448">
@@ -16202,16 +16491,16 @@
         <v>731</v>
       </c>
       <c r="B448" t="s" s="7">
-        <v>1730</v>
+        <v>1775</v>
       </c>
       <c r="E448" s="10">
         <v>2</v>
       </c>
       <c r="F448" t="s" s="11">
-        <v>1731</v>
+        <v>1776</v>
       </c>
       <c r="G448" t="s" s="12">
-        <v>1732</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="449">
@@ -16219,16 +16508,16 @@
         <v>732</v>
       </c>
       <c r="B449" t="s" s="7">
-        <v>1733</v>
+        <v>1778</v>
       </c>
       <c r="E449" s="10">
         <v>2</v>
       </c>
       <c r="F449" t="s" s="11">
-        <v>1734</v>
+        <v>1779</v>
       </c>
       <c r="G449" t="s" s="12">
-        <v>1735</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="450">
@@ -16236,16 +16525,16 @@
         <v>733</v>
       </c>
       <c r="B450" t="s" s="7">
-        <v>1736</v>
+        <v>1781</v>
       </c>
       <c r="E450" s="10">
         <v>2</v>
       </c>
       <c r="F450" t="s" s="11">
-        <v>1737</v>
+        <v>1782</v>
       </c>
       <c r="G450" t="s" s="12">
-        <v>1738</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="451">
@@ -16253,16 +16542,16 @@
         <v>734</v>
       </c>
       <c r="B451" t="s" s="7">
-        <v>1739</v>
+        <v>1784</v>
       </c>
       <c r="E451" s="10">
         <v>2</v>
       </c>
       <c r="F451" t="s" s="11">
-        <v>1740</v>
+        <v>1785</v>
       </c>
       <c r="G451" t="s" s="12">
-        <v>1741</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="452">
@@ -16270,16 +16559,16 @@
         <v>735</v>
       </c>
       <c r="B452" t="s" s="7">
-        <v>1742</v>
+        <v>1787</v>
       </c>
       <c r="E452" s="10">
         <v>2</v>
       </c>
       <c r="F452" t="s" s="11">
-        <v>1743</v>
+        <v>1788</v>
       </c>
       <c r="G452" t="s" s="12">
-        <v>1744</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="453">
@@ -16287,16 +16576,16 @@
         <v>736</v>
       </c>
       <c r="B453" t="s" s="7">
-        <v>1745</v>
+        <v>1790</v>
       </c>
       <c r="E453" s="10">
         <v>2</v>
       </c>
       <c r="F453" t="s" s="11">
-        <v>1746</v>
+        <v>1791</v>
       </c>
       <c r="G453" t="s" s="12">
-        <v>1747</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="454">
@@ -16304,16 +16593,16 @@
         <v>737</v>
       </c>
       <c r="B454" t="s" s="7">
-        <v>1748</v>
+        <v>1793</v>
       </c>
       <c r="E454" s="10">
         <v>2</v>
       </c>
       <c r="F454" t="s" s="11">
-        <v>1749</v>
+        <v>1794</v>
       </c>
       <c r="G454" t="s" s="12">
-        <v>1750</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="455">
@@ -16321,19 +16610,19 @@
         <v>738</v>
       </c>
       <c r="B455" t="s" s="7">
-        <v>1751</v>
+        <v>1796</v>
       </c>
       <c r="C455" t="s" s="8">
-        <v>1752</v>
+        <v>1797</v>
       </c>
       <c r="E455" s="10">
         <v>12</v>
       </c>
       <c r="F455" t="s" s="11">
-        <v>1753</v>
+        <v>1798</v>
       </c>
       <c r="G455" t="s" s="12">
-        <v>1754</v>
+        <v>1799</v>
       </c>
       <c r="I455" s="14">
         <v>34</v>
@@ -16344,19 +16633,19 @@
         <v>739</v>
       </c>
       <c r="B456" t="s" s="7">
-        <v>1755</v>
+        <v>1800</v>
       </c>
       <c r="C456" t="s" s="8">
-        <v>1756</v>
+        <v>1801</v>
       </c>
       <c r="E456" s="10">
         <v>12</v>
       </c>
       <c r="F456" t="s" s="11">
-        <v>1757</v>
+        <v>1802</v>
       </c>
       <c r="G456" t="s" s="12">
-        <v>1758</v>
+        <v>1803</v>
       </c>
       <c r="I456" s="14">
         <v>34</v>
@@ -16367,19 +16656,19 @@
         <v>740</v>
       </c>
       <c r="B457" t="s" s="7">
-        <v>1759</v>
+        <v>1804</v>
       </c>
       <c r="C457" t="s" s="8">
-        <v>1760</v>
+        <v>1805</v>
       </c>
       <c r="E457" s="10">
         <v>12</v>
       </c>
       <c r="F457" t="s" s="11">
-        <v>1761</v>
+        <v>1806</v>
       </c>
       <c r="G457" t="s" s="12">
-        <v>1762</v>
+        <v>1807</v>
       </c>
       <c r="I457" s="14">
         <v>34</v>
@@ -16390,19 +16679,19 @@
         <v>741</v>
       </c>
       <c r="B458" t="s" s="7">
-        <v>1763</v>
+        <v>1808</v>
       </c>
       <c r="C458" t="s" s="8">
-        <v>1764</v>
+        <v>1809</v>
       </c>
       <c r="E458" s="10">
         <v>12</v>
       </c>
       <c r="F458" t="s" s="11">
-        <v>1765</v>
+        <v>1810</v>
       </c>
       <c r="G458" t="s" s="12">
-        <v>1766</v>
+        <v>1811</v>
       </c>
       <c r="I458" s="14">
         <v>34</v>
@@ -16413,19 +16702,19 @@
         <v>742</v>
       </c>
       <c r="B459" t="s" s="7">
-        <v>1767</v>
+        <v>1812</v>
       </c>
       <c r="C459" t="s" s="8">
-        <v>1768</v>
+        <v>1813</v>
       </c>
       <c r="E459" s="10">
         <v>12</v>
       </c>
       <c r="F459" t="s" s="11">
-        <v>1769</v>
+        <v>1814</v>
       </c>
       <c r="G459" t="s" s="12">
-        <v>1770</v>
+        <v>1815</v>
       </c>
       <c r="I459" s="14">
         <v>34</v>
@@ -16436,19 +16725,19 @@
         <v>743</v>
       </c>
       <c r="B460" t="s" s="7">
-        <v>1771</v>
+        <v>1816</v>
       </c>
       <c r="C460" t="s" s="8">
-        <v>1772</v>
+        <v>1817</v>
       </c>
       <c r="E460" s="10">
         <v>12</v>
       </c>
       <c r="F460" t="s" s="11">
-        <v>1773</v>
+        <v>1818</v>
       </c>
       <c r="G460" t="s" s="12">
-        <v>1774</v>
+        <v>1819</v>
       </c>
       <c r="I460" s="14">
         <v>34</v>
@@ -16459,19 +16748,19 @@
         <v>744</v>
       </c>
       <c r="B461" t="s" s="7">
-        <v>1775</v>
+        <v>1820</v>
       </c>
       <c r="C461" t="s" s="8">
-        <v>1776</v>
+        <v>1821</v>
       </c>
       <c r="E461" s="10">
         <v>12</v>
       </c>
       <c r="F461" t="s" s="11">
-        <v>1777</v>
+        <v>1822</v>
       </c>
       <c r="G461" t="s" s="12">
-        <v>1778</v>
+        <v>1823</v>
       </c>
       <c r="I461" s="14">
         <v>34</v>
@@ -16482,19 +16771,19 @@
         <v>745</v>
       </c>
       <c r="B462" t="s" s="7">
-        <v>1779</v>
+        <v>1824</v>
       </c>
       <c r="C462" t="s" s="8">
-        <v>1780</v>
+        <v>1825</v>
       </c>
       <c r="E462" s="10">
         <v>12</v>
       </c>
       <c r="F462" t="s" s="11">
-        <v>1781</v>
+        <v>1826</v>
       </c>
       <c r="G462" t="s" s="12">
-        <v>1782</v>
+        <v>1827</v>
       </c>
       <c r="I462" s="14">
         <v>34</v>
@@ -16505,19 +16794,19 @@
         <v>746</v>
       </c>
       <c r="B463" t="s" s="7">
-        <v>1783</v>
+        <v>1828</v>
       </c>
       <c r="C463" t="s" s="8">
-        <v>1784</v>
+        <v>1829</v>
       </c>
       <c r="E463" s="10">
         <v>12</v>
       </c>
       <c r="F463" t="s" s="11">
-        <v>1785</v>
+        <v>1830</v>
       </c>
       <c r="G463" t="s" s="12">
-        <v>1786</v>
+        <v>1831</v>
       </c>
       <c r="I463" s="14">
         <v>34</v>
@@ -16528,19 +16817,19 @@
         <v>747</v>
       </c>
       <c r="B464" t="s" s="7">
-        <v>1787</v>
+        <v>1832</v>
       </c>
       <c r="C464" t="s" s="8">
-        <v>1788</v>
+        <v>1833</v>
       </c>
       <c r="E464" s="10">
         <v>12</v>
       </c>
       <c r="F464" t="s" s="11">
-        <v>1789</v>
+        <v>1834</v>
       </c>
       <c r="G464" t="s" s="12">
-        <v>1790</v>
+        <v>1835</v>
       </c>
       <c r="I464" s="14">
         <v>34</v>
@@ -16551,19 +16840,19 @@
         <v>748</v>
       </c>
       <c r="B465" t="s" s="7">
-        <v>1791</v>
+        <v>1836</v>
       </c>
       <c r="C465" t="s" s="8">
-        <v>1792</v>
+        <v>1837</v>
       </c>
       <c r="E465" s="10">
         <v>12</v>
       </c>
       <c r="F465" t="s" s="11">
-        <v>1793</v>
+        <v>1838</v>
       </c>
       <c r="G465" t="s" s="12">
-        <v>1794</v>
+        <v>1839</v>
       </c>
       <c r="I465" s="14">
         <v>34</v>
@@ -16574,19 +16863,19 @@
         <v>749</v>
       </c>
       <c r="B466" t="s" s="7">
-        <v>1795</v>
+        <v>1840</v>
       </c>
       <c r="C466" t="s" s="8">
-        <v>1796</v>
+        <v>1841</v>
       </c>
       <c r="E466" s="10">
         <v>12</v>
       </c>
       <c r="F466" t="s" s="11">
-        <v>1797</v>
+        <v>1842</v>
       </c>
       <c r="G466" t="s" s="12">
-        <v>1798</v>
+        <v>1843</v>
       </c>
       <c r="I466" s="14">
         <v>34</v>
@@ -16597,7 +16886,7 @@
         <v>751</v>
       </c>
       <c r="B467" t="s" s="7">
-        <v>1799</v>
+        <v>1844</v>
       </c>
       <c r="D467" s="9">
         <v>225</v>
@@ -16606,7 +16895,7 @@
         <v>10</v>
       </c>
       <c r="F467" t="s" s="11">
-        <v>1800</v>
+        <v>1845</v>
       </c>
       <c r="G467" t="s" s="12">
         <v>720</v>
@@ -16617,7 +16906,7 @@
         <v>752</v>
       </c>
       <c r="B468" t="s" s="7">
-        <v>1801</v>
+        <v>1846</v>
       </c>
       <c r="D468" s="9">
         <v>225</v>
@@ -16626,7 +16915,7 @@
         <v>10</v>
       </c>
       <c r="F468" t="s" s="11">
-        <v>1802</v>
+        <v>1847</v>
       </c>
       <c r="G468" t="s" s="12">
         <v>724</v>
@@ -16637,7 +16926,7 @@
         <v>753</v>
       </c>
       <c r="B469" t="s" s="7">
-        <v>1803</v>
+        <v>1848</v>
       </c>
       <c r="D469" s="9">
         <v>225</v>
@@ -16646,7 +16935,7 @@
         <v>10</v>
       </c>
       <c r="F469" t="s" s="11">
-        <v>1804</v>
+        <v>1849</v>
       </c>
       <c r="G469" t="s" s="12">
         <v>728</v>
@@ -16657,7 +16946,7 @@
         <v>754</v>
       </c>
       <c r="B470" t="s" s="7">
-        <v>1805</v>
+        <v>1850</v>
       </c>
       <c r="D470" s="9">
         <v>225</v>
@@ -16666,7 +16955,7 @@
         <v>10</v>
       </c>
       <c r="F470" t="s" s="11">
-        <v>1806</v>
+        <v>1851</v>
       </c>
       <c r="G470" t="s" s="12">
         <v>732</v>
@@ -16677,7 +16966,7 @@
         <v>755</v>
       </c>
       <c r="B471" t="s" s="7">
-        <v>1807</v>
+        <v>1852</v>
       </c>
       <c r="D471" s="9">
         <v>225</v>
@@ -16686,7 +16975,7 @@
         <v>10</v>
       </c>
       <c r="F471" t="s" s="11">
-        <v>1808</v>
+        <v>1853</v>
       </c>
       <c r="G471" t="s" s="12">
         <v>736</v>
@@ -16697,7 +16986,7 @@
         <v>757</v>
       </c>
       <c r="B472" t="s" s="7">
-        <v>1809</v>
+        <v>1854</v>
       </c>
       <c r="D472" s="9">
         <v>225</v>
@@ -16706,7 +16995,7 @@
         <v>10</v>
       </c>
       <c r="F472" t="s" s="11">
-        <v>1810</v>
+        <v>1855</v>
       </c>
       <c r="G472" t="s" s="12">
         <v>744</v>
@@ -16717,7 +17006,7 @@
         <v>758</v>
       </c>
       <c r="B473" t="s" s="7">
-        <v>1811</v>
+        <v>1856</v>
       </c>
       <c r="D473" s="9">
         <v>225</v>
@@ -16726,7 +17015,7 @@
         <v>10</v>
       </c>
       <c r="F473" t="s" s="11">
-        <v>1812</v>
+        <v>1857</v>
       </c>
       <c r="G473" t="s" s="12">
         <v>748</v>
@@ -16737,7 +17026,7 @@
         <v>759</v>
       </c>
       <c r="B474" t="s" s="7">
-        <v>1813</v>
+        <v>1858</v>
       </c>
       <c r="D474" s="9">
         <v>225</v>
@@ -16746,7 +17035,7 @@
         <v>10</v>
       </c>
       <c r="F474" t="s" s="11">
-        <v>1814</v>
+        <v>1859</v>
       </c>
       <c r="G474" t="s" s="12">
         <v>662</v>
@@ -16757,7 +17046,7 @@
         <v>760</v>
       </c>
       <c r="B475" t="s" s="7">
-        <v>1815</v>
+        <v>1860</v>
       </c>
       <c r="D475" s="9">
         <v>225</v>
@@ -16766,7 +17055,7 @@
         <v>10</v>
       </c>
       <c r="F475" t="s" s="11">
-        <v>1816</v>
+        <v>1861</v>
       </c>
       <c r="G475" t="s" s="12">
         <v>666</v>
@@ -16777,7 +17066,7 @@
         <v>761</v>
       </c>
       <c r="B476" t="s" s="7">
-        <v>1817</v>
+        <v>1862</v>
       </c>
       <c r="D476" s="9">
         <v>225</v>
@@ -16786,7 +17075,7 @@
         <v>10</v>
       </c>
       <c r="F476" t="s" s="11">
-        <v>1818</v>
+        <v>1863</v>
       </c>
       <c r="G476" t="s" s="12">
         <v>40</v>
@@ -16797,19 +17086,19 @@
         <v>762</v>
       </c>
       <c r="B477" t="s" s="7">
-        <v>1819</v>
+        <v>1864</v>
       </c>
       <c r="C477" t="s" s="8">
-        <v>1820</v>
+        <v>1865</v>
       </c>
       <c r="E477" s="10">
         <v>13</v>
       </c>
       <c r="F477" t="s" s="11">
-        <v>1821</v>
+        <v>1866</v>
       </c>
       <c r="G477" t="s" s="12">
-        <v>1822</v>
+        <v>1867</v>
       </c>
       <c r="I477" s="14">
         <v>352</v>
@@ -16820,19 +17109,19 @@
         <v>763</v>
       </c>
       <c r="B478" t="s" s="7">
-        <v>1823</v>
+        <v>1868</v>
       </c>
       <c r="C478" t="s" s="8">
-        <v>1824</v>
+        <v>1869</v>
       </c>
       <c r="E478" s="10">
         <v>13</v>
       </c>
       <c r="F478" t="s" s="11">
-        <v>1825</v>
+        <v>1870</v>
       </c>
       <c r="G478" t="s" s="12">
-        <v>1826</v>
+        <v>1871</v>
       </c>
       <c r="I478" s="14">
         <v>352</v>
@@ -16843,19 +17132,19 @@
         <v>764</v>
       </c>
       <c r="B479" t="s" s="7">
-        <v>1827</v>
+        <v>1872</v>
       </c>
       <c r="C479" t="s" s="8">
-        <v>1828</v>
+        <v>1873</v>
       </c>
       <c r="E479" s="10">
         <v>13</v>
       </c>
       <c r="F479" t="s" s="11">
-        <v>1829</v>
+        <v>1874</v>
       </c>
       <c r="G479" t="s" s="12">
-        <v>1830</v>
+        <v>1875</v>
       </c>
       <c r="I479" s="14">
         <v>352</v>
@@ -16866,19 +17155,19 @@
         <v>765</v>
       </c>
       <c r="B480" t="s" s="7">
-        <v>1831</v>
+        <v>1876</v>
       </c>
       <c r="C480" t="s" s="8">
-        <v>1832</v>
+        <v>1877</v>
       </c>
       <c r="E480" s="10">
         <v>13</v>
       </c>
       <c r="F480" t="s" s="11">
-        <v>1833</v>
+        <v>1878</v>
       </c>
       <c r="G480" t="s" s="12">
-        <v>1834</v>
+        <v>1879</v>
       </c>
       <c r="I480" s="14">
         <v>352</v>
@@ -16889,19 +17178,19 @@
         <v>766</v>
       </c>
       <c r="B481" t="s" s="7">
-        <v>1835</v>
+        <v>1880</v>
       </c>
       <c r="C481" t="s" s="8">
-        <v>1836</v>
+        <v>1881</v>
       </c>
       <c r="E481" s="10">
         <v>13</v>
       </c>
       <c r="F481" t="s" s="11">
-        <v>1837</v>
+        <v>1882</v>
       </c>
       <c r="G481" t="s" s="12">
-        <v>1838</v>
+        <v>1883</v>
       </c>
       <c r="I481" s="14">
         <v>352</v>
@@ -16912,19 +17201,19 @@
         <v>767</v>
       </c>
       <c r="B482" t="s" s="7">
-        <v>1839</v>
+        <v>1884</v>
       </c>
       <c r="C482" t="s" s="8">
-        <v>1840</v>
+        <v>1885</v>
       </c>
       <c r="E482" s="10">
         <v>13</v>
       </c>
       <c r="F482" t="s" s="11">
-        <v>1841</v>
+        <v>1886</v>
       </c>
       <c r="G482" t="s" s="12">
-        <v>1842</v>
+        <v>1887</v>
       </c>
       <c r="I482" s="14">
         <v>352</v>
@@ -16935,19 +17224,19 @@
         <v>768</v>
       </c>
       <c r="B483" t="s" s="7">
-        <v>1843</v>
+        <v>1888</v>
       </c>
       <c r="C483" t="s" s="8">
-        <v>1844</v>
+        <v>1889</v>
       </c>
       <c r="E483" s="10">
         <v>13</v>
       </c>
       <c r="F483" t="s" s="11">
-        <v>1845</v>
+        <v>1890</v>
       </c>
       <c r="G483" t="s" s="12">
-        <v>1846</v>
+        <v>1891</v>
       </c>
       <c r="I483" s="14">
         <v>352</v>
@@ -16958,19 +17247,19 @@
         <v>769</v>
       </c>
       <c r="B484" t="s" s="7">
-        <v>1847</v>
+        <v>1892</v>
       </c>
       <c r="C484" t="s" s="8">
-        <v>1848</v>
+        <v>1893</v>
       </c>
       <c r="E484" s="10">
         <v>13</v>
       </c>
       <c r="F484" t="s" s="11">
-        <v>1849</v>
+        <v>1894</v>
       </c>
       <c r="G484" t="s" s="12">
-        <v>1850</v>
+        <v>1895</v>
       </c>
       <c r="I484" s="14">
         <v>352</v>
@@ -16981,19 +17270,19 @@
         <v>770</v>
       </c>
       <c r="B485" t="s" s="7">
-        <v>1851</v>
+        <v>1896</v>
       </c>
       <c r="C485" t="s" s="8">
-        <v>1852</v>
+        <v>1897</v>
       </c>
       <c r="E485" s="10">
         <v>13</v>
       </c>
       <c r="F485" t="s" s="11">
-        <v>1853</v>
+        <v>1898</v>
       </c>
       <c r="G485" t="s" s="12">
-        <v>1854</v>
+        <v>1899</v>
       </c>
       <c r="I485" s="14">
         <v>352</v>
@@ -17004,19 +17293,19 @@
         <v>771</v>
       </c>
       <c r="B486" t="s" s="7">
-        <v>1855</v>
+        <v>1900</v>
       </c>
       <c r="C486" t="s" s="8">
-        <v>1856</v>
+        <v>1901</v>
       </c>
       <c r="E486" s="10">
         <v>13</v>
       </c>
       <c r="F486" t="s" s="11">
-        <v>1857</v>
+        <v>1902</v>
       </c>
       <c r="G486" t="s" s="12">
-        <v>1858</v>
+        <v>1903</v>
       </c>
       <c r="I486" s="14">
         <v>352</v>
@@ -17027,19 +17316,19 @@
         <v>772</v>
       </c>
       <c r="B487" t="s" s="7">
-        <v>1859</v>
+        <v>1904</v>
       </c>
       <c r="C487" t="s" s="8">
-        <v>1860</v>
+        <v>1905</v>
       </c>
       <c r="E487" s="10">
         <v>13</v>
       </c>
       <c r="F487" t="s" s="11">
-        <v>1861</v>
+        <v>1906</v>
       </c>
       <c r="G487" t="s" s="12">
-        <v>1862</v>
+        <v>1907</v>
       </c>
       <c r="I487" s="14">
         <v>352</v>
@@ -17050,19 +17339,19 @@
         <v>773</v>
       </c>
       <c r="B488" t="s" s="7">
-        <v>1863</v>
+        <v>1908</v>
       </c>
       <c r="C488" t="s" s="8">
-        <v>1864</v>
+        <v>1909</v>
       </c>
       <c r="E488" s="10">
         <v>13</v>
       </c>
       <c r="F488" t="s" s="11">
-        <v>1865</v>
+        <v>1910</v>
       </c>
       <c r="G488" t="s" s="12">
-        <v>1866</v>
+        <v>1911</v>
       </c>
       <c r="I488" s="14">
         <v>352</v>
@@ -17073,19 +17362,19 @@
         <v>774</v>
       </c>
       <c r="B489" t="s" s="7">
-        <v>1867</v>
+        <v>1912</v>
       </c>
       <c r="C489" t="s" s="8">
-        <v>1868</v>
+        <v>1913</v>
       </c>
       <c r="E489" s="10">
         <v>13</v>
       </c>
       <c r="F489" t="s" s="11">
-        <v>1869</v>
+        <v>1914</v>
       </c>
       <c r="G489" t="s" s="12">
-        <v>1870</v>
+        <v>1915</v>
       </c>
       <c r="I489" s="14">
         <v>352</v>
@@ -17096,19 +17385,19 @@
         <v>775</v>
       </c>
       <c r="B490" t="s" s="7">
-        <v>1871</v>
+        <v>1916</v>
       </c>
       <c r="C490" t="s" s="8">
-        <v>1872</v>
+        <v>1917</v>
       </c>
       <c r="E490" s="10">
         <v>13</v>
       </c>
       <c r="F490" t="s" s="11">
-        <v>1873</v>
+        <v>1918</v>
       </c>
       <c r="G490" t="s" s="12">
-        <v>1874</v>
+        <v>1919</v>
       </c>
       <c r="I490" s="14">
         <v>352</v>
@@ -17119,19 +17408,19 @@
         <v>776</v>
       </c>
       <c r="B491" t="s" s="7">
-        <v>1875</v>
+        <v>1920</v>
       </c>
       <c r="C491" t="s" s="8">
-        <v>1876</v>
+        <v>1921</v>
       </c>
       <c r="E491" s="10">
         <v>13</v>
       </c>
       <c r="F491" t="s" s="11">
-        <v>1877</v>
+        <v>1922</v>
       </c>
       <c r="G491" t="s" s="12">
-        <v>1878</v>
+        <v>1923</v>
       </c>
       <c r="I491" s="14">
         <v>352</v>
@@ -17142,19 +17431,19 @@
         <v>777</v>
       </c>
       <c r="B492" t="s" s="7">
-        <v>1879</v>
+        <v>1924</v>
       </c>
       <c r="C492" t="s" s="8">
-        <v>1880</v>
+        <v>1925</v>
       </c>
       <c r="E492" s="10">
         <v>13</v>
       </c>
       <c r="F492" t="s" s="11">
-        <v>1881</v>
+        <v>1926</v>
       </c>
       <c r="G492" t="s" s="12">
-        <v>1882</v>
+        <v>1927</v>
       </c>
       <c r="I492" s="14">
         <v>352</v>
@@ -17165,19 +17454,19 @@
         <v>778</v>
       </c>
       <c r="B493" t="s" s="7">
-        <v>1883</v>
+        <v>1928</v>
       </c>
       <c r="C493" t="s" s="8">
-        <v>1884</v>
+        <v>1929</v>
       </c>
       <c r="E493" s="10">
         <v>13</v>
       </c>
       <c r="F493" t="s" s="11">
-        <v>1885</v>
+        <v>1930</v>
       </c>
       <c r="G493" t="s" s="12">
-        <v>1886</v>
+        <v>1931</v>
       </c>
       <c r="I493" s="14">
         <v>352</v>
@@ -17188,22 +17477,22 @@
         <v>779</v>
       </c>
       <c r="B494" t="s" s="7">
-        <v>1887</v>
+        <v>1932</v>
       </c>
       <c r="C494" t="s" s="8">
-        <v>1888</v>
+        <v>1933</v>
       </c>
       <c r="E494" s="10">
         <v>13</v>
       </c>
       <c r="F494" t="s" s="11">
-        <v>1889</v>
+        <v>1934</v>
       </c>
       <c r="G494" t="s" s="12">
-        <v>1890</v>
+        <v>1935</v>
       </c>
       <c r="H494" t="s" s="13">
-        <v>1891</v>
+        <v>1936</v>
       </c>
       <c r="I494" s="14">
         <v>352</v>
@@ -17214,19 +17503,19 @@
         <v>780</v>
       </c>
       <c r="B495" t="s" s="7">
-        <v>1892</v>
+        <v>1937</v>
       </c>
       <c r="C495" t="s" s="8">
-        <v>1893</v>
+        <v>1938</v>
       </c>
       <c r="E495" s="10">
         <v>13</v>
       </c>
       <c r="F495" t="s" s="11">
-        <v>1894</v>
+        <v>1939</v>
       </c>
       <c r="G495" t="s" s="12">
-        <v>1895</v>
+        <v>1940</v>
       </c>
       <c r="I495" s="14">
         <v>352</v>
@@ -17237,10 +17526,10 @@
         <v>781</v>
       </c>
       <c r="B496" t="s" s="7">
-        <v>1896</v>
+        <v>1941</v>
       </c>
       <c r="C496" t="s" s="8">
-        <v>1897</v>
+        <v>1942</v>
       </c>
       <c r="D496" s="9">
         <v>225</v>
@@ -17249,10 +17538,10 @@
         <v>1</v>
       </c>
       <c r="F496" t="s" s="11">
-        <v>1898</v>
+        <v>1943</v>
       </c>
       <c r="G496" t="s" s="12">
-        <v>1899</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="497">
@@ -17260,19 +17549,19 @@
         <v>783</v>
       </c>
       <c r="B497" t="s" s="7">
-        <v>1900</v>
+        <v>1945</v>
       </c>
       <c r="C497" t="s" s="8">
-        <v>1901</v>
+        <v>1946</v>
       </c>
       <c r="E497" s="10">
         <v>12</v>
       </c>
       <c r="F497" t="s" s="11">
-        <v>1902</v>
+        <v>1947</v>
       </c>
       <c r="G497" t="s" s="12">
-        <v>1903</v>
+        <v>1948</v>
       </c>
       <c r="I497" s="14">
         <v>34</v>
@@ -17283,19 +17572,19 @@
         <v>784</v>
       </c>
       <c r="B498" t="s" s="7">
-        <v>1904</v>
+        <v>1949</v>
       </c>
       <c r="C498" t="s" s="8">
-        <v>1905</v>
+        <v>1950</v>
       </c>
       <c r="E498" s="10">
         <v>12</v>
       </c>
       <c r="F498" t="s" s="11">
-        <v>1906</v>
+        <v>1951</v>
       </c>
       <c r="G498" t="s" s="12">
-        <v>1907</v>
+        <v>1952</v>
       </c>
       <c r="I498" s="14">
         <v>34</v>
@@ -17306,19 +17595,19 @@
         <v>785</v>
       </c>
       <c r="B499" t="s" s="7">
-        <v>1908</v>
+        <v>1953</v>
       </c>
       <c r="C499" t="s" s="8">
-        <v>1909</v>
+        <v>1954</v>
       </c>
       <c r="E499" s="10">
         <v>12</v>
       </c>
       <c r="F499" t="s" s="11">
-        <v>1910</v>
+        <v>1955</v>
       </c>
       <c r="G499" t="s" s="12">
-        <v>1911</v>
+        <v>1956</v>
       </c>
       <c r="I499" s="14">
         <v>34</v>
@@ -17329,19 +17618,19 @@
         <v>786</v>
       </c>
       <c r="B500" t="s" s="7">
-        <v>1912</v>
+        <v>1957</v>
       </c>
       <c r="C500" t="s" s="8">
-        <v>1913</v>
+        <v>1958</v>
       </c>
       <c r="E500" s="10">
         <v>12</v>
       </c>
       <c r="F500" t="s" s="11">
-        <v>1914</v>
+        <v>1959</v>
       </c>
       <c r="G500" t="s" s="12">
-        <v>1915</v>
+        <v>1960</v>
       </c>
       <c r="I500" s="14">
         <v>34</v>
@@ -17352,19 +17641,19 @@
         <v>787</v>
       </c>
       <c r="B501" t="s" s="7">
-        <v>1916</v>
+        <v>1961</v>
       </c>
       <c r="C501" t="s" s="8">
-        <v>1917</v>
+        <v>1962</v>
       </c>
       <c r="E501" s="10">
         <v>12</v>
       </c>
       <c r="F501" t="s" s="11">
-        <v>1918</v>
+        <v>1963</v>
       </c>
       <c r="G501" t="s" s="12">
-        <v>1919</v>
+        <v>1964</v>
       </c>
       <c r="I501" s="14">
         <v>34</v>
@@ -17375,19 +17664,19 @@
         <v>788</v>
       </c>
       <c r="B502" t="s" s="7">
-        <v>1920</v>
+        <v>1965</v>
       </c>
       <c r="C502" t="s" s="8">
-        <v>1921</v>
+        <v>1966</v>
       </c>
       <c r="E502" s="10">
         <v>12</v>
       </c>
       <c r="F502" t="s" s="11">
-        <v>1922</v>
+        <v>1967</v>
       </c>
       <c r="G502" t="s" s="12">
-        <v>1923</v>
+        <v>1968</v>
       </c>
       <c r="I502" s="14">
         <v>34</v>
@@ -17398,19 +17687,19 @@
         <v>789</v>
       </c>
       <c r="B503" t="s" s="7">
-        <v>1924</v>
+        <v>1969</v>
       </c>
       <c r="C503" t="s" s="8">
-        <v>1925</v>
+        <v>1970</v>
       </c>
       <c r="E503" s="10">
         <v>12</v>
       </c>
       <c r="F503" t="s" s="11">
-        <v>1926</v>
+        <v>1971</v>
       </c>
       <c r="G503" t="s" s="12">
-        <v>1927</v>
+        <v>1972</v>
       </c>
       <c r="I503" s="14">
         <v>34</v>
@@ -17421,19 +17710,19 @@
         <v>790</v>
       </c>
       <c r="B504" t="s" s="7">
-        <v>1928</v>
+        <v>1973</v>
       </c>
       <c r="C504" t="s" s="8">
-        <v>1929</v>
+        <v>1974</v>
       </c>
       <c r="E504" s="10">
         <v>12</v>
       </c>
       <c r="F504" t="s" s="11">
-        <v>1930</v>
+        <v>1975</v>
       </c>
       <c r="G504" t="s" s="12">
-        <v>1931</v>
+        <v>1976</v>
       </c>
       <c r="I504" s="14">
         <v>34</v>
@@ -17444,19 +17733,19 @@
         <v>791</v>
       </c>
       <c r="B505" t="s" s="7">
-        <v>1932</v>
+        <v>1977</v>
       </c>
       <c r="C505" t="s" s="8">
-        <v>1933</v>
+        <v>1978</v>
       </c>
       <c r="E505" s="10">
         <v>14</v>
       </c>
       <c r="F505" t="s" s="11">
-        <v>1934</v>
+        <v>1979</v>
       </c>
       <c r="G505" t="s" s="12">
-        <v>1935</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="506">
@@ -17464,19 +17753,19 @@
         <v>792</v>
       </c>
       <c r="B506" t="s" s="7">
-        <v>1936</v>
+        <v>1981</v>
       </c>
       <c r="C506" t="s" s="8">
-        <v>1937</v>
+        <v>1982</v>
       </c>
       <c r="E506" s="10">
         <v>14</v>
       </c>
       <c r="F506" t="s" s="11">
-        <v>1938</v>
+        <v>1983</v>
       </c>
       <c r="G506" t="s" s="12">
-        <v>1939</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="507">
@@ -17484,19 +17773,19 @@
         <v>793</v>
       </c>
       <c r="B507" t="s" s="7">
-        <v>1940</v>
+        <v>1985</v>
       </c>
       <c r="C507" t="s" s="8">
-        <v>1941</v>
+        <v>1986</v>
       </c>
       <c r="E507" s="10">
         <v>14</v>
       </c>
       <c r="F507" t="s" s="11">
-        <v>1942</v>
+        <v>1987</v>
       </c>
       <c r="G507" t="s" s="12">
-        <v>1943</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="508">
@@ -17504,19 +17793,19 @@
         <v>794</v>
       </c>
       <c r="B508" t="s" s="7">
-        <v>1944</v>
+        <v>1989</v>
       </c>
       <c r="C508" t="s" s="8">
-        <v>1945</v>
+        <v>1990</v>
       </c>
       <c r="E508" s="10">
         <v>14</v>
       </c>
       <c r="F508" t="s" s="11">
-        <v>1946</v>
+        <v>1991</v>
       </c>
       <c r="G508" t="s" s="12">
-        <v>1947</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="509">
@@ -17524,19 +17813,19 @@
         <v>795</v>
       </c>
       <c r="B509" t="s" s="7">
-        <v>1948</v>
+        <v>1993</v>
       </c>
       <c r="C509" t="s" s="8">
-        <v>1949</v>
+        <v>1994</v>
       </c>
       <c r="E509" s="10">
         <v>14</v>
       </c>
       <c r="F509" t="s" s="11">
-        <v>1950</v>
+        <v>1995</v>
       </c>
       <c r="G509" t="s" s="12">
-        <v>1951</v>
+        <v>1996</v>
       </c>
     </row>
   </sheetData>
